--- a/data/base/base implantação.xlsx
+++ b/data/base/base implantação.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/warruda_mgcontecnica_com_br/Documents/Documentos/python/Portal-implantacao-tmp/data/base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="582" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B302B61B-F6AF-4175-8BE1-1778158AB9FF}"/>
+  <xr:revisionPtr revIDLastSave="607" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73EC1ED9-1A89-48FE-8703-CD14F37C8ACE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="234">
   <si>
     <t>ID</t>
   </si>
@@ -564,9 +564,6 @@
   </si>
   <si>
     <t>AA&amp;amp;MARTINS PARTICIPACOES LTDA ;ADRIANO AUGUSTO MARTINS ;E&amp;amp;G MARTINS PARTICIPACOES LTDA ;EDUARDO DE JESUS MARTINS  ; B&amp;amp;SOLAR PARTICIPACOES LTDA ;MARCOS MARQUES MARTINS ;</t>
-  </si>
-  <si>
-    <t>Karina Santos</t>
   </si>
   <si>
     <t>COMERCIO VAREJISTA DE MERCADORIAS 3M LTDA (FILIAL 1)</t>
@@ -1890,7 +1887,7 @@
         <v>54</v>
       </c>
       <c r="N4" s="9">
-        <v>46232</v>
+        <v>46290</v>
       </c>
       <c r="O4" s="5" t="s">
         <v>39</v>
@@ -1951,8 +1948,8 @@
       <c r="M5" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="N5" s="8">
-        <v>46232</v>
+      <c r="N5" s="9">
+        <v>46290</v>
       </c>
       <c r="O5" s="7" t="s">
         <v>39</v>
@@ -3145,9 +3142,7 @@
       <c r="O23" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="P23" s="7" t="s">
-        <v>176</v>
-      </c>
+      <c r="P23" s="7"/>
       <c r="Q23" s="7"/>
       <c r="R23" s="7"/>
       <c r="S23" s="7"/>
@@ -3170,7 +3165,7 @@
         <v>7012</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C24" s="5">
         <v>46235</v>
@@ -3191,7 +3186,7 @@
         <v>102</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>173</v>
@@ -3203,7 +3198,7 @@
         <v>64</v>
       </c>
       <c r="M24" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="N24" s="20">
         <v>46255</v>
@@ -3211,9 +3206,7 @@
       <c r="O24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="P24" s="7" t="s">
-        <v>176</v>
-      </c>
+      <c r="P24" s="5"/>
       <c r="Q24" s="5"/>
       <c r="R24" s="5"/>
       <c r="S24" s="5"/>
@@ -3236,7 +3229,7 @@
         <v>7014</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C25" s="7">
         <v>46235</v>
@@ -3257,19 +3250,19 @@
         <v>93</v>
       </c>
       <c r="I25" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="J25" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="J25" s="7" t="s">
+      <c r="K25" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="K25" s="7" t="s">
+      <c r="L25" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="L25" s="7" t="s">
+      <c r="M25" s="7" t="s">
         <v>184</v>
-      </c>
-      <c r="M25" s="7" t="s">
-        <v>185</v>
       </c>
       <c r="N25" s="20">
         <v>46255</v>
@@ -3277,9 +3270,7 @@
       <c r="O25" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="P25" s="7" t="s">
-        <v>176</v>
-      </c>
+      <c r="P25" s="7"/>
       <c r="Q25" s="7"/>
       <c r="R25" s="7"/>
       <c r="S25" s="7"/>
@@ -3302,7 +3293,7 @@
         <v>7015</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C26" s="5">
         <v>46235</v>
@@ -3323,10 +3314,10 @@
         <v>93</v>
       </c>
       <c r="I26" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="J26" s="5" t="s">
         <v>187</v>
-      </c>
-      <c r="J26" s="5" t="s">
-        <v>188</v>
       </c>
       <c r="K26" s="5" t="s">
         <v>174</v>
@@ -3335,7 +3326,7 @@
         <v>64</v>
       </c>
       <c r="M26" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N26" s="20">
         <v>46255</v>
@@ -3343,9 +3334,7 @@
       <c r="O26" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="P26" s="7" t="s">
-        <v>176</v>
-      </c>
+      <c r="P26" s="5"/>
       <c r="Q26" s="5"/>
       <c r="R26" s="5"/>
       <c r="S26" s="5"/>
@@ -3368,7 +3357,7 @@
         <v>7016</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C27" s="7">
         <v>46235</v>
@@ -3377,10 +3366,10 @@
         <v>169</v>
       </c>
       <c r="E27" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="F27" s="7" t="s">
         <v>191</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>192</v>
       </c>
       <c r="G27" s="7" t="s">
         <v>150</v>
@@ -3389,19 +3378,19 @@
         <v>93</v>
       </c>
       <c r="I27" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="K27" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="J27" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="K27" s="7" t="s">
+      <c r="L27" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="M27" s="7" t="s">
         <v>194</v>
-      </c>
-      <c r="L27" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="M27" s="7" t="s">
-        <v>195</v>
       </c>
       <c r="N27" s="20">
         <v>46255</v>
@@ -3409,9 +3398,7 @@
       <c r="O27" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="P27" s="7" t="s">
-        <v>176</v>
-      </c>
+      <c r="P27" s="7"/>
       <c r="Q27" s="7"/>
       <c r="R27" s="7"/>
       <c r="S27" s="7"/>
@@ -3434,7 +3421,7 @@
         <v>7017</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C28" s="5">
         <v>46235</v>
@@ -3455,7 +3442,7 @@
         <v>93</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J28" s="5" t="s">
         <v>173</v>
@@ -3467,7 +3454,7 @@
         <v>64</v>
       </c>
       <c r="M28" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N28" s="20">
         <v>46255</v>
@@ -3475,9 +3462,7 @@
       <c r="O28" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="P28" s="7" t="s">
-        <v>176</v>
-      </c>
+      <c r="P28" s="5"/>
       <c r="Q28" s="5"/>
       <c r="R28" s="5"/>
       <c r="S28" s="5"/>
@@ -3500,7 +3485,7 @@
         <v>7018</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C29" s="7">
         <v>46235</v>
@@ -3509,10 +3494,10 @@
         <v>169</v>
       </c>
       <c r="E29" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="F29" s="7" t="s">
         <v>191</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>192</v>
       </c>
       <c r="G29" s="7" t="s">
         <v>150</v>
@@ -3521,7 +3506,7 @@
         <v>93</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J29" s="7" t="s">
         <v>173</v>
@@ -3533,7 +3518,7 @@
         <v>64</v>
       </c>
       <c r="M29" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="N29" s="20">
         <v>46255</v>
@@ -3541,9 +3526,7 @@
       <c r="O29" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="P29" s="7" t="s">
-        <v>176</v>
-      </c>
+      <c r="P29" s="7"/>
       <c r="Q29" s="7"/>
       <c r="R29" s="7"/>
       <c r="S29" s="7"/>
@@ -3566,7 +3549,7 @@
         <v>7019</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C30" s="5">
         <v>46235</v>
@@ -3587,10 +3570,10 @@
         <v>93</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="K30" s="5" t="s">
         <v>174</v>
@@ -3599,7 +3582,7 @@
         <v>64</v>
       </c>
       <c r="M30" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="N30" s="20">
         <v>46255</v>
@@ -3607,9 +3590,7 @@
       <c r="O30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="P30" s="7" t="s">
-        <v>176</v>
-      </c>
+      <c r="P30" s="5"/>
       <c r="Q30" s="5"/>
       <c r="R30" s="5"/>
       <c r="S30" s="5"/>
@@ -3632,7 +3613,7 @@
         <v>7020</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C31" s="7">
         <v>46235</v>
@@ -3653,19 +3634,19 @@
         <v>93</v>
       </c>
       <c r="I31" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="L31" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="M31" s="7" t="s">
         <v>200</v>
-      </c>
-      <c r="J31" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="K31" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="L31" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="M31" s="7" t="s">
-        <v>201</v>
       </c>
       <c r="N31" s="20">
         <v>46255</v>
@@ -3673,9 +3654,7 @@
       <c r="O31" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="P31" s="7" t="s">
-        <v>176</v>
-      </c>
+      <c r="P31" s="7"/>
       <c r="Q31" s="7"/>
       <c r="R31" s="7"/>
       <c r="S31" s="7"/>
@@ -3698,7 +3677,7 @@
         <v>7021</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C32" s="5">
         <v>46235</v>
@@ -3707,10 +3686,10 @@
         <v>169</v>
       </c>
       <c r="E32" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="F32" s="5" t="s">
         <v>191</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>192</v>
       </c>
       <c r="G32" s="5" t="s">
         <v>150</v>
@@ -3719,19 +3698,19 @@
         <v>93</v>
       </c>
       <c r="I32" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="K32" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="J32" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="K32" s="5" t="s">
-        <v>194</v>
-      </c>
       <c r="L32" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="M32" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N32" s="20">
         <v>46255</v>
@@ -3739,9 +3718,7 @@
       <c r="O32" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="P32" s="7" t="s">
-        <v>176</v>
-      </c>
+      <c r="P32" s="5"/>
       <c r="Q32" s="5"/>
       <c r="R32" s="5"/>
       <c r="S32" s="5"/>
@@ -3764,16 +3741,16 @@
         <v>6992</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C33" s="7">
         <v>46266</v>
       </c>
       <c r="D33" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="E33" s="7" t="s">
         <v>204</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>205</v>
       </c>
       <c r="F33" s="7" t="s">
         <v>149</v>
@@ -3785,19 +3762,19 @@
         <v>102</v>
       </c>
       <c r="I33" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="J33" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="J33" s="7" t="s">
+      <c r="K33" s="7" t="s">
         <v>207</v>
-      </c>
-      <c r="K33" s="7" t="s">
-        <v>208</v>
       </c>
       <c r="L33" s="7" t="s">
         <v>64</v>
       </c>
       <c r="M33" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="N33" s="7"/>
       <c r="O33" s="7" t="s">
@@ -3828,16 +3805,16 @@
         <v>6993</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C34" s="5">
         <v>46266</v>
       </c>
       <c r="D34" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="E34" s="5" t="s">
         <v>204</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>205</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>149</v>
@@ -3849,19 +3826,19 @@
         <v>33</v>
       </c>
       <c r="I34" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="J34" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="J34" s="5" t="s">
+      <c r="K34" s="5" t="s">
         <v>212</v>
-      </c>
-      <c r="K34" s="5" t="s">
-        <v>213</v>
       </c>
       <c r="L34" s="5" t="s">
         <v>64</v>
       </c>
       <c r="M34" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="N34" s="5"/>
       <c r="O34" s="5" t="s">
@@ -3892,13 +3869,13 @@
         <v>6945</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C35" s="7">
         <v>46174</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>148</v>
@@ -3913,19 +3890,19 @@
         <v>33</v>
       </c>
       <c r="I35" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="J35" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="J35" s="7" t="s">
+      <c r="K35" s="7" t="s">
         <v>218</v>
-      </c>
-      <c r="K35" s="7" t="s">
-        <v>219</v>
       </c>
       <c r="L35" s="7" t="s">
         <v>37</v>
       </c>
       <c r="M35" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N35" s="8">
         <v>46219</v>
@@ -3960,19 +3937,19 @@
         <v>7036</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C36" s="5">
         <v>46266</v>
       </c>
       <c r="D36" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="E36" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="F36" s="5" t="s">
         <v>223</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>224</v>
       </c>
       <c r="G36" s="5" t="s">
         <v>150</v>
@@ -3981,32 +3958,32 @@
         <v>102</v>
       </c>
       <c r="I36" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="J36" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="J36" s="5" t="s">
+      <c r="K36" s="5" t="s">
         <v>226</v>
-      </c>
-      <c r="K36" s="5" t="s">
-        <v>227</v>
       </c>
       <c r="L36" s="5" t="s">
         <v>64</v>
       </c>
       <c r="M36" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="N36" s="5"/>
       <c r="O36" s="5" t="s">
         <v>39</v>
       </c>
       <c r="P36" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q36" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="Q36" s="5" t="s">
+      <c r="R36" s="5" t="s">
         <v>230</v>
-      </c>
-      <c r="R36" s="5" t="s">
-        <v>231</v>
       </c>
       <c r="S36" s="5"/>
       <c r="T36" s="5" t="s">
@@ -4028,19 +4005,19 @@
         <v>7037</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C37" s="15">
         <v>46266</v>
       </c>
       <c r="D37" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="E37" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="E37" s="15" t="s">
+      <c r="F37" s="15" t="s">
         <v>223</v>
-      </c>
-      <c r="F37" s="15" t="s">
-        <v>224</v>
       </c>
       <c r="G37" s="15" t="s">
         <v>150</v>
@@ -4049,32 +4026,32 @@
         <v>33</v>
       </c>
       <c r="I37" s="15" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J37" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="K37" s="15" t="s">
         <v>226</v>
-      </c>
-      <c r="K37" s="15" t="s">
-        <v>227</v>
       </c>
       <c r="L37" s="15" t="s">
         <v>64</v>
       </c>
       <c r="M37" s="15" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="N37" s="15"/>
       <c r="O37" s="15" t="s">
         <v>39</v>
       </c>
       <c r="P37" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q37" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="Q37" s="7" t="s">
+      <c r="R37" s="19" t="s">
         <v>230</v>
-      </c>
-      <c r="R37" s="19" t="s">
-        <v>231</v>
       </c>
       <c r="S37" s="15"/>
       <c r="T37" s="15" t="s">

--- a/data/base/base implantação.xlsx
+++ b/data/base/base implantação.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/warruda_mgcontecnica_com_br/Documents/Documentos/python/Portal-implantacao-tmp/data/base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="607" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73EC1ED9-1A89-48FE-8703-CD14F37C8ACE}"/>
+  <xr:revisionPtr revIDLastSave="666" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9479EFB2-9292-414F-82B7-277FD9FF53D9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="240">
   <si>
     <t>ID</t>
   </si>
@@ -739,6 +739,24 @@
   </si>
   <si>
     <t>MARIA SOCORRO BENÍCIO DA SILVA ;</t>
+  </si>
+  <si>
+    <t>RAMIRO EQUIPAMENTOS GASTRONOMICOS LTDA</t>
+  </si>
+  <si>
+    <t>RAMIRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALAMEDA SANTO AMARO, Num.: 420 Comple.: , Bairro: SANTO AMARO / </t>
+  </si>
+  <si>
+    <t>ramiroequipamentos@gmail.com;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(11) 4103-9760 / </t>
+  </si>
+  <si>
+    <t>JOÃO MACHADO NETO;LUCAS DIOGO MACHADO;FRANCISCO RAMIRO MACHADO ALVES;</t>
   </si>
 </sst>
 </file>
@@ -806,7 +824,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -914,12 +932,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -943,6 +970,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -1243,8 +1276,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:AB37">
-  <autoFilter ref="A1:AB37" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:AB59">
+  <autoFilter ref="A1:AB59" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T19">
     <sortCondition ref="D1:D19"/>
   </sortState>
@@ -1599,7 +1632,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB37"/>
+  <dimension ref="A1:AB59"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
@@ -4057,9 +4090,9 @@
       <c r="T37" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="U37" s="15"/>
-      <c r="V37" s="15"/>
-      <c r="W37" s="15"/>
+      <c r="U37" s="7"/>
+      <c r="V37" s="7"/>
+      <c r="W37" s="7"/>
       <c r="X37" s="15"/>
       <c r="Y37" s="15" t="s">
         <v>39</v>
@@ -4068,16 +4101,291 @@
       <c r="AA37" s="15"/>
       <c r="AB37" s="15"/>
     </row>
+    <row r="38" spans="1:28">
+      <c r="A38" s="25">
+        <v>7046</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>234</v>
+      </c>
+      <c r="C38" s="25">
+        <v>46266</v>
+      </c>
+      <c r="D38" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="E38" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="F38" s="25" t="s">
+        <v>163</v>
+      </c>
+      <c r="G38" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="H38" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="I38" s="25" t="s">
+        <v>236</v>
+      </c>
+      <c r="J38" s="25" t="s">
+        <v>237</v>
+      </c>
+      <c r="K38" s="25" t="s">
+        <v>238</v>
+      </c>
+      <c r="L38" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="M38" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="N38" s="1">
+        <v>46266</v>
+      </c>
+      <c r="O38" t="s">
+        <v>39</v>
+      </c>
+      <c r="S38" s="1">
+        <v>46266</v>
+      </c>
+      <c r="T38" t="s">
+        <v>39</v>
+      </c>
+      <c r="U38" s="5"/>
+      <c r="V38" s="5"/>
+      <c r="W38" s="5"/>
+      <c r="X38" s="1">
+        <v>46266</v>
+      </c>
+      <c r="Y38" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z38" s="5"/>
+      <c r="AA38" s="5"/>
+      <c r="AB38" s="5"/>
+    </row>
+    <row r="39" spans="1:28">
+      <c r="U39" s="7"/>
+      <c r="V39" s="7"/>
+      <c r="W39" s="7"/>
+      <c r="Y39" s="21"/>
+      <c r="Z39" s="15"/>
+      <c r="AA39" s="15"/>
+      <c r="AB39" s="15"/>
+    </row>
+    <row r="40" spans="1:28">
+      <c r="U40" s="5"/>
+      <c r="V40" s="5"/>
+      <c r="W40" s="5"/>
+      <c r="Y40" s="21"/>
+      <c r="Z40" s="5"/>
+      <c r="AA40" s="5"/>
+      <c r="AB40" s="5"/>
+    </row>
+    <row r="41" spans="1:28">
+      <c r="U41" s="7"/>
+      <c r="V41" s="7"/>
+      <c r="W41" s="7"/>
+      <c r="Y41" s="21"/>
+      <c r="Z41" s="15"/>
+      <c r="AA41" s="15"/>
+      <c r="AB41" s="15"/>
+    </row>
+    <row r="42" spans="1:28">
+      <c r="U42" s="5"/>
+      <c r="V42" s="5"/>
+      <c r="W42" s="5"/>
+      <c r="Y42" s="21"/>
+      <c r="Z42" s="5"/>
+      <c r="AA42" s="5"/>
+      <c r="AB42" s="5"/>
+    </row>
+    <row r="43" spans="1:28">
+      <c r="U43" s="7"/>
+      <c r="V43" s="7"/>
+      <c r="W43" s="7"/>
+      <c r="Y43" s="21"/>
+      <c r="Z43" s="15"/>
+      <c r="AA43" s="15"/>
+      <c r="AB43" s="15"/>
+    </row>
+    <row r="44" spans="1:28">
+      <c r="U44" s="5"/>
+      <c r="V44" s="5"/>
+      <c r="W44" s="5"/>
+      <c r="Y44" s="21"/>
+      <c r="Z44" s="5"/>
+      <c r="AA44" s="5"/>
+      <c r="AB44" s="5"/>
+    </row>
+    <row r="45" spans="1:28">
+      <c r="U45" s="7"/>
+      <c r="V45" s="7"/>
+      <c r="W45" s="7"/>
+      <c r="Y45" s="21"/>
+      <c r="Z45" s="15"/>
+      <c r="AA45" s="15"/>
+      <c r="AB45" s="15"/>
+    </row>
+    <row r="46" spans="1:28">
+      <c r="U46" s="5"/>
+      <c r="V46" s="5"/>
+      <c r="W46" s="5"/>
+      <c r="Y46" s="21"/>
+      <c r="Z46" s="5"/>
+      <c r="AA46" s="5"/>
+      <c r="AB46" s="5"/>
+    </row>
+    <row r="47" spans="1:28">
+      <c r="U47" s="7"/>
+      <c r="V47" s="7"/>
+      <c r="W47" s="7"/>
+      <c r="Y47" s="21"/>
+      <c r="Z47" s="15"/>
+      <c r="AA47" s="15"/>
+      <c r="AB47" s="15"/>
+    </row>
+    <row r="48" spans="1:28">
+      <c r="U48" s="5"/>
+      <c r="V48" s="5"/>
+      <c r="W48" s="5"/>
+      <c r="Y48" s="21"/>
+      <c r="Z48" s="5"/>
+      <c r="AA48" s="5"/>
+      <c r="AB48" s="5"/>
+    </row>
+    <row r="49" spans="1:28">
+      <c r="U49" s="7"/>
+      <c r="V49" s="7"/>
+      <c r="W49" s="7"/>
+      <c r="Y49" s="21"/>
+      <c r="Z49" s="15"/>
+      <c r="AA49" s="15"/>
+      <c r="AB49" s="15"/>
+    </row>
+    <row r="50" spans="1:28">
+      <c r="U50" s="5"/>
+      <c r="V50" s="5"/>
+      <c r="W50" s="5"/>
+      <c r="Y50" s="21"/>
+      <c r="Z50" s="5"/>
+      <c r="AA50" s="5"/>
+      <c r="AB50" s="5"/>
+    </row>
+    <row r="51" spans="1:28">
+      <c r="U51" s="7"/>
+      <c r="V51" s="7"/>
+      <c r="W51" s="7"/>
+      <c r="Y51" s="21"/>
+      <c r="Z51" s="15"/>
+      <c r="AA51" s="15"/>
+      <c r="AB51" s="15"/>
+    </row>
+    <row r="52" spans="1:28">
+      <c r="U52" s="5"/>
+      <c r="V52" s="5"/>
+      <c r="W52" s="5"/>
+      <c r="Y52" s="21"/>
+      <c r="Z52" s="5"/>
+      <c r="AA52" s="5"/>
+      <c r="AB52" s="5"/>
+    </row>
+    <row r="53" spans="1:28">
+      <c r="U53" s="7"/>
+      <c r="V53" s="7"/>
+      <c r="W53" s="7"/>
+      <c r="Y53" s="21"/>
+      <c r="Z53" s="15"/>
+      <c r="AA53" s="15"/>
+      <c r="AB53" s="15"/>
+    </row>
+    <row r="54" spans="1:28">
+      <c r="U54" s="5"/>
+      <c r="V54" s="5"/>
+      <c r="W54" s="5"/>
+      <c r="Y54" s="21"/>
+      <c r="Z54" s="5"/>
+      <c r="AA54" s="5"/>
+      <c r="AB54" s="5"/>
+    </row>
+    <row r="55" spans="1:28">
+      <c r="U55" s="7"/>
+      <c r="V55" s="7"/>
+      <c r="W55" s="7"/>
+      <c r="Y55" s="21"/>
+      <c r="Z55" s="15"/>
+      <c r="AA55" s="15"/>
+      <c r="AB55" s="15"/>
+    </row>
+    <row r="56" spans="1:28">
+      <c r="U56" s="5"/>
+      <c r="V56" s="5"/>
+      <c r="W56" s="5"/>
+      <c r="Y56" s="21"/>
+      <c r="Z56" s="5"/>
+      <c r="AA56" s="5"/>
+      <c r="AB56" s="5"/>
+    </row>
+    <row r="57" spans="1:28">
+      <c r="U57" s="7"/>
+      <c r="V57" s="7"/>
+      <c r="W57" s="7"/>
+      <c r="Y57" s="21"/>
+      <c r="Z57" s="15"/>
+      <c r="AA57" s="15"/>
+      <c r="AB57" s="15"/>
+    </row>
+    <row r="58" spans="1:28">
+      <c r="U58" s="5"/>
+      <c r="V58" s="5"/>
+      <c r="W58" s="5"/>
+      <c r="Y58" s="21"/>
+      <c r="Z58" s="5"/>
+      <c r="AA58" s="5"/>
+      <c r="AB58" s="5"/>
+    </row>
+    <row r="59" spans="1:28">
+      <c r="A59" s="22"/>
+      <c r="B59" s="22"/>
+      <c r="C59" s="22"/>
+      <c r="D59" s="22"/>
+      <c r="E59" s="22"/>
+      <c r="F59" s="22"/>
+      <c r="G59" s="22"/>
+      <c r="H59" s="22"/>
+      <c r="I59" s="22"/>
+      <c r="J59" s="22"/>
+      <c r="K59" s="22"/>
+      <c r="L59" s="22"/>
+      <c r="M59" s="22"/>
+      <c r="N59" s="23"/>
+      <c r="O59" s="22"/>
+      <c r="P59" s="23"/>
+      <c r="Q59" s="22"/>
+      <c r="R59" s="23"/>
+      <c r="S59" s="22"/>
+      <c r="T59" s="22"/>
+      <c r="U59" s="7"/>
+      <c r="V59" s="7"/>
+      <c r="W59" s="7"/>
+      <c r="X59" s="22"/>
+      <c r="Y59" s="24"/>
+      <c r="Z59" s="15"/>
+      <c r="AA59" s="15"/>
+      <c r="AB59" s="15"/>
+    </row>
   </sheetData>
-  <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S38:S1048576" xr:uid="{F98435C8-1E0D-420B-93AD-1750A0AD1E4D}">
+  <dataValidations count="11">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S60:S1048576" xr:uid="{F98435C8-1E0D-420B-93AD-1750A0AD1E4D}">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Insira uma data" error="O valor digitado deve ser uma data." promptTitle="Insira uma data" prompt="Use o formato dd/mm/aaaa" sqref="N38:N1048576" xr:uid="{E30AD5C4-327F-471C-A8FE-8847233F32A8}">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Insira uma data" error="O valor digitado deve ser uma data." promptTitle="Insira uma data" prompt="Use o formato dd/mm/aaaa" sqref="N60:N1048576" xr:uid="{E30AD5C4-327F-471C-A8FE-8847233F32A8}">
       <formula1>46023</formula1>
       <formula2>46387</formula2>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="O valor digitado deve ser uma data." promptTitle="Insira uma data " prompt="Use o formato dd/mm/aaaa" sqref="P38:P1048576" xr:uid="{C38150F2-07B9-4A40-94E9-2F60486C9785}">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="O valor digitado deve ser uma data." promptTitle="Insira uma data " prompt="Use o formato dd/mm/aaaa" sqref="P60:P1048576" xr:uid="{C38150F2-07B9-4A40-94E9-2F60486C9785}">
       <formula1>46023</formula1>
       <formula2>46387</formula2>
     </dataValidation>
@@ -4085,8 +4393,26 @@
       <formula1>46023</formula1>
       <formula2>46387</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Sim ou Não" promptTitle="Sim ou Não" sqref="O38:O1048576 Q38:Q1048576" xr:uid="{A33B9050-2903-44EC-9C32-C551C6DD218F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Sim ou Não" promptTitle="Sim ou Não" sqref="Q60:Q1048576 O60:O1048576" xr:uid="{A33B9050-2903-44EC-9C32-C551C6DD218F}">
       <formula1>"Sim,Não"</formula1>
+    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P59 Q2:Q59 R2:R59" xr:uid="{66A39B3A-FA32-40B1-A327-70A015F2D105}"/>
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Data inválida" error="Informe uma data entre 01/01/2026 e 31/12/2026." sqref="S2:S59 X2:X59" xr:uid="{7CAE3D66-F37A-4DC6-831F-B6867AFE899B}">
+      <formula1>46023</formula1>
+      <formula2>46387</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Sim ou Não" promptTitle="Sim ou Não" sqref="Y2:Y59" xr:uid="{A8256CAE-D3ED-469B-B2FC-C7F240BFF314}">
+      <formula1>"Sim,Não"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Sim ou Não" promptTitle="Sim ou Não" sqref="O2:O59 T2:T59" xr:uid="{2B1CDC7A-A9D4-4E67-B8E0-C4C62588687E}">
+      <formula1>"Sim,Não"</formula1>
+    </dataValidation>
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Data inválida" error="Informe uma data entre 01/01/2026 e 31/12/2026." sqref="N2:N59" xr:uid="{1714F817-F282-4D50-B48A-1A4077276E1B}">
+      <formula1>46023</formula1>
+      <formula2>46387</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Sim ou Não" promptTitle="Sim ou Não" sqref="O2:O59" xr:uid="{DA1ED78E-091C-41E8-9E96-D1D63B85A012}">
+      <formula1>"Sim;Não"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>

--- a/data/base/base implantação.xlsx
+++ b/data/base/base implantação.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/warruda_mgcontecnica_com_br/Documents/Documentos/python/Portal-implantacao-tmp/data/base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="692" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37F68BA8-8CAF-4072-AC05-1E70B31825A7}"/>
+  <xr:revisionPtr revIDLastSave="700" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{935379C5-444B-4E2C-8705-7F2841D7C7C9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3048,9 +3048,11 @@
       <c r="P21" s="7"/>
       <c r="Q21" s="7"/>
       <c r="R21" s="7"/>
-      <c r="S21" s="7"/>
+      <c r="S21" s="25">
+        <v>46255</v>
+      </c>
       <c r="T21" s="7" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="U21" s="7"/>
       <c r="V21" s="7"/>
@@ -3112,9 +3114,11 @@
       <c r="P22" s="5"/>
       <c r="Q22" s="5"/>
       <c r="R22" s="5"/>
-      <c r="S22" s="5"/>
+      <c r="S22" s="25">
+        <v>46255</v>
+      </c>
       <c r="T22" s="5" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="U22" s="5"/>
       <c r="V22" s="5"/>
@@ -3176,9 +3180,11 @@
       <c r="P23" s="7"/>
       <c r="Q23" s="7"/>
       <c r="R23" s="7"/>
-      <c r="S23" s="7"/>
+      <c r="S23" s="25">
+        <v>46255</v>
+      </c>
       <c r="T23" s="7" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="U23" s="7"/>
       <c r="V23" s="7"/>
@@ -3240,9 +3246,11 @@
       <c r="P24" s="5"/>
       <c r="Q24" s="5"/>
       <c r="R24" s="5"/>
-      <c r="S24" s="5"/>
+      <c r="S24" s="25">
+        <v>46255</v>
+      </c>
       <c r="T24" s="5" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="U24" s="5"/>
       <c r="V24" s="5"/>
@@ -3304,9 +3312,11 @@
       <c r="P25" s="7"/>
       <c r="Q25" s="7"/>
       <c r="R25" s="7"/>
-      <c r="S25" s="7"/>
+      <c r="S25" s="25">
+        <v>46255</v>
+      </c>
       <c r="T25" s="7" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="U25" s="7"/>
       <c r="V25" s="7"/>
@@ -3368,9 +3378,11 @@
       <c r="P26" s="5"/>
       <c r="Q26" s="5"/>
       <c r="R26" s="5"/>
-      <c r="S26" s="5"/>
+      <c r="S26" s="25">
+        <v>46255</v>
+      </c>
       <c r="T26" s="5" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="U26" s="5"/>
       <c r="V26" s="5"/>
@@ -3432,9 +3444,11 @@
       <c r="P27" s="7"/>
       <c r="Q27" s="7"/>
       <c r="R27" s="7"/>
-      <c r="S27" s="7"/>
+      <c r="S27" s="25">
+        <v>46255</v>
+      </c>
       <c r="T27" s="7" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="U27" s="7"/>
       <c r="V27" s="7"/>
@@ -3496,9 +3510,11 @@
       <c r="P28" s="5"/>
       <c r="Q28" s="5"/>
       <c r="R28" s="5"/>
-      <c r="S28" s="5"/>
+      <c r="S28" s="25">
+        <v>46255</v>
+      </c>
       <c r="T28" s="5" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="U28" s="5"/>
       <c r="V28" s="5"/>
@@ -3560,9 +3576,11 @@
       <c r="P29" s="7"/>
       <c r="Q29" s="7"/>
       <c r="R29" s="7"/>
-      <c r="S29" s="7"/>
+      <c r="S29" s="25">
+        <v>46255</v>
+      </c>
       <c r="T29" s="7" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="U29" s="7"/>
       <c r="V29" s="7"/>
@@ -3624,9 +3642,11 @@
       <c r="P30" s="5"/>
       <c r="Q30" s="5"/>
       <c r="R30" s="5"/>
-      <c r="S30" s="5"/>
+      <c r="S30" s="25">
+        <v>46255</v>
+      </c>
       <c r="T30" s="5" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="U30" s="5"/>
       <c r="V30" s="5"/>

--- a/data/base/base implantação.xlsx
+++ b/data/base/base implantação.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/warruda_mgcontecnica_com_br/Documents/Documentos/python/Portal-implantacao-tmp/data/base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="700" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{935379C5-444B-4E2C-8705-7F2841D7C7C9}"/>
+  <xr:revisionPtr revIDLastSave="703" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8A5266C-6756-4668-8F92-29330977C1D8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -946,7 +946,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -973,11 +973,12 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="1" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -2977,7 +2978,9 @@
       <c r="M20" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="N20" s="5"/>
+      <c r="N20" s="9">
+        <v>46269</v>
+      </c>
       <c r="O20" s="5" t="s">
         <v>39</v>
       </c>
@@ -4095,7 +4098,9 @@
       <c r="M37" s="23" t="s">
         <v>233</v>
       </c>
-      <c r="N37" s="23"/>
+      <c r="N37" s="29">
+        <v>46261</v>
+      </c>
       <c r="O37" s="23" t="s">
         <v>39</v>
       </c>
@@ -4163,7 +4168,9 @@
       <c r="M38" s="24" t="s">
         <v>239</v>
       </c>
-      <c r="N38" s="24"/>
+      <c r="N38" s="29">
+        <v>46261</v>
+      </c>
       <c r="O38" s="24" t="s">
         <v>39</v>
       </c>
@@ -4400,7 +4407,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Sim ou Não" promptTitle="Sim ou Não" sqref="Q60:Q1048576 O2:O1048576 T2:T59 Y2:Y59" xr:uid="{A33B9050-2903-44EC-9C32-C551C6DD218F}">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P59 Q2:Q59 R2:R59" xr:uid="{66A39B3A-FA32-40B1-A327-70A015F2D105}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:R59" xr:uid="{66A39B3A-FA32-40B1-A327-70A015F2D105}"/>
     <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Data inválida" error="Informe uma data entre 01/01/2026 e 31/12/2026." sqref="S2:S59 X2:X59 N2:N59" xr:uid="{7CAE3D66-F37A-4DC6-831F-B6867AFE899B}">
       <formula1>46023</formula1>
       <formula2>46387</formula2>

--- a/data/base/base implantação.xlsx
+++ b/data/base/base implantação.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/warruda_mgcontecnica_com_br/Documents/Documentos/python/Portal-implantacao-tmp/data/base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="703" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8A5266C-6756-4668-8F92-29330977C1D8}"/>
+  <xr:revisionPtr revIDLastSave="705" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3E91385-5392-46FA-8B46-53FE4CA7BCA3}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4041,9 +4041,11 @@
       <c r="P36" s="7"/>
       <c r="Q36" s="7"/>
       <c r="R36" s="7"/>
-      <c r="S36" s="7"/>
+      <c r="S36" s="8">
+        <v>46252</v>
+      </c>
       <c r="T36" s="7" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="U36" s="7"/>
       <c r="V36" s="7"/>

--- a/data/base/base implantação.xlsx
+++ b/data/base/base implantação.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/warruda_mgcontecnica_com_br/Documents/Documentos/python/Portal-implantacao-tmp/data/base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="705" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3E91385-5392-46FA-8B46-53FE4CA7BCA3}"/>
+  <xr:revisionPtr revIDLastSave="709" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83A67BCB-0069-4010-8017-41CE7CA277CD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2787,7 +2787,7 @@
         <v>138</v>
       </c>
       <c r="N17" s="25">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="O17" s="27" t="s">
         <v>39</v>
@@ -2796,7 +2796,7 @@
       <c r="Q17" s="27"/>
       <c r="R17" s="25"/>
       <c r="S17" s="25">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="T17" s="27" t="s">
         <v>39</v>
@@ -4410,7 +4410,7 @@
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:R59" xr:uid="{66A39B3A-FA32-40B1-A327-70A015F2D105}"/>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Data inválida" error="Informe uma data entre 01/01/2026 e 31/12/2026." sqref="S2:S59 X2:X59 N2:N59" xr:uid="{7CAE3D66-F37A-4DC6-831F-B6867AFE899B}">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Data inválida" error="Informe uma data entre 01/01/2026 e 31/12/2026." sqref="N2:N59 X2:X59 S2:S59" xr:uid="{7CAE3D66-F37A-4DC6-831F-B6867AFE899B}">
       <formula1>46023</formula1>
       <formula2>46387</formula2>
     </dataValidation>

--- a/data/base/base implantação.xlsx
+++ b/data/base/base implantação.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/warruda_mgcontecnica_com_br/Documents/Documentos/python/Portal-implantacao-tmp/data/base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="709" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83A67BCB-0069-4010-8017-41CE7CA277CD}"/>
+  <xr:revisionPtr revIDLastSave="734" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B3FE630-3F1F-4A86-8D7D-97071C63F087}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="273">
   <si>
     <t>ID</t>
   </si>
@@ -750,6 +750,18 @@
     <t>(11) 9181-5736</t>
   </si>
   <si>
+    <t>Fernanda</t>
+  </si>
+  <si>
+    <t>faturamento01@viasupri.com.br</t>
+  </si>
+  <si>
+    <t>Michele</t>
+  </si>
+  <si>
+    <t>adm@viasupri.com.br</t>
+  </si>
+  <si>
     <t>EXPAND COMERCIO E SERVICOS ADMINISTRATIVOS LTDA</t>
   </si>
   <si>
@@ -757,6 +769,93 @@
   </si>
   <si>
     <t>MARIA SOCORRO BENÍCIO DA SILVA ;</t>
+  </si>
+  <si>
+    <t>AMANCIO S ELETRICA, HIDRAULICA E CONSTRUCAO EM GERAL LTDA (MATRIZ)</t>
+  </si>
+  <si>
+    <t>RC MATERIAIS</t>
+  </si>
+  <si>
+    <t>Joyce Cristinne - SAC;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUA GARCIA DE ORTA, Num.: 272 Comple.: , Bairro: PARQUE INDEPENDÊNCIA / </t>
+  </si>
+  <si>
+    <t>amancio.eletrica@bol.com.br;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(11) 5873-6083 / </t>
+  </si>
+  <si>
+    <t>GISELA NEVES MOREIRA AMANCIO;ADRIANO PEREIRA AMANCIO;</t>
+  </si>
+  <si>
+    <t>AMANCIO S ELETRICA, HIDRAULICA E CONSTRUCAO EM GERAL LTDA (FILIAL 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVENIDA DA MOENDA VELHA , Num.: 71 Comple.: , Bairro: PARQUE INDEPENDÊNCIA / </t>
+  </si>
+  <si>
+    <t>ADRIANO PEREIRA AMANCIO;GISELA NEVES MOREIRA AMANCIO;</t>
+  </si>
+  <si>
+    <t>BANDEIRANTE SUPERMERCADOS MIRASSOL LTDA</t>
+  </si>
+  <si>
+    <t>SUP. BANDEIRANTE</t>
+  </si>
+  <si>
+    <t> </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rua 9 de Julho , Num.: 1621 Comple.: , Bairro: Centro  / </t>
+  </si>
+  <si>
+    <t>paulo@bandeirantesupermercados.com.br;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(17) 3243-7290 / </t>
+  </si>
+  <si>
+    <t>Paulo Massaharu Takata ;</t>
+  </si>
+  <si>
+    <t>VITAL TRANSPORTE E LOGISTICA INTELIGENTE LTDA</t>
+  </si>
+  <si>
+    <t>VITAL TRANSPORTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AVENIDA MONSENHOR ALDERIGI, Num.: 255 Comple.: SALA 25, Bairro: JARDIM COUNTRY CLUB / </t>
+  </si>
+  <si>
+    <t>pedro.rabelo@vitaltransporte.com.br;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48 9963-0671 / </t>
+  </si>
+  <si>
+    <t>PABLO HENRIQUE CONINCK PACHECO;</t>
+  </si>
+  <si>
+    <t>NANDAMATOS STORE LTDA</t>
+  </si>
+  <si>
+    <t>NANDAMATOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUA DIOLINA BATISTA, Num.: 164 Comple.: , Bairro: SETOR PARQUE TREMENDÃO  / </t>
+  </si>
+  <si>
+    <t>nandamatos.storesfinanceiro@gmail.com;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(62) 99250-1081 / </t>
+  </si>
+  <si>
+    <t>FERNANDA DIAS DE MATOS;</t>
   </si>
 </sst>
 </file>
@@ -824,7 +923,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -941,12 +1040,56 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF44B3E1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF44B3E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF44B3E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF44B3E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF44B3E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF44B3E1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF44B3E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF44B3E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -979,6 +1122,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="1" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -1659,12 +1812,12 @@
     <col min="19" max="19" width="17.140625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="27.5703125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="30.5703125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="28.140625" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="14.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4104,7 +4257,7 @@
         <v>46261</v>
       </c>
       <c r="O37" s="23" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="P37" s="5" t="s">
         <v>234</v>
@@ -4115,19 +4268,29 @@
       <c r="R37" s="28" t="s">
         <v>236</v>
       </c>
-      <c r="S37" s="23"/>
+      <c r="S37" s="29">
+        <v>46261</v>
+      </c>
       <c r="T37" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="U37" s="5"/>
-      <c r="V37" s="5"/>
+        <v>49</v>
+      </c>
+      <c r="U37" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="V37" s="30" t="s">
+        <v>238</v>
+      </c>
       <c r="W37" s="5"/>
       <c r="X37" s="23"/>
       <c r="Y37" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="Z37" s="23"/>
-      <c r="AA37" s="23"/>
+      <c r="Z37" s="23" t="s">
+        <v>239</v>
+      </c>
+      <c r="AA37" s="31" t="s">
+        <v>240</v>
+      </c>
       <c r="AB37" s="23"/>
     </row>
     <row r="38" spans="1:28">
@@ -4135,7 +4298,7 @@
         <v>7037</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C38" s="20">
         <v>46266</v>
@@ -4156,7 +4319,7 @@
         <v>33</v>
       </c>
       <c r="I38" s="20" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="J38" s="20" t="s">
         <v>231</v>
@@ -4168,13 +4331,13 @@
         <v>73</v>
       </c>
       <c r="M38" s="24" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="N38" s="29">
         <v>46261</v>
       </c>
       <c r="O38" s="24" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="P38" s="24" t="s">
         <v>234</v>
@@ -4185,22 +4348,71 @@
       <c r="R38" s="18" t="s">
         <v>236</v>
       </c>
-      <c r="S38" s="24"/>
+      <c r="S38" s="29">
+        <v>46261</v>
+      </c>
       <c r="T38" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="U38" s="7"/>
-      <c r="V38" s="7"/>
+        <v>49</v>
+      </c>
+      <c r="U38" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="V38" s="30" t="s">
+        <v>238</v>
+      </c>
       <c r="W38" s="7"/>
       <c r="X38" s="24"/>
       <c r="Y38" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="Z38" s="7"/>
-      <c r="AA38" s="7"/>
+      <c r="Z38" s="23" t="s">
+        <v>239</v>
+      </c>
+      <c r="AA38" s="18" t="s">
+        <v>240</v>
+      </c>
       <c r="AB38" s="7"/>
     </row>
     <row r="39" spans="1:28">
+      <c r="A39" s="38">
+        <v>6990</v>
+      </c>
+      <c r="B39" s="39" t="s">
+        <v>244</v>
+      </c>
+      <c r="C39" s="39">
+        <v>46235</v>
+      </c>
+      <c r="D39" s="39" t="s">
+        <v>245</v>
+      </c>
+      <c r="E39" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="F39" s="39" t="s">
+        <v>246</v>
+      </c>
+      <c r="G39" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="H39" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="I39" s="39" t="s">
+        <v>247</v>
+      </c>
+      <c r="J39" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="K39" s="39" t="s">
+        <v>249</v>
+      </c>
+      <c r="L39" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="M39" s="39" t="s">
+        <v>250</v>
+      </c>
       <c r="U39" s="7"/>
       <c r="V39" s="7"/>
       <c r="W39" s="7"/>
@@ -4210,6 +4422,45 @@
       <c r="AB39" s="14"/>
     </row>
     <row r="40" spans="1:28">
+      <c r="A40" s="34">
+        <v>6991</v>
+      </c>
+      <c r="B40" s="35" t="s">
+        <v>251</v>
+      </c>
+      <c r="C40" s="35">
+        <v>46235</v>
+      </c>
+      <c r="D40" s="35" t="s">
+        <v>245</v>
+      </c>
+      <c r="E40" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="F40" s="35" t="s">
+        <v>246</v>
+      </c>
+      <c r="G40" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="H40" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="I40" s="35" t="s">
+        <v>252</v>
+      </c>
+      <c r="J40" s="35" t="s">
+        <v>248</v>
+      </c>
+      <c r="K40" s="35" t="s">
+        <v>249</v>
+      </c>
+      <c r="L40" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="M40" s="35" t="s">
+        <v>253</v>
+      </c>
       <c r="U40" s="5"/>
       <c r="V40" s="5"/>
       <c r="W40" s="5"/>
@@ -4219,6 +4470,43 @@
       <c r="AB40" s="5"/>
     </row>
     <row r="41" spans="1:28">
+      <c r="A41" s="34">
+        <v>4252</v>
+      </c>
+      <c r="B41" s="35" t="s">
+        <v>254</v>
+      </c>
+      <c r="C41" s="35">
+        <v>44162</v>
+      </c>
+      <c r="D41" s="36" t="s">
+        <v>255</v>
+      </c>
+      <c r="E41" s="37"/>
+      <c r="F41" s="35" t="s">
+        <v>256</v>
+      </c>
+      <c r="G41" s="35" t="s">
+        <v>256</v>
+      </c>
+      <c r="H41" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="I41" s="35" t="s">
+        <v>257</v>
+      </c>
+      <c r="J41" s="35" t="s">
+        <v>258</v>
+      </c>
+      <c r="K41" s="35" t="s">
+        <v>259</v>
+      </c>
+      <c r="L41" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="M41" s="35" t="s">
+        <v>260</v>
+      </c>
       <c r="U41" s="7"/>
       <c r="V41" s="7"/>
       <c r="W41" s="7"/>
@@ -4228,6 +4516,45 @@
       <c r="AB41" s="14"/>
     </row>
     <row r="42" spans="1:28">
+      <c r="A42" s="32">
+        <v>7050</v>
+      </c>
+      <c r="B42" s="33" t="s">
+        <v>261</v>
+      </c>
+      <c r="C42" s="33">
+        <v>46266</v>
+      </c>
+      <c r="D42" s="33" t="s">
+        <v>262</v>
+      </c>
+      <c r="E42" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="F42" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="G42" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="H42" s="33" t="s">
+        <v>111</v>
+      </c>
+      <c r="I42" s="33" t="s">
+        <v>263</v>
+      </c>
+      <c r="J42" s="33" t="s">
+        <v>264</v>
+      </c>
+      <c r="K42" s="33" t="s">
+        <v>265</v>
+      </c>
+      <c r="L42" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="M42" s="33" t="s">
+        <v>266</v>
+      </c>
       <c r="U42" s="5"/>
       <c r="V42" s="5"/>
       <c r="W42" s="5"/>
@@ -4237,6 +4564,45 @@
       <c r="AB42" s="5"/>
     </row>
     <row r="43" spans="1:28">
+      <c r="A43" s="32">
+        <v>7048</v>
+      </c>
+      <c r="B43" s="33" t="s">
+        <v>267</v>
+      </c>
+      <c r="C43" s="33">
+        <v>46266</v>
+      </c>
+      <c r="D43" s="33" t="s">
+        <v>268</v>
+      </c>
+      <c r="E43" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="F43" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="G43" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="H43" s="33" t="s">
+        <v>111</v>
+      </c>
+      <c r="I43" s="33" t="s">
+        <v>269</v>
+      </c>
+      <c r="J43" s="33" t="s">
+        <v>270</v>
+      </c>
+      <c r="K43" s="33" t="s">
+        <v>271</v>
+      </c>
+      <c r="L43" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="M43" s="33" t="s">
+        <v>272</v>
+      </c>
       <c r="U43" s="7"/>
       <c r="V43" s="7"/>
       <c r="W43" s="7"/>
@@ -4423,10 +4789,13 @@
     <hyperlink ref="J3" r:id="rId2" xr:uid="{2C71ACE8-F29E-423C-AC01-4FFAE1F9088D}"/>
     <hyperlink ref="Q37" r:id="rId3" xr:uid="{E698CFD6-B238-46F2-B3C1-0504D5AFD533}"/>
     <hyperlink ref="Q38" r:id="rId4" xr:uid="{7A13F7C7-377F-4FEF-8EE6-CBF954B876C0}"/>
+    <hyperlink ref="V38" r:id="rId5" xr:uid="{CB6E0BC5-D492-4C21-A804-140655BAA4EC}"/>
+    <hyperlink ref="AA37" r:id="rId6" xr:uid="{CD1B56FA-D520-4276-A597-5265A809594E}"/>
+    <hyperlink ref="V37" r:id="rId7" xr:uid="{09992C2A-6C99-44DD-A65D-579BACD92DA4}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <tableParts count="1">
-    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId8"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/base/base implantação.xlsx
+++ b/data/base/base implantação.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/warruda_mgcontecnica_com_br/Documents/Documentos/python/Portal-implantacao-tmp/data/base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="734" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B3FE630-3F1F-4A86-8D7D-97071C63F087}"/>
+  <xr:revisionPtr revIDLastSave="735" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3CBBAEDC-971A-409B-9991-BA5CE5A1DBF6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="266">
   <si>
     <t>ID</t>
   </si>
@@ -799,27 +799,6 @@
   </si>
   <si>
     <t>ADRIANO PEREIRA AMANCIO;GISELA NEVES MOREIRA AMANCIO;</t>
-  </si>
-  <si>
-    <t>BANDEIRANTE SUPERMERCADOS MIRASSOL LTDA</t>
-  </si>
-  <si>
-    <t>SUP. BANDEIRANTE</t>
-  </si>
-  <si>
-    <t> </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rua 9 de Julho , Num.: 1621 Comple.: , Bairro: Centro  / </t>
-  </si>
-  <si>
-    <t>paulo@bandeirantesupermercados.com.br;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(17) 3243-7290 / </t>
-  </si>
-  <si>
-    <t>Paulo Massaharu Takata ;</t>
   </si>
   <si>
     <t>VITAL TRANSPORTE E LOGISTICA INTELIGENTE LTDA</t>
@@ -1089,7 +1068,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1124,14 +1103,12 @@
     <xf numFmtId="14" fontId="1" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -1432,10 +1409,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:AB59">
-  <autoFilter ref="A1:AB59" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AB59">
-    <sortCondition ref="D1:D59"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:AB58">
+  <autoFilter ref="A1:AB58" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AB58">
+    <sortCondition ref="D1:D58"/>
   </sortState>
   <tableColumns count="28">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" totalsRowFunction="average"/>
@@ -1788,7 +1765,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB59"/>
+  <dimension ref="A1:AB58"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
@@ -4374,43 +4351,43 @@
       <c r="AB38" s="7"/>
     </row>
     <row r="39" spans="1:28">
-      <c r="A39" s="38">
+      <c r="A39" s="36">
         <v>6990</v>
       </c>
-      <c r="B39" s="39" t="s">
+      <c r="B39" s="37" t="s">
         <v>244</v>
       </c>
-      <c r="C39" s="39">
+      <c r="C39" s="37">
         <v>46235</v>
       </c>
-      <c r="D39" s="39" t="s">
+      <c r="D39" s="37" t="s">
         <v>245</v>
       </c>
-      <c r="E39" s="39" t="s">
+      <c r="E39" s="37" t="s">
         <v>133</v>
       </c>
-      <c r="F39" s="39" t="s">
+      <c r="F39" s="37" t="s">
         <v>246</v>
       </c>
-      <c r="G39" s="39" t="s">
+      <c r="G39" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="H39" s="39" t="s">
+      <c r="H39" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="I39" s="39" t="s">
+      <c r="I39" s="37" t="s">
         <v>247</v>
       </c>
-      <c r="J39" s="39" t="s">
+      <c r="J39" s="37" t="s">
         <v>248</v>
       </c>
-      <c r="K39" s="39" t="s">
+      <c r="K39" s="37" t="s">
         <v>249</v>
       </c>
-      <c r="L39" s="39" t="s">
+      <c r="L39" s="37" t="s">
         <v>73</v>
       </c>
-      <c r="M39" s="39" t="s">
+      <c r="M39" s="37" t="s">
         <v>250</v>
       </c>
       <c r="U39" s="7"/>
@@ -4470,63 +4447,65 @@
       <c r="AB40" s="5"/>
     </row>
     <row r="41" spans="1:28">
-      <c r="A41" s="34">
-        <v>4252</v>
-      </c>
-      <c r="B41" s="35" t="s">
+      <c r="A41" s="32">
+        <v>7050</v>
+      </c>
+      <c r="B41" s="33" t="s">
         <v>254</v>
       </c>
-      <c r="C41" s="35">
-        <v>44162</v>
-      </c>
-      <c r="D41" s="36" t="s">
+      <c r="C41" s="33">
+        <v>46266</v>
+      </c>
+      <c r="D41" s="33" t="s">
         <v>255</v>
       </c>
-      <c r="E41" s="37"/>
-      <c r="F41" s="35" t="s">
+      <c r="E41" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="F41" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="G41" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="H41" s="33" t="s">
+        <v>111</v>
+      </c>
+      <c r="I41" s="33" t="s">
         <v>256</v>
       </c>
-      <c r="G41" s="35" t="s">
-        <v>256</v>
-      </c>
-      <c r="H41" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="I41" s="35" t="s">
+      <c r="J41" s="33" t="s">
         <v>257</v>
       </c>
-      <c r="J41" s="35" t="s">
+      <c r="K41" s="33" t="s">
         <v>258</v>
       </c>
-      <c r="K41" s="35" t="s">
+      <c r="L41" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="M41" s="33" t="s">
         <v>259</v>
       </c>
-      <c r="L41" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="M41" s="35" t="s">
-        <v>260</v>
-      </c>
-      <c r="U41" s="7"/>
-      <c r="V41" s="7"/>
-      <c r="W41" s="7"/>
+      <c r="U41" s="5"/>
+      <c r="V41" s="5"/>
+      <c r="W41" s="5"/>
       <c r="Y41" s="7"/>
-      <c r="Z41" s="14"/>
-      <c r="AA41" s="14"/>
-      <c r="AB41" s="14"/>
+      <c r="Z41" s="5"/>
+      <c r="AA41" s="5"/>
+      <c r="AB41" s="5"/>
     </row>
     <row r="42" spans="1:28">
       <c r="A42" s="32">
-        <v>7050</v>
+        <v>7048</v>
       </c>
       <c r="B42" s="33" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C42" s="33">
         <v>46266</v>
       </c>
       <c r="D42" s="33" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E42" s="33" t="s">
         <v>198</v>
@@ -4541,246 +4520,198 @@
         <v>111</v>
       </c>
       <c r="I42" s="33" t="s">
+        <v>262</v>
+      </c>
+      <c r="J42" s="33" t="s">
         <v>263</v>
       </c>
-      <c r="J42" s="33" t="s">
+      <c r="K42" s="33" t="s">
         <v>264</v>
-      </c>
-      <c r="K42" s="33" t="s">
-        <v>265</v>
       </c>
       <c r="L42" s="33" t="s">
         <v>37</v>
       </c>
       <c r="M42" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="U42" s="5"/>
-      <c r="V42" s="5"/>
-      <c r="W42" s="5"/>
+        <v>265</v>
+      </c>
+      <c r="U42" s="7"/>
+      <c r="V42" s="7"/>
+      <c r="W42" s="7"/>
       <c r="Y42" s="7"/>
-      <c r="Z42" s="5"/>
-      <c r="AA42" s="5"/>
-      <c r="AB42" s="5"/>
+      <c r="Z42" s="14"/>
+      <c r="AA42" s="14"/>
+      <c r="AB42" s="14"/>
     </row>
     <row r="43" spans="1:28">
-      <c r="A43" s="32">
-        <v>7048</v>
-      </c>
-      <c r="B43" s="33" t="s">
-        <v>267</v>
-      </c>
-      <c r="C43" s="33">
-        <v>46266</v>
-      </c>
-      <c r="D43" s="33" t="s">
-        <v>268</v>
-      </c>
-      <c r="E43" s="33" t="s">
-        <v>198</v>
-      </c>
-      <c r="F43" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="G43" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="H43" s="33" t="s">
-        <v>111</v>
-      </c>
-      <c r="I43" s="33" t="s">
-        <v>269</v>
-      </c>
-      <c r="J43" s="33" t="s">
-        <v>270</v>
-      </c>
-      <c r="K43" s="33" t="s">
-        <v>271</v>
-      </c>
-      <c r="L43" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="M43" s="33" t="s">
-        <v>272</v>
-      </c>
-      <c r="U43" s="7"/>
-      <c r="V43" s="7"/>
-      <c r="W43" s="7"/>
+      <c r="U43" s="5"/>
+      <c r="V43" s="5"/>
+      <c r="W43" s="5"/>
       <c r="Y43" s="7"/>
-      <c r="Z43" s="14"/>
-      <c r="AA43" s="14"/>
-      <c r="AB43" s="14"/>
+      <c r="Z43" s="5"/>
+      <c r="AA43" s="5"/>
+      <c r="AB43" s="5"/>
     </row>
     <row r="44" spans="1:28">
-      <c r="U44" s="5"/>
-      <c r="V44" s="5"/>
-      <c r="W44" s="5"/>
+      <c r="U44" s="7"/>
+      <c r="V44" s="7"/>
+      <c r="W44" s="7"/>
       <c r="Y44" s="7"/>
-      <c r="Z44" s="5"/>
-      <c r="AA44" s="5"/>
-      <c r="AB44" s="5"/>
+      <c r="Z44" s="14"/>
+      <c r="AA44" s="14"/>
+      <c r="AB44" s="14"/>
     </row>
     <row r="45" spans="1:28">
-      <c r="U45" s="7"/>
-      <c r="V45" s="7"/>
-      <c r="W45" s="7"/>
+      <c r="U45" s="5"/>
+      <c r="V45" s="5"/>
+      <c r="W45" s="5"/>
       <c r="Y45" s="7"/>
-      <c r="Z45" s="14"/>
-      <c r="AA45" s="14"/>
-      <c r="AB45" s="14"/>
+      <c r="Z45" s="5"/>
+      <c r="AA45" s="5"/>
+      <c r="AB45" s="5"/>
     </row>
     <row r="46" spans="1:28">
-      <c r="U46" s="5"/>
-      <c r="V46" s="5"/>
-      <c r="W46" s="5"/>
+      <c r="U46" s="7"/>
+      <c r="V46" s="7"/>
+      <c r="W46" s="7"/>
       <c r="Y46" s="7"/>
-      <c r="Z46" s="5"/>
-      <c r="AA46" s="5"/>
-      <c r="AB46" s="5"/>
+      <c r="Z46" s="14"/>
+      <c r="AA46" s="14"/>
+      <c r="AB46" s="14"/>
     </row>
     <row r="47" spans="1:28">
-      <c r="U47" s="7"/>
-      <c r="V47" s="7"/>
-      <c r="W47" s="7"/>
+      <c r="U47" s="5"/>
+      <c r="V47" s="5"/>
+      <c r="W47" s="5"/>
       <c r="Y47" s="7"/>
-      <c r="Z47" s="14"/>
-      <c r="AA47" s="14"/>
-      <c r="AB47" s="14"/>
+      <c r="Z47" s="5"/>
+      <c r="AA47" s="5"/>
+      <c r="AB47" s="5"/>
     </row>
     <row r="48" spans="1:28">
-      <c r="U48" s="5"/>
-      <c r="V48" s="5"/>
-      <c r="W48" s="5"/>
+      <c r="U48" s="7"/>
+      <c r="V48" s="7"/>
+      <c r="W48" s="7"/>
       <c r="Y48" s="7"/>
-      <c r="Z48" s="5"/>
-      <c r="AA48" s="5"/>
-      <c r="AB48" s="5"/>
+      <c r="Z48" s="14"/>
+      <c r="AA48" s="14"/>
+      <c r="AB48" s="14"/>
     </row>
     <row r="49" spans="21:28">
-      <c r="U49" s="7"/>
-      <c r="V49" s="7"/>
-      <c r="W49" s="7"/>
+      <c r="U49" s="5"/>
+      <c r="V49" s="5"/>
+      <c r="W49" s="5"/>
       <c r="Y49" s="7"/>
-      <c r="Z49" s="14"/>
-      <c r="AA49" s="14"/>
-      <c r="AB49" s="14"/>
+      <c r="Z49" s="5"/>
+      <c r="AA49" s="5"/>
+      <c r="AB49" s="5"/>
     </row>
     <row r="50" spans="21:28">
-      <c r="U50" s="5"/>
-      <c r="V50" s="5"/>
-      <c r="W50" s="5"/>
+      <c r="U50" s="7"/>
+      <c r="V50" s="7"/>
+      <c r="W50" s="7"/>
       <c r="Y50" s="7"/>
-      <c r="Z50" s="5"/>
-      <c r="AA50" s="5"/>
-      <c r="AB50" s="5"/>
+      <c r="Z50" s="14"/>
+      <c r="AA50" s="14"/>
+      <c r="AB50" s="14"/>
     </row>
     <row r="51" spans="21:28">
-      <c r="U51" s="7"/>
-      <c r="V51" s="7"/>
-      <c r="W51" s="7"/>
+      <c r="U51" s="5"/>
+      <c r="V51" s="5"/>
+      <c r="W51" s="5"/>
       <c r="Y51" s="7"/>
-      <c r="Z51" s="14"/>
-      <c r="AA51" s="14"/>
-      <c r="AB51" s="14"/>
+      <c r="Z51" s="5"/>
+      <c r="AA51" s="5"/>
+      <c r="AB51" s="5"/>
     </row>
     <row r="52" spans="21:28">
-      <c r="U52" s="5"/>
-      <c r="V52" s="5"/>
-      <c r="W52" s="5"/>
+      <c r="U52" s="7"/>
+      <c r="V52" s="7"/>
+      <c r="W52" s="7"/>
       <c r="Y52" s="7"/>
-      <c r="Z52" s="5"/>
-      <c r="AA52" s="5"/>
-      <c r="AB52" s="5"/>
+      <c r="Z52" s="14"/>
+      <c r="AA52" s="14"/>
+      <c r="AB52" s="14"/>
     </row>
     <row r="53" spans="21:28">
-      <c r="U53" s="7"/>
-      <c r="V53" s="7"/>
-      <c r="W53" s="7"/>
+      <c r="U53" s="5"/>
+      <c r="V53" s="5"/>
+      <c r="W53" s="5"/>
       <c r="Y53" s="7"/>
-      <c r="Z53" s="14"/>
-      <c r="AA53" s="14"/>
-      <c r="AB53" s="14"/>
+      <c r="Z53" s="5"/>
+      <c r="AA53" s="5"/>
+      <c r="AB53" s="5"/>
     </row>
     <row r="54" spans="21:28">
-      <c r="U54" s="5"/>
-      <c r="V54" s="5"/>
-      <c r="W54" s="5"/>
+      <c r="U54" s="7"/>
+      <c r="V54" s="7"/>
+      <c r="W54" s="7"/>
       <c r="Y54" s="7"/>
-      <c r="Z54" s="5"/>
-      <c r="AA54" s="5"/>
-      <c r="AB54" s="5"/>
+      <c r="Z54" s="14"/>
+      <c r="AA54" s="14"/>
+      <c r="AB54" s="14"/>
     </row>
     <row r="55" spans="21:28">
-      <c r="U55" s="7"/>
-      <c r="V55" s="7"/>
-      <c r="W55" s="7"/>
+      <c r="U55" s="5"/>
+      <c r="V55" s="5"/>
+      <c r="W55" s="5"/>
       <c r="Y55" s="7"/>
-      <c r="Z55" s="14"/>
-      <c r="AA55" s="14"/>
-      <c r="AB55" s="14"/>
+      <c r="Z55" s="5"/>
+      <c r="AA55" s="5"/>
+      <c r="AB55" s="5"/>
     </row>
     <row r="56" spans="21:28">
-      <c r="U56" s="5"/>
-      <c r="V56" s="5"/>
-      <c r="W56" s="5"/>
+      <c r="U56" s="7"/>
+      <c r="V56" s="7"/>
+      <c r="W56" s="7"/>
       <c r="Y56" s="7"/>
-      <c r="Z56" s="5"/>
-      <c r="AA56" s="5"/>
-      <c r="AB56" s="5"/>
+      <c r="Z56" s="14"/>
+      <c r="AA56" s="14"/>
+      <c r="AB56" s="14"/>
     </row>
     <row r="57" spans="21:28">
-      <c r="U57" s="7"/>
-      <c r="V57" s="7"/>
-      <c r="W57" s="7"/>
+      <c r="U57" s="5"/>
+      <c r="V57" s="5"/>
+      <c r="W57" s="5"/>
       <c r="Y57" s="7"/>
-      <c r="Z57" s="14"/>
-      <c r="AA57" s="14"/>
-      <c r="AB57" s="14"/>
+      <c r="Z57" s="5"/>
+      <c r="AA57" s="5"/>
+      <c r="AB57" s="5"/>
     </row>
     <row r="58" spans="21:28">
-      <c r="U58" s="5"/>
-      <c r="V58" s="5"/>
-      <c r="W58" s="5"/>
-      <c r="Y58" s="7"/>
-      <c r="Z58" s="5"/>
-      <c r="AA58" s="5"/>
-      <c r="AB58" s="5"/>
-    </row>
-    <row r="59" spans="21:28">
-      <c r="U59" s="7"/>
-      <c r="V59" s="7"/>
-      <c r="W59" s="7"/>
-      <c r="Y59" s="14"/>
-      <c r="Z59" s="14"/>
-      <c r="AA59" s="14"/>
-      <c r="AB59" s="14"/>
+      <c r="U58" s="7"/>
+      <c r="V58" s="7"/>
+      <c r="W58" s="7"/>
+      <c r="Y58" s="14"/>
+      <c r="Z58" s="14"/>
+      <c r="AA58" s="14"/>
+      <c r="AB58" s="14"/>
     </row>
   </sheetData>
   <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S60:S1048576" xr:uid="{F98435C8-1E0D-420B-93AD-1750A0AD1E4D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S59:S1048576" xr:uid="{F98435C8-1E0D-420B-93AD-1750A0AD1E4D}">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Insira uma data" error="O valor digitado deve ser uma data." promptTitle="Insira uma data" prompt="Use o formato dd/mm/aaaa" sqref="N60:N1048576" xr:uid="{E30AD5C4-327F-471C-A8FE-8847233F32A8}">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Insira uma data" error="O valor digitado deve ser uma data." promptTitle="Insira uma data" prompt="Use o formato dd/mm/aaaa" sqref="N59:N1048576" xr:uid="{E30AD5C4-327F-471C-A8FE-8847233F32A8}">
       <formula1>46023</formula1>
       <formula2>46387</formula2>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="O valor digitado deve ser uma data." promptTitle="Insira uma data " prompt="Use o formato dd/mm/aaaa" sqref="P60:P1048576" xr:uid="{C38150F2-07B9-4A40-94E9-2F60486C9785}">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="O valor digitado deve ser uma data." promptTitle="Insira uma data " prompt="Use o formato dd/mm/aaaa" sqref="P59:P1048576" xr:uid="{C38150F2-07B9-4A40-94E9-2F60486C9785}">
       <formula1>46023</formula1>
       <formula2>46387</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Sim ou Não" promptTitle="Sim ou Não" sqref="Q59:Q1048576 Y2:Y58 T2:T58 O2:O1048576" xr:uid="{A33B9050-2903-44EC-9C32-C551C6DD218F}">
+      <formula1>"Sim,Não"</formula1>
     </dataValidation>
     <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="O valor digitado deve ser uma data." promptTitle="Insira uma data" prompt="Use o formato dd/mm/aaaa" sqref="R38:R1048576" xr:uid="{B80591A4-C609-4DDF-A9CB-595A54330A1C}">
       <formula1>46023</formula1>
       <formula2>46387</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Sim ou Não" promptTitle="Sim ou Não" sqref="Q60:Q1048576 O2:O1048576 T2:T59 Y2:Y59" xr:uid="{A33B9050-2903-44EC-9C32-C551C6DD218F}">
-      <formula1>"Sim,Não"</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:R59" xr:uid="{66A39B3A-FA32-40B1-A327-70A015F2D105}"/>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Data inválida" error="Informe uma data entre 01/01/2026 e 31/12/2026." sqref="N2:N59 X2:X59 S2:S59" xr:uid="{7CAE3D66-F37A-4DC6-831F-B6867AFE899B}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:R58" xr:uid="{66A39B3A-FA32-40B1-A327-70A015F2D105}"/>
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Data inválida" error="Informe uma data entre 01/01/2026 e 31/12/2026." sqref="S2:S58 X2:X58 N2:N58" xr:uid="{7CAE3D66-F37A-4DC6-831F-B6867AFE899B}">
       <formula1>46023</formula1>
       <formula2>46387</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Sim ou Não" promptTitle="Sim ou Não" sqref="O2:O59" xr:uid="{DA1ED78E-091C-41E8-9E96-D1D63B85A012}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Sim ou Não" promptTitle="Sim ou Não" sqref="O2:O58" xr:uid="{DA1ED78E-091C-41E8-9E96-D1D63B85A012}">
       <formula1>"Sim;Não"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/base/base implantação.xlsx
+++ b/data/base/base implantação.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/warruda_mgcontecnica_com_br/Documents/Documentos/python/Portal-implantacao-tmp/data/base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="735" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3CBBAEDC-971A-409B-9991-BA5CE5A1DBF6}"/>
+  <xr:revisionPtr revIDLastSave="737" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C296476B-885B-43EB-9E8B-F413872266A5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="272">
   <si>
     <t>ID</t>
   </si>
@@ -835,6 +835,24 @@
   </si>
   <si>
     <t>FERNANDA DIAS DE MATOS;</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SUPERMERCADOS BANDEIRA LTDA.</t>
+  </si>
+  <si>
+    <t>SUPERMERCADO BANDEIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRAÇA DAS BANDEIRAS, Num.: 17 Comple.: 17 A, Bairro: CENTRO  / </t>
+  </si>
+  <si>
+    <t>joaofhayashi@gmail.com ;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(11) 99650-0565  / </t>
+  </si>
+  <si>
+    <t>JOÃO VITOR FURQUIM HAYASHI;GABRIEL FURQUIM HAYASHI;SUSUMU HAYASHI;</t>
   </si>
 </sst>
 </file>
@@ -902,7 +920,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -1063,12 +1081,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF44B3E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF44B3E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF44B3E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1109,6 +1140,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -4054,7 +4088,7 @@
       <c r="AA34" s="7"/>
       <c r="AB34" s="7"/>
     </row>
-    <row r="35" spans="1:28" ht="17.25" customHeight="1">
+    <row r="35" spans="1:28">
       <c r="A35" s="4">
         <v>6949</v>
       </c>
@@ -4543,6 +4577,45 @@
       <c r="AB42" s="14"/>
     </row>
     <row r="43" spans="1:28">
+      <c r="A43" s="38">
+        <v>6984</v>
+      </c>
+      <c r="B43" s="39" t="s">
+        <v>266</v>
+      </c>
+      <c r="C43" s="39">
+        <v>46235</v>
+      </c>
+      <c r="D43" s="39" t="s">
+        <v>267</v>
+      </c>
+      <c r="E43" s="39" t="s">
+        <v>228</v>
+      </c>
+      <c r="F43" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="G43" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="H43" s="39" t="s">
+        <v>111</v>
+      </c>
+      <c r="I43" s="39" t="s">
+        <v>268</v>
+      </c>
+      <c r="J43" s="39" t="s">
+        <v>269</v>
+      </c>
+      <c r="K43" s="39" t="s">
+        <v>270</v>
+      </c>
+      <c r="L43" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="M43" s="40" t="s">
+        <v>271</v>
+      </c>
       <c r="U43" s="5"/>
       <c r="V43" s="5"/>
       <c r="W43" s="5"/>

--- a/data/base/base implantação.xlsx
+++ b/data/base/base implantação.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/warruda_mgcontecnica_com_br/Documents/Documentos/python/Portal-implantacao-tmp/data/base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="741" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3CF0B2C7-DCE7-4E46-8E02-5E3317C41A3D}"/>
+  <xr:revisionPtr revIDLastSave="743" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F5648F2-1770-41F6-B70C-5335F4346921}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1285,7 +1285,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1320,13 +1320,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1337,7 +1334,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -3429,43 +3425,43 @@
       <c r="AB21" s="7"/>
     </row>
     <row r="22" spans="1:28">
-      <c r="A22" s="43">
+      <c r="A22" s="40">
         <v>6991</v>
       </c>
-      <c r="B22" s="48" t="s">
+      <c r="B22" s="45" t="s">
         <v>165</v>
       </c>
-      <c r="C22" s="48">
+      <c r="C22" s="45">
         <v>46235</v>
       </c>
-      <c r="D22" s="48" t="s">
+      <c r="D22" s="45" t="s">
         <v>158</v>
       </c>
-      <c r="E22" s="48" t="s">
+      <c r="E22" s="45" t="s">
         <v>159</v>
       </c>
-      <c r="F22" s="48" t="s">
+      <c r="F22" s="45" t="s">
         <v>160</v>
       </c>
-      <c r="G22" s="48" t="s">
+      <c r="G22" s="45" t="s">
         <v>66</v>
       </c>
-      <c r="H22" s="48" t="s">
+      <c r="H22" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="I22" s="48" t="s">
+      <c r="I22" s="45" t="s">
         <v>166</v>
       </c>
-      <c r="J22" s="48" t="s">
+      <c r="J22" s="45" t="s">
         <v>162</v>
       </c>
-      <c r="K22" s="48" t="s">
+      <c r="K22" s="45" t="s">
         <v>163</v>
       </c>
-      <c r="L22" s="48" t="s">
+      <c r="L22" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="M22" s="48" t="s">
+      <c r="M22" s="45" t="s">
         <v>167</v>
       </c>
       <c r="N22" s="22"/>
@@ -3588,7 +3584,7 @@
       <c r="M24" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="N24" s="51"/>
+      <c r="N24" s="47"/>
       <c r="O24" s="5" t="s">
         <v>38</v>
       </c>
@@ -3652,7 +3648,7 @@
       <c r="M25" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="N25" s="52">
+      <c r="N25" s="48">
         <v>46252</v>
       </c>
       <c r="O25" s="7" t="s">
@@ -3720,7 +3716,7 @@
       <c r="M26" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="N26" s="51"/>
+      <c r="N26" s="47"/>
       <c r="O26" s="5" t="s">
         <v>38</v>
       </c>
@@ -3844,7 +3840,7 @@
       <c r="M28" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="N28" s="53">
+      <c r="N28" s="49">
         <v>46269</v>
       </c>
       <c r="O28" s="5" t="s">
@@ -3908,7 +3904,7 @@
       <c r="M29" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="N29" s="52">
+      <c r="N29" s="48">
         <v>46255</v>
       </c>
       <c r="O29" s="7" t="s">
@@ -3974,7 +3970,7 @@
       <c r="M30" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="N30" s="52">
+      <c r="N30" s="48">
         <v>46255</v>
       </c>
       <c r="O30" s="5" t="s">
@@ -4397,7 +4393,7 @@
       <c r="AB36" s="5"/>
     </row>
     <row r="37" spans="1:28">
-      <c r="A37" s="42">
+      <c r="A37" s="39">
         <v>7020</v>
       </c>
       <c r="B37" s="14" t="s">
@@ -4436,7 +4432,7 @@
       <c r="M37" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="N37" s="55">
+      <c r="N37" s="51">
         <v>46255</v>
       </c>
       <c r="O37" s="14" t="s">
@@ -4445,7 +4441,7 @@
       <c r="P37" s="7"/>
       <c r="Q37" s="7"/>
       <c r="R37" s="29"/>
-      <c r="S37" s="57">
+      <c r="S37" s="53">
         <v>46255</v>
       </c>
       <c r="T37" s="14" t="s">
@@ -4463,130 +4459,130 @@
       <c r="AB37" s="14"/>
     </row>
     <row r="38" spans="1:28">
-      <c r="A38" s="45">
+      <c r="A38" s="42">
         <v>7021</v>
       </c>
-      <c r="B38" s="45" t="s">
+      <c r="B38" s="42" t="s">
         <v>237</v>
       </c>
-      <c r="C38" s="45">
+      <c r="C38" s="42">
         <v>46235</v>
       </c>
-      <c r="D38" s="45" t="s">
+      <c r="D38" s="42" t="s">
         <v>205</v>
       </c>
-      <c r="E38" s="45" t="s">
+      <c r="E38" s="42" t="s">
         <v>226</v>
       </c>
-      <c r="F38" s="45" t="s">
+      <c r="F38" s="42" t="s">
         <v>227</v>
       </c>
-      <c r="G38" s="45" t="s">
+      <c r="G38" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="H38" s="45" t="s">
+      <c r="H38" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="I38" s="45" t="s">
+      <c r="I38" s="42" t="s">
         <v>228</v>
       </c>
-      <c r="J38" s="45" t="s">
+      <c r="J38" s="42" t="s">
         <v>217</v>
       </c>
-      <c r="K38" s="45" t="s">
+      <c r="K38" s="42" t="s">
         <v>229</v>
       </c>
-      <c r="L38" s="45" t="s">
+      <c r="L38" s="42" t="s">
         <v>219</v>
       </c>
-      <c r="M38" s="51" t="s">
+      <c r="M38" s="47" t="s">
         <v>236</v>
       </c>
-      <c r="N38" s="55">
+      <c r="N38" s="51">
         <v>46255</v>
       </c>
-      <c r="O38" s="51" t="s">
+      <c r="O38" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="P38" s="51"/>
-      <c r="Q38" s="51"/>
-      <c r="R38" s="51"/>
-      <c r="S38" s="57">
+      <c r="P38" s="47"/>
+      <c r="Q38" s="47"/>
+      <c r="R38" s="47"/>
+      <c r="S38" s="53">
         <v>46255</v>
       </c>
-      <c r="T38" s="51" t="s">
+      <c r="T38" s="47" t="s">
         <v>50</v>
       </c>
       <c r="U38" s="5"/>
       <c r="V38" s="5"/>
       <c r="W38" s="5"/>
-      <c r="X38" s="51"/>
+      <c r="X38" s="47"/>
       <c r="Y38" s="5" t="s">
         <v>38</v>
       </c>
       <c r="Z38" s="20"/>
-      <c r="AA38" s="51"/>
+      <c r="AA38" s="47"/>
       <c r="AB38" s="5"/>
     </row>
     <row r="39" spans="1:28">
-      <c r="A39" s="41">
+      <c r="A39" s="38">
         <v>7036</v>
       </c>
-      <c r="B39" s="47" t="s">
+      <c r="B39" s="44" t="s">
         <v>238</v>
       </c>
-      <c r="C39" s="47">
+      <c r="C39" s="44">
         <v>46266</v>
       </c>
-      <c r="D39" s="47" t="s">
+      <c r="D39" s="44" t="s">
         <v>239</v>
       </c>
-      <c r="E39" s="47" t="s">
+      <c r="E39" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="F39" s="47" t="s">
+      <c r="F39" s="44" t="s">
         <v>143</v>
       </c>
-      <c r="G39" s="47" t="s">
+      <c r="G39" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="H39" s="47" t="s">
+      <c r="H39" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="I39" s="47" t="s">
+      <c r="I39" s="44" t="s">
         <v>240</v>
       </c>
-      <c r="J39" s="47" t="s">
+      <c r="J39" s="44" t="s">
         <v>241</v>
       </c>
-      <c r="K39" s="47" t="s">
+      <c r="K39" s="44" t="s">
         <v>242</v>
       </c>
-      <c r="L39" s="47" t="s">
+      <c r="L39" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="M39" s="47" t="s">
+      <c r="M39" s="44" t="s">
         <v>243</v>
       </c>
-      <c r="N39" s="53">
+      <c r="N39" s="49">
         <v>46261</v>
       </c>
-      <c r="O39" s="51" t="s">
+      <c r="O39" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="P39" s="51" t="s">
+      <c r="P39" s="47" t="s">
         <v>244</v>
       </c>
-      <c r="Q39" s="51" t="s">
+      <c r="Q39" s="47" t="s">
         <v>245</v>
       </c>
       <c r="R39" s="24" t="s">
         <v>246</v>
       </c>
-      <c r="S39" s="53">
+      <c r="S39" s="49">
         <v>46261</v>
       </c>
-      <c r="T39" s="51" t="s">
+      <c r="T39" s="47" t="s">
         <v>50</v>
       </c>
       <c r="U39" s="5" t="s">
@@ -4596,7 +4592,7 @@
         <v>248</v>
       </c>
       <c r="W39" s="5"/>
-      <c r="X39" s="51"/>
+      <c r="X39" s="47"/>
       <c r="Y39" s="5" t="s">
         <v>38</v>
       </c>
@@ -4609,7 +4605,7 @@
       <c r="AB39" s="20"/>
     </row>
     <row r="40" spans="1:28">
-      <c r="A40" s="44">
+      <c r="A40" s="41">
         <v>7037</v>
       </c>
       <c r="B40" s="28" t="s">
@@ -4648,7 +4644,7 @@
       <c r="M40" s="28" t="s">
         <v>253</v>
       </c>
-      <c r="N40" s="53">
+      <c r="N40" s="49">
         <v>46261</v>
       </c>
       <c r="O40" s="21" t="s">
@@ -4663,7 +4659,7 @@
       <c r="R40" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="S40" s="53">
+      <c r="S40" s="49">
         <v>46261</v>
       </c>
       <c r="T40" s="21" t="s">
@@ -4683,7 +4679,7 @@
       <c r="Z40" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="AA40" s="58" t="s">
+      <c r="AA40" s="54" t="s">
         <v>250</v>
       </c>
       <c r="AB40" s="7"/>
@@ -4728,25 +4724,25 @@
       <c r="M41" s="28" t="s">
         <v>259</v>
       </c>
-      <c r="N41" s="54">
+      <c r="N41" s="50">
         <v>46267</v>
       </c>
-      <c r="O41" s="56" t="s">
+      <c r="O41" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="P41" s="54"/>
-      <c r="Q41" s="56"/>
-      <c r="R41" s="54"/>
-      <c r="S41" s="54">
+      <c r="P41" s="50"/>
+      <c r="Q41" s="52"/>
+      <c r="R41" s="50"/>
+      <c r="S41" s="50">
         <v>46267</v>
       </c>
-      <c r="T41" s="56" t="s">
+      <c r="T41" s="52" t="s">
         <v>38</v>
       </c>
       <c r="U41" s="5"/>
       <c r="V41" s="5"/>
       <c r="W41" s="5"/>
-      <c r="X41" s="54">
+      <c r="X41" s="50">
         <v>46266</v>
       </c>
       <c r="Y41" s="7" t="s">
@@ -4763,7 +4759,7 @@
       <c r="B42" s="28" t="s">
         <v>260</v>
       </c>
-      <c r="C42" s="28">
+      <c r="C42" s="5">
         <v>46266</v>
       </c>
       <c r="D42" s="28" t="s">
@@ -4811,7 +4807,7 @@
       <c r="B43" s="31" t="s">
         <v>260</v>
       </c>
-      <c r="C43" s="32">
+      <c r="C43" s="5">
         <v>46266</v>
       </c>
       <c r="D43" s="31" t="s">
@@ -4841,7 +4837,7 @@
       <c r="L43" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="M43" s="50" t="s">
+      <c r="M43" s="46" t="s">
         <v>265</v>
       </c>
       <c r="U43" s="7"/>
@@ -4853,43 +4849,43 @@
       <c r="AB43" s="7"/>
     </row>
     <row r="44" spans="1:28">
-      <c r="A44" s="40">
+      <c r="A44" s="37">
         <v>7049</v>
       </c>
-      <c r="B44" s="46" t="s">
+      <c r="B44" s="43" t="s">
         <v>266</v>
       </c>
-      <c r="C44" s="49">
+      <c r="C44" s="5">
         <v>46266</v>
       </c>
-      <c r="D44" s="46" t="s">
+      <c r="D44" s="43" t="s">
         <v>261</v>
       </c>
-      <c r="E44" s="46" t="s">
+      <c r="E44" s="43" t="s">
         <v>170</v>
       </c>
-      <c r="F44" s="46" t="s">
+      <c r="F44" s="43" t="s">
         <v>267</v>
       </c>
-      <c r="G44" s="46" t="s">
+      <c r="G44" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="H44" s="46" t="s">
+      <c r="H44" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="I44" s="46" t="s">
+      <c r="I44" s="43" t="s">
         <v>268</v>
       </c>
-      <c r="J44" s="46" t="s">
+      <c r="J44" s="43" t="s">
         <v>269</v>
       </c>
-      <c r="K44" s="46" t="s">
+      <c r="K44" s="43" t="s">
         <v>270</v>
       </c>
-      <c r="L44" s="46" t="s">
+      <c r="L44" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="M44" s="46" t="s">
+      <c r="M44" s="43" t="s">
         <v>271</v>
       </c>
       <c r="U44" s="5"/>
@@ -4907,7 +4903,7 @@
       <c r="B45" s="28" t="s">
         <v>272</v>
       </c>
-      <c r="C45" s="28">
+      <c r="C45" s="5">
         <v>46266</v>
       </c>
       <c r="D45" s="28" t="s">
@@ -4949,43 +4945,43 @@
       <c r="AB45" s="5"/>
     </row>
     <row r="46" spans="1:28">
-      <c r="A46" s="36">
+      <c r="A46" s="34">
         <v>7050</v>
       </c>
-      <c r="B46" s="37" t="s">
+      <c r="B46" s="35" t="s">
         <v>272</v>
       </c>
-      <c r="C46" s="38">
+      <c r="C46" s="5">
         <v>46266</v>
       </c>
-      <c r="D46" s="37" t="s">
+      <c r="D46" s="35" t="s">
         <v>273</v>
       </c>
-      <c r="E46" s="37" t="s">
+      <c r="E46" s="35" t="s">
         <v>170</v>
       </c>
-      <c r="F46" s="37" t="s">
+      <c r="F46" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="G46" s="37" t="s">
+      <c r="G46" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="H46" s="37" t="s">
+      <c r="H46" s="35" t="s">
         <v>74</v>
       </c>
-      <c r="I46" s="37" t="s">
+      <c r="I46" s="35" t="s">
         <v>274</v>
       </c>
-      <c r="J46" s="37" t="s">
+      <c r="J46" s="35" t="s">
         <v>275</v>
       </c>
-      <c r="K46" s="37" t="s">
+      <c r="K46" s="35" t="s">
         <v>276</v>
       </c>
-      <c r="L46" s="37" t="s">
+      <c r="L46" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M46" s="37" t="s">
+      <c r="M46" s="35" t="s">
         <v>277</v>
       </c>
       <c r="U46" s="5"/>
@@ -4997,43 +4993,43 @@
       <c r="AB46" s="20"/>
     </row>
     <row r="47" spans="1:28">
-      <c r="A47" s="36">
+      <c r="A47" s="34">
         <v>7052</v>
       </c>
-      <c r="B47" s="37" t="s">
+      <c r="B47" s="35" t="s">
         <v>278</v>
       </c>
-      <c r="C47" s="38">
+      <c r="C47" s="5">
         <v>46266</v>
       </c>
-      <c r="D47" s="37" t="s">
+      <c r="D47" s="35" t="s">
         <v>279</v>
       </c>
-      <c r="E47" s="37" t="s">
+      <c r="E47" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="F47" s="37" t="s">
+      <c r="F47" s="35" t="s">
         <v>267</v>
       </c>
-      <c r="G47" s="37" t="s">
+      <c r="G47" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="H47" s="37" t="s">
+      <c r="H47" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="I47" s="37" t="s">
+      <c r="I47" s="35" t="s">
         <v>280</v>
       </c>
-      <c r="J47" s="37" t="s">
+      <c r="J47" s="35" t="s">
         <v>281</v>
       </c>
-      <c r="K47" s="37" t="s">
+      <c r="K47" s="35" t="s">
         <v>282</v>
       </c>
-      <c r="L47" s="37" t="s">
+      <c r="L47" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M47" s="37" t="s">
+      <c r="M47" s="35" t="s">
         <v>283</v>
       </c>
       <c r="U47" s="5"/>
@@ -5045,43 +5041,43 @@
       <c r="AB47" s="5"/>
     </row>
     <row r="48" spans="1:28">
-      <c r="A48" s="33">
+      <c r="A48" s="32">
         <v>7053</v>
       </c>
-      <c r="B48" s="34" t="s">
+      <c r="B48" s="33" t="s">
         <v>284</v>
       </c>
-      <c r="C48" s="35">
+      <c r="C48" s="5">
         <v>46266</v>
       </c>
-      <c r="D48" s="34" t="s">
+      <c r="D48" s="33" t="s">
         <v>279</v>
       </c>
-      <c r="E48" s="34" t="s">
+      <c r="E48" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="F48" s="34" t="s">
+      <c r="F48" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="G48" s="34" t="s">
+      <c r="G48" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="H48" s="34" t="s">
+      <c r="H48" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="I48" s="34" t="s">
+      <c r="I48" s="33" t="s">
         <v>285</v>
       </c>
-      <c r="J48" s="34" t="s">
+      <c r="J48" s="33" t="s">
         <v>286</v>
       </c>
-      <c r="K48" s="34" t="s">
+      <c r="K48" s="33" t="s">
         <v>282</v>
       </c>
-      <c r="L48" s="34" t="s">
+      <c r="L48" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="M48" s="34" t="s">
+      <c r="M48" s="33" t="s">
         <v>287</v>
       </c>
       <c r="U48" s="7"/>
@@ -5093,43 +5089,43 @@
       <c r="AB48" s="14"/>
     </row>
     <row r="49" spans="1:28">
-      <c r="A49" s="36">
+      <c r="A49" s="34">
         <v>7054</v>
       </c>
-      <c r="B49" s="37" t="s">
+      <c r="B49" s="35" t="s">
         <v>288</v>
       </c>
-      <c r="C49" s="38">
+      <c r="C49" s="5">
         <v>46266</v>
       </c>
-      <c r="D49" s="37" t="s">
+      <c r="D49" s="35" t="s">
         <v>279</v>
       </c>
-      <c r="E49" s="37" t="s">
+      <c r="E49" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="F49" s="37" t="s">
+      <c r="F49" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="G49" s="37" t="s">
+      <c r="G49" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="H49" s="37" t="s">
+      <c r="H49" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="I49" s="37" t="s">
+      <c r="I49" s="35" t="s">
         <v>289</v>
       </c>
-      <c r="J49" s="37" t="s">
+      <c r="J49" s="35" t="s">
         <v>290</v>
       </c>
-      <c r="K49" s="37" t="s">
+      <c r="K49" s="35" t="s">
         <v>291</v>
       </c>
-      <c r="L49" s="37" t="s">
+      <c r="L49" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M49" s="37" t="s">
+      <c r="M49" s="35" t="s">
         <v>292</v>
       </c>
       <c r="U49" s="5"/>
@@ -5141,43 +5137,43 @@
       <c r="AB49" s="5"/>
     </row>
     <row r="50" spans="1:28">
-      <c r="A50" s="33">
+      <c r="A50" s="32">
         <v>7055</v>
       </c>
-      <c r="B50" s="34" t="s">
+      <c r="B50" s="33" t="s">
         <v>293</v>
       </c>
-      <c r="C50" s="35">
+      <c r="C50" s="5">
         <v>46266</v>
       </c>
-      <c r="D50" s="34" t="s">
+      <c r="D50" s="33" t="s">
         <v>279</v>
       </c>
-      <c r="E50" s="34" t="s">
+      <c r="E50" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="F50" s="34" t="s">
+      <c r="F50" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="G50" s="34" t="s">
+      <c r="G50" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="H50" s="34" t="s">
+      <c r="H50" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="I50" s="34" t="s">
+      <c r="I50" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="J50" s="34" t="s">
+      <c r="J50" s="33" t="s">
         <v>295</v>
       </c>
-      <c r="K50" s="34" t="s">
+      <c r="K50" s="33" t="s">
         <v>296</v>
       </c>
-      <c r="L50" s="34" t="s">
+      <c r="L50" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="M50" s="34" t="s">
+      <c r="M50" s="33" t="s">
         <v>297</v>
       </c>
       <c r="U50" s="7"/>
@@ -5189,91 +5185,91 @@
       <c r="AB50" s="14"/>
     </row>
     <row r="51" spans="1:28">
-      <c r="A51" s="36">
+      <c r="A51" s="34">
         <v>7056</v>
       </c>
-      <c r="B51" s="37" t="s">
+      <c r="B51" s="35" t="s">
         <v>298</v>
       </c>
-      <c r="C51" s="38">
+      <c r="C51" s="5">
         <v>46266</v>
       </c>
-      <c r="D51" s="37" t="s">
+      <c r="D51" s="35" t="s">
         <v>279</v>
       </c>
-      <c r="E51" s="37" t="s">
+      <c r="E51" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="F51" s="37" t="s">
+      <c r="F51" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="G51" s="37" t="s">
+      <c r="G51" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="H51" s="37" t="s">
+      <c r="H51" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="I51" s="37" t="s">
+      <c r="I51" s="35" t="s">
         <v>289</v>
       </c>
-      <c r="J51" s="37" t="s">
+      <c r="J51" s="35" t="s">
         <v>299</v>
       </c>
-      <c r="K51" s="37" t="s">
+      <c r="K51" s="35" t="s">
         <v>296</v>
       </c>
-      <c r="L51" s="37" t="s">
+      <c r="L51" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M51" s="37" t="s">
+      <c r="M51" s="35" t="s">
         <v>300</v>
       </c>
-      <c r="U51" s="39"/>
-      <c r="V51" s="39"/>
-      <c r="W51" s="39"/>
-      <c r="Y51" s="39"/>
-      <c r="Z51" s="39"/>
-      <c r="AA51" s="39"/>
-      <c r="AB51" s="39"/>
+      <c r="U51" s="36"/>
+      <c r="V51" s="36"/>
+      <c r="W51" s="36"/>
+      <c r="Y51" s="36"/>
+      <c r="Z51" s="36"/>
+      <c r="AA51" s="36"/>
+      <c r="AB51" s="36"/>
     </row>
     <row r="52" spans="1:28">
-      <c r="A52" s="36">
+      <c r="A52" s="34">
         <v>7057</v>
       </c>
-      <c r="B52" s="37" t="s">
+      <c r="B52" s="35" t="s">
         <v>301</v>
       </c>
-      <c r="C52" s="38">
+      <c r="C52" s="5">
         <v>46266</v>
       </c>
-      <c r="D52" s="37" t="s">
+      <c r="D52" s="35" t="s">
         <v>302</v>
       </c>
-      <c r="E52" s="37" t="s">
+      <c r="E52" s="35" t="s">
         <v>303</v>
       </c>
-      <c r="F52" s="37" t="s">
+      <c r="F52" s="35" t="s">
         <v>304</v>
       </c>
-      <c r="G52" s="37" t="s">
+      <c r="G52" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="H52" s="37" t="s">
+      <c r="H52" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="I52" s="37" t="s">
+      <c r="I52" s="35" t="s">
         <v>305</v>
       </c>
-      <c r="J52" s="37" t="s">
+      <c r="J52" s="35" t="s">
         <v>306</v>
       </c>
-      <c r="K52" s="37" t="s">
+      <c r="K52" s="35" t="s">
         <v>307</v>
       </c>
-      <c r="L52" s="37" t="s">
+      <c r="L52" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M52" s="37" t="s">
+      <c r="M52" s="35" t="s">
         <v>308</v>
       </c>
       <c r="U52" s="7"/>
@@ -5285,43 +5281,43 @@
       <c r="AB52" s="14"/>
     </row>
     <row r="53" spans="1:28">
-      <c r="A53" s="33">
+      <c r="A53" s="32">
         <v>7058</v>
       </c>
-      <c r="B53" s="34" t="s">
+      <c r="B53" s="33" t="s">
         <v>309</v>
       </c>
-      <c r="C53" s="35">
+      <c r="C53" s="5">
         <v>46266</v>
       </c>
-      <c r="D53" s="34" t="s">
+      <c r="D53" s="33" t="s">
         <v>302</v>
       </c>
-      <c r="E53" s="34" t="s">
+      <c r="E53" s="33" t="s">
         <v>303</v>
       </c>
-      <c r="F53" s="34" t="s">
+      <c r="F53" s="33" t="s">
         <v>304</v>
       </c>
-      <c r="G53" s="34" t="s">
+      <c r="G53" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="H53" s="34" t="s">
+      <c r="H53" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="I53" s="34" t="s">
+      <c r="I53" s="33" t="s">
         <v>310</v>
       </c>
-      <c r="J53" s="34" t="s">
+      <c r="J53" s="33" t="s">
         <v>306</v>
       </c>
-      <c r="K53" s="34" t="s">
+      <c r="K53" s="33" t="s">
         <v>307</v>
       </c>
-      <c r="L53" s="34" t="s">
+      <c r="L53" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="M53" s="34" t="s">
+      <c r="M53" s="33" t="s">
         <v>311</v>
       </c>
       <c r="U53" s="5"/>
@@ -5333,43 +5329,43 @@
       <c r="AB53" s="5"/>
     </row>
     <row r="54" spans="1:28">
-      <c r="A54" s="36">
+      <c r="A54" s="34">
         <v>7059</v>
       </c>
-      <c r="B54" s="37" t="s">
+      <c r="B54" s="35" t="s">
         <v>312</v>
       </c>
-      <c r="C54" s="38">
+      <c r="C54" s="5">
         <v>46266</v>
       </c>
-      <c r="D54" s="37" t="s">
+      <c r="D54" s="35" t="s">
         <v>302</v>
       </c>
-      <c r="E54" s="37" t="s">
+      <c r="E54" s="35" t="s">
         <v>303</v>
       </c>
-      <c r="F54" s="37" t="s">
+      <c r="F54" s="35" t="s">
         <v>304</v>
       </c>
-      <c r="G54" s="37" t="s">
+      <c r="G54" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="H54" s="37" t="s">
+      <c r="H54" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="I54" s="37" t="s">
+      <c r="I54" s="35" t="s">
         <v>313</v>
       </c>
-      <c r="J54" s="37" t="s">
+      <c r="J54" s="35" t="s">
         <v>306</v>
       </c>
-      <c r="K54" s="37" t="s">
+      <c r="K54" s="35" t="s">
         <v>307</v>
       </c>
-      <c r="L54" s="37" t="s">
+      <c r="L54" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M54" s="37" t="s">
+      <c r="M54" s="35" t="s">
         <v>311</v>
       </c>
       <c r="U54" s="7"/>
@@ -5381,43 +5377,43 @@
       <c r="AB54" s="14"/>
     </row>
     <row r="55" spans="1:28">
-      <c r="A55" s="33">
+      <c r="A55" s="32">
         <v>7060</v>
       </c>
-      <c r="B55" s="34" t="s">
+      <c r="B55" s="33" t="s">
         <v>314</v>
       </c>
-      <c r="C55" s="35">
+      <c r="C55" s="5">
         <v>46266</v>
       </c>
-      <c r="D55" s="34" t="s">
+      <c r="D55" s="33" t="s">
         <v>302</v>
       </c>
-      <c r="E55" s="34" t="s">
+      <c r="E55" s="33" t="s">
         <v>303</v>
       </c>
-      <c r="F55" s="34" t="s">
+      <c r="F55" s="33" t="s">
         <v>304</v>
       </c>
-      <c r="G55" s="34" t="s">
+      <c r="G55" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="H55" s="34" t="s">
+      <c r="H55" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="I55" s="34" t="s">
+      <c r="I55" s="33" t="s">
         <v>315</v>
       </c>
-      <c r="J55" s="34" t="s">
+      <c r="J55" s="33" t="s">
         <v>316</v>
       </c>
-      <c r="K55" s="34" t="s">
+      <c r="K55" s="33" t="s">
         <v>317</v>
       </c>
-      <c r="L55" s="34" t="s">
+      <c r="L55" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="M55" s="34" t="s">
+      <c r="M55" s="33" t="s">
         <v>318</v>
       </c>
       <c r="U55" s="5"/>
@@ -5429,43 +5425,43 @@
       <c r="AB55" s="5"/>
     </row>
     <row r="56" spans="1:28">
-      <c r="A56" s="36">
+      <c r="A56" s="34">
         <v>7061</v>
       </c>
-      <c r="B56" s="37" t="s">
+      <c r="B56" s="35" t="s">
         <v>319</v>
       </c>
-      <c r="C56" s="38">
+      <c r="C56" s="5">
         <v>46266</v>
       </c>
-      <c r="D56" s="37" t="s">
+      <c r="D56" s="35" t="s">
         <v>302</v>
       </c>
-      <c r="E56" s="37" t="s">
+      <c r="E56" s="35" t="s">
         <v>303</v>
       </c>
-      <c r="F56" s="37" t="s">
+      <c r="F56" s="35" t="s">
         <v>304</v>
       </c>
-      <c r="G56" s="37" t="s">
+      <c r="G56" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="H56" s="37" t="s">
+      <c r="H56" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="I56" s="37" t="s">
+      <c r="I56" s="35" t="s">
         <v>320</v>
       </c>
-      <c r="J56" s="37" t="s">
+      <c r="J56" s="35" t="s">
         <v>316</v>
       </c>
-      <c r="K56" s="37" t="s">
+      <c r="K56" s="35" t="s">
         <v>317</v>
       </c>
-      <c r="L56" s="37" t="s">
+      <c r="L56" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M56" s="37" t="s">
+      <c r="M56" s="35" t="s">
         <v>318</v>
       </c>
       <c r="U56" s="7"/>
@@ -5477,43 +5473,43 @@
       <c r="AB56" s="14"/>
     </row>
     <row r="57" spans="1:28">
-      <c r="A57" s="33">
+      <c r="A57" s="32">
         <v>7062</v>
       </c>
-      <c r="B57" s="34" t="s">
+      <c r="B57" s="33" t="s">
         <v>321</v>
       </c>
-      <c r="C57" s="35">
+      <c r="C57" s="5">
         <v>46266</v>
       </c>
-      <c r="D57" s="34" t="s">
+      <c r="D57" s="33" t="s">
         <v>302</v>
       </c>
-      <c r="E57" s="34" t="s">
+      <c r="E57" s="33" t="s">
         <v>303</v>
       </c>
-      <c r="F57" s="34" t="s">
+      <c r="F57" s="33" t="s">
         <v>304</v>
       </c>
-      <c r="G57" s="34" t="s">
+      <c r="G57" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="H57" s="34" t="s">
+      <c r="H57" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="I57" s="34" t="s">
+      <c r="I57" s="33" t="s">
         <v>322</v>
       </c>
-      <c r="J57" s="34" t="s">
+      <c r="J57" s="33" t="s">
         <v>306</v>
       </c>
-      <c r="K57" s="34" t="s">
+      <c r="K57" s="33" t="s">
         <v>323</v>
       </c>
-      <c r="L57" s="34" t="s">
+      <c r="L57" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="M57" s="34" t="s">
+      <c r="M57" s="33" t="s">
         <v>324</v>
       </c>
       <c r="U57" s="5"/>
@@ -5525,43 +5521,43 @@
       <c r="AB57" s="5"/>
     </row>
     <row r="58" spans="1:28">
-      <c r="A58" s="36">
+      <c r="A58" s="34">
         <v>7063</v>
       </c>
-      <c r="B58" s="37" t="s">
+      <c r="B58" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="C58" s="38">
+      <c r="C58" s="5">
         <v>46266</v>
       </c>
-      <c r="D58" s="37" t="s">
+      <c r="D58" s="35" t="s">
         <v>302</v>
       </c>
-      <c r="E58" s="37" t="s">
+      <c r="E58" s="35" t="s">
         <v>303</v>
       </c>
-      <c r="F58" s="37" t="s">
+      <c r="F58" s="35" t="s">
         <v>304</v>
       </c>
-      <c r="G58" s="37" t="s">
+      <c r="G58" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="H58" s="37" t="s">
+      <c r="H58" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="I58" s="37" t="s">
+      <c r="I58" s="35" t="s">
         <v>326</v>
       </c>
-      <c r="J58" s="37" t="s">
+      <c r="J58" s="35" t="s">
         <v>306</v>
       </c>
-      <c r="K58" s="37" t="s">
+      <c r="K58" s="35" t="s">
         <v>323</v>
       </c>
-      <c r="L58" s="37" t="s">
+      <c r="L58" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M58" s="37" t="s">
+      <c r="M58" s="35" t="s">
         <v>327</v>
       </c>
       <c r="U58" s="7"/>
@@ -5573,43 +5569,43 @@
       <c r="AB58" s="14"/>
     </row>
     <row r="59" spans="1:28">
-      <c r="A59" s="36">
+      <c r="A59" s="34">
         <v>7064</v>
       </c>
-      <c r="B59" s="37" t="s">
+      <c r="B59" s="35" t="s">
         <v>328</v>
       </c>
-      <c r="C59" s="38">
+      <c r="C59" s="5">
         <v>46266</v>
       </c>
-      <c r="D59" s="37" t="s">
+      <c r="D59" s="35" t="s">
         <v>329</v>
       </c>
-      <c r="E59" s="37" t="s">
+      <c r="E59" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="F59" s="37" t="s">
+      <c r="F59" s="35" t="s">
         <v>267</v>
       </c>
-      <c r="G59" s="37" t="s">
+      <c r="G59" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="H59" s="37" t="s">
+      <c r="H59" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="I59" s="37" t="s">
+      <c r="I59" s="35" t="s">
         <v>330</v>
       </c>
-      <c r="J59" s="37" t="s">
+      <c r="J59" s="35" t="s">
         <v>331</v>
       </c>
-      <c r="K59" s="37" t="s">
+      <c r="K59" s="35" t="s">
         <v>332</v>
       </c>
-      <c r="L59" s="37" t="s">
+      <c r="L59" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="M59" s="37" t="s">
+      <c r="M59" s="35" t="s">
         <v>333</v>
       </c>
       <c r="U59" s="7"/>

--- a/data/base/base implantação.xlsx
+++ b/data/base/base implantação.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/warruda_mgcontecnica_com_br/Documents/Documentos/python/Portal-implantacao-tmp/data/base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="743" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F5648F2-1770-41F6-B70C-5335F4346921}"/>
+  <xr:revisionPtr revIDLastSave="751" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A91D41A5-B774-42DC-BC36-7BD10E10A39A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="334">
   <si>
     <t>ID</t>
   </si>
@@ -4792,54 +4792,37 @@
       <c r="M42" s="28" t="s">
         <v>265</v>
       </c>
+      <c r="O42" t="s">
+        <v>38</v>
+      </c>
+      <c r="T42" s="52" t="s">
+        <v>38</v>
+      </c>
       <c r="U42" s="7"/>
       <c r="V42" s="7"/>
       <c r="W42" s="7"/>
-      <c r="Y42" s="7"/>
+      <c r="Y42" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="Z42" s="14"/>
       <c r="AA42" s="14"/>
       <c r="AB42" s="14"/>
     </row>
     <row r="43" spans="1:28">
-      <c r="A43" s="30">
-        <v>7048</v>
-      </c>
-      <c r="B43" s="31" t="s">
-        <v>260</v>
-      </c>
-      <c r="C43" s="5">
-        <v>46266</v>
-      </c>
-      <c r="D43" s="31" t="s">
-        <v>261</v>
-      </c>
-      <c r="E43" s="31" t="s">
-        <v>170</v>
-      </c>
-      <c r="F43" s="31" t="s">
-        <v>65</v>
-      </c>
-      <c r="G43" s="31" t="s">
-        <v>66</v>
-      </c>
-      <c r="H43" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="I43" s="31" t="s">
-        <v>262</v>
-      </c>
-      <c r="J43" s="31" t="s">
-        <v>263</v>
-      </c>
-      <c r="K43" s="31" t="s">
-        <v>264</v>
-      </c>
-      <c r="L43" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="M43" s="46" t="s">
-        <v>265</v>
-      </c>
+      <c r="A43" s="30"/>
+      <c r="B43" s="31"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="31"/>
+      <c r="E43" s="31"/>
+      <c r="F43" s="31"/>
+      <c r="G43" s="31"/>
+      <c r="H43" s="31"/>
+      <c r="I43" s="31"/>
+      <c r="J43" s="31"/>
+      <c r="K43" s="31"/>
+      <c r="L43" s="31"/>
+      <c r="M43" s="46"/>
+      <c r="T43" s="52"/>
       <c r="U43" s="7"/>
       <c r="V43" s="7"/>
       <c r="W43" s="7"/>
@@ -4888,10 +4871,18 @@
       <c r="M44" s="43" t="s">
         <v>271</v>
       </c>
+      <c r="O44" t="s">
+        <v>38</v>
+      </c>
+      <c r="T44" s="52" t="s">
+        <v>38</v>
+      </c>
       <c r="U44" s="5"/>
       <c r="V44" s="5"/>
       <c r="W44" s="5"/>
-      <c r="Y44" s="7"/>
+      <c r="Y44" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="Z44" s="20"/>
       <c r="AA44" s="20"/>
       <c r="AB44" s="20"/>
@@ -4936,54 +4927,37 @@
       <c r="M45" s="28" t="s">
         <v>277</v>
       </c>
+      <c r="O45" t="s">
+        <v>38</v>
+      </c>
+      <c r="T45" s="52" t="s">
+        <v>38</v>
+      </c>
       <c r="U45" s="5"/>
       <c r="V45" s="5"/>
       <c r="W45" s="5"/>
-      <c r="Y45" s="7"/>
+      <c r="Y45" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="Z45" s="5"/>
       <c r="AA45" s="5"/>
       <c r="AB45" s="5"/>
     </row>
     <row r="46" spans="1:28">
-      <c r="A46" s="34">
-        <v>7050</v>
-      </c>
-      <c r="B46" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C46" s="5">
-        <v>46266</v>
-      </c>
-      <c r="D46" s="35" t="s">
-        <v>273</v>
-      </c>
-      <c r="E46" s="35" t="s">
-        <v>170</v>
-      </c>
-      <c r="F46" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="G46" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="H46" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="I46" s="35" t="s">
-        <v>274</v>
-      </c>
-      <c r="J46" s="35" t="s">
-        <v>275</v>
-      </c>
-      <c r="K46" s="35" t="s">
-        <v>276</v>
-      </c>
-      <c r="L46" s="35" t="s">
-        <v>36</v>
-      </c>
-      <c r="M46" s="35" t="s">
-        <v>277</v>
-      </c>
+      <c r="A46" s="34"/>
+      <c r="B46" s="35"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="35"/>
+      <c r="E46" s="35"/>
+      <c r="F46" s="35"/>
+      <c r="G46" s="35"/>
+      <c r="H46" s="35"/>
+      <c r="I46" s="35"/>
+      <c r="J46" s="35"/>
+      <c r="K46" s="35"/>
+      <c r="L46" s="35"/>
+      <c r="M46" s="35"/>
+      <c r="T46" s="52"/>
       <c r="U46" s="5"/>
       <c r="V46" s="5"/>
       <c r="W46" s="5"/>
@@ -5032,10 +5006,18 @@
       <c r="M47" s="35" t="s">
         <v>283</v>
       </c>
+      <c r="O47" t="s">
+        <v>38</v>
+      </c>
+      <c r="T47" s="52" t="s">
+        <v>38</v>
+      </c>
       <c r="U47" s="5"/>
       <c r="V47" s="5"/>
       <c r="W47" s="5"/>
-      <c r="Y47" s="7"/>
+      <c r="Y47" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="Z47" s="5"/>
       <c r="AA47" s="5"/>
       <c r="AB47" s="5"/>
@@ -5080,10 +5062,18 @@
       <c r="M48" s="33" t="s">
         <v>287</v>
       </c>
+      <c r="O48" t="s">
+        <v>38</v>
+      </c>
+      <c r="T48" s="52" t="s">
+        <v>38</v>
+      </c>
       <c r="U48" s="7"/>
       <c r="V48" s="7"/>
       <c r="W48" s="7"/>
-      <c r="Y48" s="7"/>
+      <c r="Y48" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="Z48" s="14"/>
       <c r="AA48" s="14"/>
       <c r="AB48" s="14"/>
@@ -5128,10 +5118,18 @@
       <c r="M49" s="35" t="s">
         <v>292</v>
       </c>
+      <c r="O49" t="s">
+        <v>38</v>
+      </c>
+      <c r="T49" s="52" t="s">
+        <v>38</v>
+      </c>
       <c r="U49" s="5"/>
       <c r="V49" s="5"/>
       <c r="W49" s="5"/>
-      <c r="Y49" s="7"/>
+      <c r="Y49" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="Z49" s="5"/>
       <c r="AA49" s="5"/>
       <c r="AB49" s="5"/>
@@ -5176,10 +5174,18 @@
       <c r="M50" s="33" t="s">
         <v>297</v>
       </c>
+      <c r="O50" t="s">
+        <v>38</v>
+      </c>
+      <c r="T50" s="52" t="s">
+        <v>38</v>
+      </c>
       <c r="U50" s="7"/>
       <c r="V50" s="7"/>
       <c r="W50" s="7"/>
-      <c r="Y50" s="7"/>
+      <c r="Y50" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="Z50" s="14"/>
       <c r="AA50" s="14"/>
       <c r="AB50" s="14"/>
@@ -5224,10 +5230,18 @@
       <c r="M51" s="35" t="s">
         <v>300</v>
       </c>
+      <c r="O51" t="s">
+        <v>38</v>
+      </c>
+      <c r="T51" s="52" t="s">
+        <v>38</v>
+      </c>
       <c r="U51" s="36"/>
       <c r="V51" s="36"/>
       <c r="W51" s="36"/>
-      <c r="Y51" s="36"/>
+      <c r="Y51" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="Z51" s="36"/>
       <c r="AA51" s="36"/>
       <c r="AB51" s="36"/>
@@ -5272,10 +5286,18 @@
       <c r="M52" s="35" t="s">
         <v>308</v>
       </c>
+      <c r="O52" t="s">
+        <v>38</v>
+      </c>
+      <c r="T52" s="52" t="s">
+        <v>38</v>
+      </c>
       <c r="U52" s="7"/>
       <c r="V52" s="7"/>
       <c r="W52" s="7"/>
-      <c r="Y52" s="7"/>
+      <c r="Y52" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="Z52" s="14"/>
       <c r="AA52" s="14"/>
       <c r="AB52" s="14"/>
@@ -5320,10 +5342,18 @@
       <c r="M53" s="33" t="s">
         <v>311</v>
       </c>
+      <c r="O53" t="s">
+        <v>38</v>
+      </c>
+      <c r="T53" s="52" t="s">
+        <v>38</v>
+      </c>
       <c r="U53" s="5"/>
       <c r="V53" s="5"/>
       <c r="W53" s="5"/>
-      <c r="Y53" s="7"/>
+      <c r="Y53" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="Z53" s="5"/>
       <c r="AA53" s="5"/>
       <c r="AB53" s="5"/>
@@ -5368,10 +5398,18 @@
       <c r="M54" s="35" t="s">
         <v>311</v>
       </c>
+      <c r="O54" t="s">
+        <v>38</v>
+      </c>
+      <c r="T54" s="52" t="s">
+        <v>38</v>
+      </c>
       <c r="U54" s="7"/>
       <c r="V54" s="7"/>
       <c r="W54" s="7"/>
-      <c r="Y54" s="7"/>
+      <c r="Y54" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="Z54" s="14"/>
       <c r="AA54" s="14"/>
       <c r="AB54" s="14"/>
@@ -5416,10 +5454,18 @@
       <c r="M55" s="33" t="s">
         <v>318</v>
       </c>
+      <c r="O55" t="s">
+        <v>38</v>
+      </c>
+      <c r="T55" s="52" t="s">
+        <v>38</v>
+      </c>
       <c r="U55" s="5"/>
       <c r="V55" s="5"/>
       <c r="W55" s="5"/>
-      <c r="Y55" s="7"/>
+      <c r="Y55" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="Z55" s="5"/>
       <c r="AA55" s="5"/>
       <c r="AB55" s="5"/>
@@ -5464,10 +5510,18 @@
       <c r="M56" s="35" t="s">
         <v>318</v>
       </c>
+      <c r="O56" t="s">
+        <v>38</v>
+      </c>
+      <c r="T56" s="52" t="s">
+        <v>38</v>
+      </c>
       <c r="U56" s="7"/>
       <c r="V56" s="7"/>
       <c r="W56" s="7"/>
-      <c r="Y56" s="7"/>
+      <c r="Y56" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="Z56" s="14"/>
       <c r="AA56" s="14"/>
       <c r="AB56" s="14"/>
@@ -5512,10 +5566,18 @@
       <c r="M57" s="33" t="s">
         <v>324</v>
       </c>
+      <c r="O57" t="s">
+        <v>38</v>
+      </c>
+      <c r="T57" s="52" t="s">
+        <v>38</v>
+      </c>
       <c r="U57" s="5"/>
       <c r="V57" s="5"/>
       <c r="W57" s="5"/>
-      <c r="Y57" s="7"/>
+      <c r="Y57" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="Z57" s="5"/>
       <c r="AA57" s="5"/>
       <c r="AB57" s="5"/>
@@ -5560,10 +5622,18 @@
       <c r="M58" s="35" t="s">
         <v>327</v>
       </c>
+      <c r="O58" t="s">
+        <v>38</v>
+      </c>
+      <c r="T58" s="52" t="s">
+        <v>38</v>
+      </c>
       <c r="U58" s="7"/>
       <c r="V58" s="7"/>
       <c r="W58" s="7"/>
-      <c r="Y58" s="14"/>
+      <c r="Y58" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="Z58" s="14"/>
       <c r="AA58" s="14"/>
       <c r="AB58" s="14"/>
@@ -5608,10 +5678,18 @@
       <c r="M59" s="35" t="s">
         <v>333</v>
       </c>
+      <c r="O59" t="s">
+        <v>38</v>
+      </c>
+      <c r="T59" s="52" t="s">
+        <v>38</v>
+      </c>
       <c r="U59" s="7"/>
       <c r="V59" s="7"/>
       <c r="W59" s="7"/>
-      <c r="Y59" s="7"/>
+      <c r="Y59" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="Z59" s="7"/>
       <c r="AA59" s="7"/>
       <c r="AB59" s="7"/>
@@ -5629,7 +5707,7 @@
       <formula1>46023</formula1>
       <formula2>46387</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Sim ou Não" promptTitle="Sim ou Não" sqref="Q60:Q1048576 Y2:Y59 T2:T59 O2:O1048576" xr:uid="{A33B9050-2903-44EC-9C32-C551C6DD218F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Sim ou Não" promptTitle="Sim ou Não" sqref="Q60:Q1048576 T2:T59 O2:O1048576 Y2:Y59" xr:uid="{A33B9050-2903-44EC-9C32-C551C6DD218F}">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:R59" xr:uid="{66A39B3A-FA32-40B1-A327-70A015F2D105}"/>

--- a/data/base/base implantação.xlsx
+++ b/data/base/base implantação.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/warruda_mgcontecnica_com_br/Documents/Documentos/python/Portal-implantacao-tmp/data/base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="751" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A91D41A5-B774-42DC-BC36-7BD10E10A39A}"/>
+  <xr:revisionPtr revIDLastSave="758" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33FC824F-6F27-4656-BD10-F34F4B63516C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1285,7 +1285,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1306,20 +1306,17 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1334,7 +1331,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1343,6 +1339,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -3290,17 +3288,17 @@
       <c r="M19" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="N19" s="22"/>
-      <c r="O19" s="23"/>
-      <c r="P19" s="22"/>
-      <c r="Q19" s="23"/>
-      <c r="R19" s="22"/>
-      <c r="S19" s="23"/>
-      <c r="T19" s="23"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="21"/>
+      <c r="P19" s="20"/>
+      <c r="Q19" s="21"/>
+      <c r="R19" s="20"/>
+      <c r="S19" s="21"/>
+      <c r="T19" s="21"/>
       <c r="U19" s="5"/>
       <c r="V19" s="5"/>
       <c r="W19" s="5"/>
-      <c r="X19" s="23"/>
+      <c r="X19" s="21"/>
       <c r="Y19" s="7"/>
       <c r="Z19" s="5"/>
       <c r="AA19" s="5"/>
@@ -3408,73 +3406,73 @@
       <c r="M21" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="N21" s="22"/>
-      <c r="O21" s="23"/>
-      <c r="P21" s="22"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="22"/>
-      <c r="S21" s="23"/>
-      <c r="T21" s="23"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="21"/>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="21"/>
+      <c r="R21" s="20"/>
+      <c r="S21" s="21"/>
+      <c r="T21" s="21"/>
       <c r="U21" s="7"/>
       <c r="V21" s="7"/>
       <c r="W21" s="7"/>
-      <c r="X21" s="23"/>
+      <c r="X21" s="21"/>
       <c r="Y21" s="7"/>
       <c r="Z21" s="7"/>
       <c r="AA21" s="7"/>
       <c r="AB21" s="7"/>
     </row>
     <row r="22" spans="1:28">
-      <c r="A22" s="40">
+      <c r="A22" s="37">
         <v>6991</v>
       </c>
-      <c r="B22" s="45" t="s">
+      <c r="B22" s="42" t="s">
         <v>165</v>
       </c>
-      <c r="C22" s="45">
+      <c r="C22" s="42">
         <v>46235</v>
       </c>
-      <c r="D22" s="45" t="s">
+      <c r="D22" s="42" t="s">
         <v>158</v>
       </c>
-      <c r="E22" s="45" t="s">
+      <c r="E22" s="42" t="s">
         <v>159</v>
       </c>
-      <c r="F22" s="45" t="s">
+      <c r="F22" s="42" t="s">
         <v>160</v>
       </c>
-      <c r="G22" s="45" t="s">
+      <c r="G22" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="H22" s="45" t="s">
+      <c r="H22" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="I22" s="45" t="s">
+      <c r="I22" s="42" t="s">
         <v>166</v>
       </c>
-      <c r="J22" s="45" t="s">
+      <c r="J22" s="42" t="s">
         <v>162</v>
       </c>
-      <c r="K22" s="45" t="s">
+      <c r="K22" s="42" t="s">
         <v>163</v>
       </c>
-      <c r="L22" s="45" t="s">
+      <c r="L22" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="M22" s="45" t="s">
+      <c r="M22" s="42" t="s">
         <v>167</v>
       </c>
-      <c r="N22" s="22"/>
-      <c r="O22" s="23"/>
-      <c r="P22" s="22"/>
-      <c r="Q22" s="23"/>
-      <c r="R22" s="22"/>
-      <c r="S22" s="23"/>
-      <c r="T22" s="23"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="21"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="21"/>
+      <c r="R22" s="20"/>
+      <c r="S22" s="21"/>
+      <c r="T22" s="21"/>
       <c r="U22" s="5"/>
       <c r="V22" s="5"/>
       <c r="W22" s="5"/>
-      <c r="X22" s="23"/>
+      <c r="X22" s="21"/>
       <c r="Y22" s="7"/>
       <c r="Z22" s="5"/>
       <c r="AA22" s="5"/>
@@ -3520,7 +3518,7 @@
       <c r="M23" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="N23" s="21"/>
+      <c r="N23" s="28"/>
       <c r="O23" s="7" t="s">
         <v>38</v>
       </c>
@@ -3584,7 +3582,7 @@
       <c r="M24" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="N24" s="47"/>
+      <c r="N24" s="43"/>
       <c r="O24" s="5" t="s">
         <v>38</v>
       </c>
@@ -3648,7 +3646,7 @@
       <c r="M25" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="N25" s="48">
+      <c r="N25" s="44">
         <v>46252</v>
       </c>
       <c r="O25" s="7" t="s">
@@ -3716,7 +3714,7 @@
       <c r="M26" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="N26" s="47"/>
+      <c r="N26" s="43"/>
       <c r="O26" s="5" t="s">
         <v>38</v>
       </c>
@@ -3778,7 +3776,7 @@
       <c r="M27" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="N27" s="29"/>
+      <c r="N27" s="28"/>
       <c r="O27" s="7" t="s">
         <v>38</v>
       </c>
@@ -3840,7 +3838,7 @@
       <c r="M28" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="N28" s="49">
+      <c r="N28" s="45">
         <v>46269</v>
       </c>
       <c r="O28" s="5" t="s">
@@ -3904,7 +3902,7 @@
       <c r="M29" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="N29" s="48">
+      <c r="N29" s="44">
         <v>46255</v>
       </c>
       <c r="O29" s="7" t="s">
@@ -3913,7 +3911,7 @@
       <c r="P29" s="7"/>
       <c r="Q29" s="7"/>
       <c r="R29" s="7"/>
-      <c r="S29" s="22">
+      <c r="S29" s="20">
         <v>46255</v>
       </c>
       <c r="T29" s="7" t="s">
@@ -3970,7 +3968,7 @@
       <c r="M30" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="N30" s="48">
+      <c r="N30" s="44">
         <v>46255</v>
       </c>
       <c r="O30" s="5" t="s">
@@ -3979,7 +3977,7 @@
       <c r="P30" s="5"/>
       <c r="Q30" s="5"/>
       <c r="R30" s="5"/>
-      <c r="S30" s="22">
+      <c r="S30" s="20">
         <v>46255</v>
       </c>
       <c r="T30" s="5" t="s">
@@ -4036,7 +4034,7 @@
       <c r="M31" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="N31" s="19">
+      <c r="N31" s="18">
         <v>46255</v>
       </c>
       <c r="O31" s="7" t="s">
@@ -4045,7 +4043,7 @@
       <c r="P31" s="7"/>
       <c r="Q31" s="7"/>
       <c r="R31" s="7"/>
-      <c r="S31" s="22">
+      <c r="S31" s="20">
         <v>46255</v>
       </c>
       <c r="T31" s="7" t="s">
@@ -4102,7 +4100,7 @@
       <c r="M32" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="N32" s="19">
+      <c r="N32" s="18">
         <v>46255</v>
       </c>
       <c r="O32" s="5" t="s">
@@ -4111,7 +4109,7 @@
       <c r="P32" s="5"/>
       <c r="Q32" s="5"/>
       <c r="R32" s="5"/>
-      <c r="S32" s="22">
+      <c r="S32" s="20">
         <v>46255</v>
       </c>
       <c r="T32" s="5" t="s">
@@ -4177,7 +4175,7 @@
       <c r="P33" s="7"/>
       <c r="Q33" s="7"/>
       <c r="R33" s="7"/>
-      <c r="S33" s="22">
+      <c r="S33" s="20">
         <v>46255</v>
       </c>
       <c r="T33" s="7" t="s">
@@ -4243,7 +4241,7 @@
       <c r="P34" s="5"/>
       <c r="Q34" s="5"/>
       <c r="R34" s="5"/>
-      <c r="S34" s="22">
+      <c r="S34" s="20">
         <v>46255</v>
       </c>
       <c r="T34" s="5" t="s">
@@ -4309,7 +4307,7 @@
       <c r="P35" s="7"/>
       <c r="Q35" s="7"/>
       <c r="R35" s="7"/>
-      <c r="S35" s="22">
+      <c r="S35" s="20">
         <v>46255</v>
       </c>
       <c r="T35" s="7" t="s">
@@ -4375,7 +4373,7 @@
       <c r="P36" s="5"/>
       <c r="Q36" s="5"/>
       <c r="R36" s="5"/>
-      <c r="S36" s="22">
+      <c r="S36" s="20">
         <v>46255</v>
       </c>
       <c r="T36" s="5" t="s">
@@ -4393,7 +4391,7 @@
       <c r="AB36" s="5"/>
     </row>
     <row r="37" spans="1:28">
-      <c r="A37" s="39">
+      <c r="A37" s="36">
         <v>7020</v>
       </c>
       <c r="B37" s="14" t="s">
@@ -4432,7 +4430,7 @@
       <c r="M37" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="N37" s="51">
+      <c r="N37" s="47">
         <v>46255</v>
       </c>
       <c r="O37" s="14" t="s">
@@ -4440,8 +4438,8 @@
       </c>
       <c r="P37" s="7"/>
       <c r="Q37" s="7"/>
-      <c r="R37" s="29"/>
-      <c r="S37" s="53">
+      <c r="R37" s="28"/>
+      <c r="S37" s="49">
         <v>46255</v>
       </c>
       <c r="T37" s="14" t="s">
@@ -4459,290 +4457,290 @@
       <c r="AB37" s="14"/>
     </row>
     <row r="38" spans="1:28">
-      <c r="A38" s="42">
+      <c r="A38" s="39">
         <v>7021</v>
       </c>
-      <c r="B38" s="42" t="s">
+      <c r="B38" s="39" t="s">
         <v>237</v>
       </c>
-      <c r="C38" s="42">
+      <c r="C38" s="39">
         <v>46235</v>
       </c>
-      <c r="D38" s="42" t="s">
+      <c r="D38" s="39" t="s">
         <v>205</v>
       </c>
-      <c r="E38" s="42" t="s">
+      <c r="E38" s="39" t="s">
         <v>226</v>
       </c>
-      <c r="F38" s="42" t="s">
+      <c r="F38" s="39" t="s">
         <v>227</v>
       </c>
-      <c r="G38" s="42" t="s">
+      <c r="G38" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="H38" s="42" t="s">
+      <c r="H38" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="I38" s="42" t="s">
+      <c r="I38" s="39" t="s">
         <v>228</v>
       </c>
-      <c r="J38" s="42" t="s">
+      <c r="J38" s="39" t="s">
         <v>217</v>
       </c>
-      <c r="K38" s="42" t="s">
+      <c r="K38" s="39" t="s">
         <v>229</v>
       </c>
-      <c r="L38" s="42" t="s">
+      <c r="L38" s="39" t="s">
         <v>219</v>
       </c>
-      <c r="M38" s="47" t="s">
+      <c r="M38" s="43" t="s">
         <v>236</v>
       </c>
-      <c r="N38" s="51">
+      <c r="N38" s="47">
         <v>46255</v>
       </c>
-      <c r="O38" s="47" t="s">
+      <c r="O38" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="P38" s="47"/>
-      <c r="Q38" s="47"/>
-      <c r="R38" s="47"/>
-      <c r="S38" s="53">
+      <c r="P38" s="43"/>
+      <c r="Q38" s="43"/>
+      <c r="R38" s="43"/>
+      <c r="S38" s="49">
         <v>46255</v>
       </c>
-      <c r="T38" s="47" t="s">
+      <c r="T38" s="43" t="s">
         <v>50</v>
       </c>
       <c r="U38" s="5"/>
       <c r="V38" s="5"/>
       <c r="W38" s="5"/>
-      <c r="X38" s="47"/>
+      <c r="X38" s="43"/>
       <c r="Y38" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="Z38" s="20"/>
-      <c r="AA38" s="47"/>
+      <c r="Z38" s="19"/>
+      <c r="AA38" s="43"/>
       <c r="AB38" s="5"/>
     </row>
     <row r="39" spans="1:28">
-      <c r="A39" s="38">
+      <c r="A39" s="35">
         <v>7036</v>
       </c>
-      <c r="B39" s="44" t="s">
+      <c r="B39" s="41" t="s">
         <v>238</v>
       </c>
-      <c r="C39" s="44">
+      <c r="C39" s="41">
         <v>46266</v>
       </c>
-      <c r="D39" s="44" t="s">
+      <c r="D39" s="41" t="s">
         <v>239</v>
       </c>
-      <c r="E39" s="44" t="s">
+      <c r="E39" s="41" t="s">
         <v>142</v>
       </c>
-      <c r="F39" s="44" t="s">
+      <c r="F39" s="41" t="s">
         <v>143</v>
       </c>
-      <c r="G39" s="44" t="s">
+      <c r="G39" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="H39" s="44" t="s">
+      <c r="H39" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="I39" s="44" t="s">
+      <c r="I39" s="41" t="s">
         <v>240</v>
       </c>
-      <c r="J39" s="44" t="s">
+      <c r="J39" s="41" t="s">
         <v>241</v>
       </c>
-      <c r="K39" s="44" t="s">
+      <c r="K39" s="41" t="s">
         <v>242</v>
       </c>
-      <c r="L39" s="44" t="s">
+      <c r="L39" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="M39" s="44" t="s">
+      <c r="M39" s="41" t="s">
         <v>243</v>
       </c>
-      <c r="N39" s="49">
+      <c r="N39" s="45">
         <v>46261</v>
       </c>
-      <c r="O39" s="47" t="s">
+      <c r="O39" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="P39" s="47" t="s">
+      <c r="P39" s="43" t="s">
         <v>244</v>
       </c>
-      <c r="Q39" s="47" t="s">
+      <c r="Q39" s="43" t="s">
         <v>245</v>
       </c>
-      <c r="R39" s="24" t="s">
+      <c r="R39" s="43" t="s">
         <v>246</v>
       </c>
-      <c r="S39" s="49">
+      <c r="S39" s="45">
         <v>46261</v>
       </c>
-      <c r="T39" s="47" t="s">
+      <c r="T39" s="43" t="s">
         <v>50</v>
       </c>
       <c r="U39" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="V39" s="25" t="s">
+      <c r="V39" s="22" t="s">
         <v>248</v>
       </c>
       <c r="W39" s="5"/>
-      <c r="X39" s="47"/>
+      <c r="X39" s="43"/>
       <c r="Y39" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="Z39" s="20" t="s">
+      <c r="Z39" s="19" t="s">
         <v>249</v>
       </c>
-      <c r="AA39" s="26" t="s">
+      <c r="AA39" s="23" t="s">
         <v>250</v>
       </c>
-      <c r="AB39" s="20"/>
+      <c r="AB39" s="19"/>
     </row>
     <row r="40" spans="1:28">
-      <c r="A40" s="41">
+      <c r="A40" s="38">
         <v>7037</v>
       </c>
-      <c r="B40" s="28" t="s">
+      <c r="B40" s="25" t="s">
         <v>251</v>
       </c>
-      <c r="C40" s="28">
+      <c r="C40" s="25">
         <v>46266</v>
       </c>
-      <c r="D40" s="28" t="s">
+      <c r="D40" s="25" t="s">
         <v>239</v>
       </c>
-      <c r="E40" s="28" t="s">
+      <c r="E40" s="25" t="s">
         <v>142</v>
       </c>
-      <c r="F40" s="28" t="s">
+      <c r="F40" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="G40" s="28" t="s">
+      <c r="G40" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H40" s="28" t="s">
+      <c r="H40" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="I40" s="28" t="s">
+      <c r="I40" s="25" t="s">
         <v>252</v>
       </c>
-      <c r="J40" s="28" t="s">
+      <c r="J40" s="25" t="s">
         <v>241</v>
       </c>
-      <c r="K40" s="28" t="s">
+      <c r="K40" s="25" t="s">
         <v>242</v>
       </c>
-      <c r="L40" s="28" t="s">
+      <c r="L40" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="M40" s="28" t="s">
+      <c r="M40" s="25" t="s">
         <v>253</v>
       </c>
-      <c r="N40" s="49">
+      <c r="N40" s="45">
         <v>46261</v>
       </c>
-      <c r="O40" s="21" t="s">
+      <c r="O40" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="P40" s="21" t="s">
+      <c r="P40" s="28" t="s">
         <v>244</v>
       </c>
-      <c r="Q40" s="21" t="s">
+      <c r="Q40" s="28" t="s">
         <v>245</v>
       </c>
-      <c r="R40" s="18" t="s">
+      <c r="R40" s="51" t="s">
         <v>246</v>
       </c>
-      <c r="S40" s="49">
+      <c r="S40" s="45">
         <v>46261</v>
       </c>
-      <c r="T40" s="21" t="s">
+      <c r="T40" s="28" t="s">
         <v>50</v>
       </c>
       <c r="U40" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="V40" s="25" t="s">
+      <c r="V40" s="22" t="s">
         <v>248</v>
       </c>
       <c r="W40" s="7"/>
-      <c r="X40" s="21"/>
+      <c r="X40" s="28"/>
       <c r="Y40" s="7" t="s">
         <v>38</v>
       </c>
       <c r="Z40" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="AA40" s="54" t="s">
+      <c r="AA40" s="50" t="s">
         <v>250</v>
       </c>
       <c r="AB40" s="7"/>
     </row>
     <row r="41" spans="1:28">
-      <c r="A41" s="27">
+      <c r="A41" s="24">
         <v>7046</v>
       </c>
-      <c r="B41" s="28" t="s">
+      <c r="B41" s="25" t="s">
         <v>254</v>
       </c>
-      <c r="C41" s="28">
+      <c r="C41" s="25">
         <v>46266</v>
       </c>
-      <c r="D41" s="28" t="s">
+      <c r="D41" s="25" t="s">
         <v>255</v>
       </c>
-      <c r="E41" s="28" t="s">
+      <c r="E41" s="25" t="s">
         <v>159</v>
       </c>
-      <c r="F41" s="28" t="s">
+      <c r="F41" s="25" t="s">
         <v>199</v>
       </c>
-      <c r="G41" s="28" t="s">
+      <c r="G41" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H41" s="28" t="s">
+      <c r="H41" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="I41" s="28" t="s">
+      <c r="I41" s="25" t="s">
         <v>256</v>
       </c>
-      <c r="J41" s="28" t="s">
+      <c r="J41" s="25" t="s">
         <v>257</v>
       </c>
-      <c r="K41" s="28" t="s">
+      <c r="K41" s="25" t="s">
         <v>258</v>
       </c>
-      <c r="L41" s="28" t="s">
+      <c r="L41" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="M41" s="28" t="s">
+      <c r="M41" s="25" t="s">
         <v>259</v>
       </c>
-      <c r="N41" s="50">
+      <c r="N41" s="46">
         <v>46267</v>
       </c>
-      <c r="O41" s="52" t="s">
-        <v>38</v>
-      </c>
-      <c r="P41" s="50"/>
-      <c r="Q41" s="52"/>
-      <c r="R41" s="50"/>
-      <c r="S41" s="50">
+      <c r="O41" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="P41" s="46"/>
+      <c r="Q41" s="48"/>
+      <c r="R41" s="46"/>
+      <c r="S41" s="46">
         <v>46267</v>
       </c>
-      <c r="T41" s="52" t="s">
+      <c r="T41" s="48" t="s">
         <v>38</v>
       </c>
       <c r="U41" s="5"/>
       <c r="V41" s="5"/>
       <c r="W41" s="5"/>
-      <c r="X41" s="50">
+      <c r="X41" s="46">
         <v>46266</v>
       </c>
       <c r="Y41" s="7" t="s">
@@ -4753,54 +4751,60 @@
       <c r="AB41" s="5"/>
     </row>
     <row r="42" spans="1:28">
-      <c r="A42" s="27">
+      <c r="A42" s="24">
         <v>7048</v>
       </c>
-      <c r="B42" s="28" t="s">
+      <c r="B42" s="25" t="s">
         <v>260</v>
       </c>
       <c r="C42" s="5">
         <v>46266</v>
       </c>
-      <c r="D42" s="28" t="s">
+      <c r="D42" s="25" t="s">
         <v>261</v>
       </c>
-      <c r="E42" s="28" t="s">
+      <c r="E42" s="25" t="s">
         <v>170</v>
       </c>
-      <c r="F42" s="28" t="s">
+      <c r="F42" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="G42" s="28" t="s">
+      <c r="G42" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H42" s="28" t="s">
+      <c r="H42" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="I42" s="28" t="s">
+      <c r="I42" s="25" t="s">
         <v>262</v>
       </c>
-      <c r="J42" s="28" t="s">
+      <c r="J42" s="25" t="s">
         <v>263</v>
       </c>
-      <c r="K42" s="28" t="s">
+      <c r="K42" s="25" t="s">
         <v>264</v>
       </c>
-      <c r="L42" s="28" t="s">
+      <c r="L42" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="M42" s="28" t="s">
+      <c r="M42" s="25" t="s">
         <v>265</v>
       </c>
-      <c r="O42" t="s">
-        <v>38</v>
-      </c>
-      <c r="T42" s="52" t="s">
+      <c r="N42" s="46"/>
+      <c r="O42" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="P42" s="46"/>
+      <c r="Q42" s="48"/>
+      <c r="R42" s="46"/>
+      <c r="S42" s="48"/>
+      <c r="T42" s="48" t="s">
         <v>38</v>
       </c>
       <c r="U42" s="7"/>
       <c r="V42" s="7"/>
       <c r="W42" s="7"/>
+      <c r="X42" s="48"/>
       <c r="Y42" s="7" t="s">
         <v>38</v>
       </c>
@@ -4809,133 +4813,184 @@
       <c r="AB42" s="14"/>
     </row>
     <row r="43" spans="1:28">
-      <c r="A43" s="30"/>
-      <c r="B43" s="31"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="31"/>
-      <c r="E43" s="31"/>
-      <c r="F43" s="31"/>
-      <c r="G43" s="31"/>
-      <c r="H43" s="31"/>
-      <c r="I43" s="31"/>
-      <c r="J43" s="31"/>
-      <c r="K43" s="31"/>
-      <c r="L43" s="31"/>
-      <c r="M43" s="46"/>
-      <c r="T43" s="52"/>
-      <c r="U43" s="7"/>
-      <c r="V43" s="7"/>
-      <c r="W43" s="7"/>
-      <c r="Y43" s="7"/>
-      <c r="Z43" s="7"/>
-      <c r="AA43" s="7"/>
-      <c r="AB43" s="7"/>
+      <c r="A43" s="34">
+        <v>7049</v>
+      </c>
+      <c r="B43" s="40" t="s">
+        <v>266</v>
+      </c>
+      <c r="C43" s="5">
+        <v>46266</v>
+      </c>
+      <c r="D43" s="40" t="s">
+        <v>261</v>
+      </c>
+      <c r="E43" s="40" t="s">
+        <v>170</v>
+      </c>
+      <c r="F43" s="40" t="s">
+        <v>267</v>
+      </c>
+      <c r="G43" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="H43" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="I43" s="40" t="s">
+        <v>268</v>
+      </c>
+      <c r="J43" s="40" t="s">
+        <v>269</v>
+      </c>
+      <c r="K43" s="40" t="s">
+        <v>270</v>
+      </c>
+      <c r="L43" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="M43" s="52" t="s">
+        <v>271</v>
+      </c>
+      <c r="N43" s="46"/>
+      <c r="O43" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="P43" s="46"/>
+      <c r="Q43" s="48"/>
+      <c r="R43" s="46"/>
+      <c r="S43" s="48"/>
+      <c r="T43" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="U43" s="5"/>
+      <c r="V43" s="5"/>
+      <c r="W43" s="5"/>
+      <c r="X43" s="48"/>
+      <c r="Y43" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z43" s="5"/>
+      <c r="AA43" s="5"/>
+      <c r="AB43" s="5"/>
     </row>
     <row r="44" spans="1:28">
-      <c r="A44" s="37">
-        <v>7049</v>
-      </c>
-      <c r="B44" s="43" t="s">
-        <v>266</v>
+      <c r="A44" s="26">
+        <v>7050</v>
+      </c>
+      <c r="B44" s="27" t="s">
+        <v>272</v>
       </c>
       <c r="C44" s="5">
         <v>46266</v>
       </c>
-      <c r="D44" s="43" t="s">
-        <v>261</v>
-      </c>
-      <c r="E44" s="43" t="s">
+      <c r="D44" s="27" t="s">
+        <v>273</v>
+      </c>
+      <c r="E44" s="27" t="s">
         <v>170</v>
       </c>
-      <c r="F44" s="43" t="s">
-        <v>267</v>
-      </c>
-      <c r="G44" s="43" t="s">
+      <c r="F44" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="G44" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="H44" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="I44" s="43" t="s">
-        <v>268</v>
-      </c>
-      <c r="J44" s="43" t="s">
-        <v>269</v>
-      </c>
-      <c r="K44" s="43" t="s">
-        <v>270</v>
-      </c>
-      <c r="L44" s="43" t="s">
+      <c r="H44" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="I44" s="27" t="s">
+        <v>274</v>
+      </c>
+      <c r="J44" s="27" t="s">
+        <v>275</v>
+      </c>
+      <c r="K44" s="27" t="s">
+        <v>276</v>
+      </c>
+      <c r="L44" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="M44" s="43" t="s">
-        <v>271</v>
-      </c>
-      <c r="O44" t="s">
-        <v>38</v>
-      </c>
-      <c r="T44" s="52" t="s">
+      <c r="M44" s="27" t="s">
+        <v>277</v>
+      </c>
+      <c r="N44" s="46"/>
+      <c r="O44" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="P44" s="46"/>
+      <c r="Q44" s="48"/>
+      <c r="R44" s="46"/>
+      <c r="S44" s="48"/>
+      <c r="T44" s="48" t="s">
         <v>38</v>
       </c>
       <c r="U44" s="5"/>
       <c r="V44" s="5"/>
       <c r="W44" s="5"/>
+      <c r="X44" s="48"/>
       <c r="Y44" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="Z44" s="20"/>
-      <c r="AA44" s="20"/>
-      <c r="AB44" s="20"/>
+      <c r="Z44" s="19"/>
+      <c r="AA44" s="19"/>
+      <c r="AB44" s="19"/>
     </row>
     <row r="45" spans="1:28">
-      <c r="A45" s="27">
-        <v>7050</v>
-      </c>
-      <c r="B45" s="28" t="s">
-        <v>272</v>
+      <c r="A45" s="31">
+        <v>7052</v>
+      </c>
+      <c r="B45" s="32" t="s">
+        <v>278</v>
       </c>
       <c r="C45" s="5">
         <v>46266</v>
       </c>
-      <c r="D45" s="28" t="s">
-        <v>273</v>
-      </c>
-      <c r="E45" s="28" t="s">
-        <v>170</v>
-      </c>
-      <c r="F45" s="28" t="s">
-        <v>65</v>
-      </c>
-      <c r="G45" s="28" t="s">
+      <c r="D45" s="32" t="s">
+        <v>279</v>
+      </c>
+      <c r="E45" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="F45" s="32" t="s">
+        <v>267</v>
+      </c>
+      <c r="G45" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="H45" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="I45" s="28" t="s">
-        <v>274</v>
-      </c>
-      <c r="J45" s="28" t="s">
-        <v>275</v>
-      </c>
-      <c r="K45" s="28" t="s">
-        <v>276</v>
-      </c>
-      <c r="L45" s="28" t="s">
+      <c r="H45" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="I45" s="32" t="s">
+        <v>280</v>
+      </c>
+      <c r="J45" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="K45" s="32" t="s">
+        <v>282</v>
+      </c>
+      <c r="L45" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="M45" s="28" t="s">
-        <v>277</v>
-      </c>
-      <c r="O45" t="s">
-        <v>38</v>
-      </c>
-      <c r="T45" s="52" t="s">
+      <c r="M45" s="32" t="s">
+        <v>283</v>
+      </c>
+      <c r="N45" s="46"/>
+      <c r="O45" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="P45" s="46"/>
+      <c r="Q45" s="48"/>
+      <c r="R45" s="46"/>
+      <c r="S45" s="48"/>
+      <c r="T45" s="48" t="s">
         <v>38</v>
       </c>
       <c r="U45" s="5"/>
       <c r="V45" s="5"/>
       <c r="W45" s="5"/>
+      <c r="X45" s="48"/>
       <c r="Y45" s="7" t="s">
         <v>38</v>
       </c>
@@ -4944,77 +4999,122 @@
       <c r="AB45" s="5"/>
     </row>
     <row r="46" spans="1:28">
-      <c r="A46" s="34"/>
-      <c r="B46" s="35"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="35"/>
-      <c r="E46" s="35"/>
-      <c r="F46" s="35"/>
-      <c r="G46" s="35"/>
-      <c r="H46" s="35"/>
-      <c r="I46" s="35"/>
-      <c r="J46" s="35"/>
-      <c r="K46" s="35"/>
-      <c r="L46" s="35"/>
-      <c r="M46" s="35"/>
-      <c r="T46" s="52"/>
-      <c r="U46" s="5"/>
-      <c r="V46" s="5"/>
-      <c r="W46" s="5"/>
-      <c r="Y46" s="7"/>
-      <c r="Z46" s="20"/>
-      <c r="AA46" s="20"/>
-      <c r="AB46" s="20"/>
+      <c r="A46" s="29">
+        <v>7053</v>
+      </c>
+      <c r="B46" s="30" t="s">
+        <v>284</v>
+      </c>
+      <c r="C46" s="5">
+        <v>46266</v>
+      </c>
+      <c r="D46" s="30" t="s">
+        <v>279</v>
+      </c>
+      <c r="E46" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="F46" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="G46" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="H46" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="I46" s="30" t="s">
+        <v>285</v>
+      </c>
+      <c r="J46" s="30" t="s">
+        <v>286</v>
+      </c>
+      <c r="K46" s="30" t="s">
+        <v>282</v>
+      </c>
+      <c r="L46" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="M46" s="30" t="s">
+        <v>287</v>
+      </c>
+      <c r="N46" s="46"/>
+      <c r="O46" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="P46" s="46"/>
+      <c r="Q46" s="48"/>
+      <c r="R46" s="46"/>
+      <c r="S46" s="48"/>
+      <c r="T46" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="U46" s="7"/>
+      <c r="V46" s="7"/>
+      <c r="W46" s="7"/>
+      <c r="X46" s="48"/>
+      <c r="Y46" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z46" s="14"/>
+      <c r="AA46" s="14"/>
+      <c r="AB46" s="14"/>
     </row>
     <row r="47" spans="1:28">
-      <c r="A47" s="34">
-        <v>7052</v>
-      </c>
-      <c r="B47" s="35" t="s">
-        <v>278</v>
+      <c r="A47" s="31">
+        <v>7054</v>
+      </c>
+      <c r="B47" s="32" t="s">
+        <v>288</v>
       </c>
       <c r="C47" s="5">
         <v>46266</v>
       </c>
-      <c r="D47" s="35" t="s">
+      <c r="D47" s="32" t="s">
         <v>279</v>
       </c>
-      <c r="E47" s="35" t="s">
+      <c r="E47" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="F47" s="35" t="s">
-        <v>267</v>
-      </c>
-      <c r="G47" s="35" t="s">
+      <c r="F47" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="G47" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="H47" s="35" t="s">
+      <c r="H47" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="I47" s="35" t="s">
-        <v>280</v>
-      </c>
-      <c r="J47" s="35" t="s">
-        <v>281</v>
-      </c>
-      <c r="K47" s="35" t="s">
-        <v>282</v>
-      </c>
-      <c r="L47" s="35" t="s">
+      <c r="I47" s="32" t="s">
+        <v>289</v>
+      </c>
+      <c r="J47" s="32" t="s">
+        <v>290</v>
+      </c>
+      <c r="K47" s="32" t="s">
+        <v>291</v>
+      </c>
+      <c r="L47" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="M47" s="35" t="s">
-        <v>283</v>
-      </c>
-      <c r="O47" t="s">
-        <v>38</v>
-      </c>
-      <c r="T47" s="52" t="s">
+      <c r="M47" s="32" t="s">
+        <v>292</v>
+      </c>
+      <c r="N47" s="46"/>
+      <c r="O47" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="P47" s="46"/>
+      <c r="Q47" s="48"/>
+      <c r="R47" s="46"/>
+      <c r="S47" s="48"/>
+      <c r="T47" s="48" t="s">
         <v>38</v>
       </c>
       <c r="U47" s="5"/>
       <c r="V47" s="5"/>
       <c r="W47" s="5"/>
+      <c r="X47" s="48"/>
       <c r="Y47" s="7" t="s">
         <v>38</v>
       </c>
@@ -5023,54 +5123,60 @@
       <c r="AB47" s="5"/>
     </row>
     <row r="48" spans="1:28">
-      <c r="A48" s="32">
-        <v>7053</v>
-      </c>
-      <c r="B48" s="33" t="s">
-        <v>284</v>
+      <c r="A48" s="29">
+        <v>7055</v>
+      </c>
+      <c r="B48" s="30" t="s">
+        <v>293</v>
       </c>
       <c r="C48" s="5">
         <v>46266</v>
       </c>
-      <c r="D48" s="33" t="s">
+      <c r="D48" s="30" t="s">
         <v>279</v>
       </c>
-      <c r="E48" s="33" t="s">
+      <c r="E48" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="F48" s="33" t="s">
+      <c r="F48" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="G48" s="33" t="s">
+      <c r="G48" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="H48" s="33" t="s">
+      <c r="H48" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="I48" s="33" t="s">
-        <v>285</v>
-      </c>
-      <c r="J48" s="33" t="s">
-        <v>286</v>
-      </c>
-      <c r="K48" s="33" t="s">
-        <v>282</v>
-      </c>
-      <c r="L48" s="33" t="s">
+      <c r="I48" s="30" t="s">
+        <v>294</v>
+      </c>
+      <c r="J48" s="30" t="s">
+        <v>295</v>
+      </c>
+      <c r="K48" s="30" t="s">
+        <v>296</v>
+      </c>
+      <c r="L48" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="M48" s="33" t="s">
-        <v>287</v>
-      </c>
-      <c r="O48" t="s">
-        <v>38</v>
-      </c>
-      <c r="T48" s="52" t="s">
+      <c r="M48" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="N48" s="46"/>
+      <c r="O48" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="P48" s="46"/>
+      <c r="Q48" s="48"/>
+      <c r="R48" s="46"/>
+      <c r="S48" s="48"/>
+      <c r="T48" s="48" t="s">
         <v>38</v>
       </c>
       <c r="U48" s="7"/>
       <c r="V48" s="7"/>
       <c r="W48" s="7"/>
+      <c r="X48" s="48"/>
       <c r="Y48" s="7" t="s">
         <v>38</v>
       </c>
@@ -5079,110 +5185,122 @@
       <c r="AB48" s="14"/>
     </row>
     <row r="49" spans="1:28">
-      <c r="A49" s="34">
-        <v>7054</v>
-      </c>
-      <c r="B49" s="35" t="s">
-        <v>288</v>
+      <c r="A49" s="31">
+        <v>7056</v>
+      </c>
+      <c r="B49" s="32" t="s">
+        <v>298</v>
       </c>
       <c r="C49" s="5">
         <v>46266</v>
       </c>
-      <c r="D49" s="35" t="s">
+      <c r="D49" s="32" t="s">
         <v>279</v>
       </c>
-      <c r="E49" s="35" t="s">
+      <c r="E49" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="F49" s="35" t="s">
+      <c r="F49" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="G49" s="35" t="s">
+      <c r="G49" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="H49" s="35" t="s">
+      <c r="H49" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="I49" s="35" t="s">
+      <c r="I49" s="32" t="s">
         <v>289</v>
       </c>
-      <c r="J49" s="35" t="s">
-        <v>290</v>
-      </c>
-      <c r="K49" s="35" t="s">
-        <v>291</v>
-      </c>
-      <c r="L49" s="35" t="s">
+      <c r="J49" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="K49" s="32" t="s">
+        <v>296</v>
+      </c>
+      <c r="L49" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="M49" s="35" t="s">
-        <v>292</v>
-      </c>
-      <c r="O49" t="s">
-        <v>38</v>
-      </c>
-      <c r="T49" s="52" t="s">
-        <v>38</v>
-      </c>
-      <c r="U49" s="5"/>
-      <c r="V49" s="5"/>
-      <c r="W49" s="5"/>
+      <c r="M49" s="32" t="s">
+        <v>300</v>
+      </c>
+      <c r="N49" s="46"/>
+      <c r="O49" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="P49" s="46"/>
+      <c r="Q49" s="48"/>
+      <c r="R49" s="46"/>
+      <c r="S49" s="48"/>
+      <c r="T49" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="U49" s="33"/>
+      <c r="V49" s="33"/>
+      <c r="W49" s="33"/>
+      <c r="X49" s="48"/>
       <c r="Y49" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="Z49" s="5"/>
-      <c r="AA49" s="5"/>
-      <c r="AB49" s="5"/>
+      <c r="Z49" s="33"/>
+      <c r="AA49" s="33"/>
+      <c r="AB49" s="33"/>
     </row>
     <row r="50" spans="1:28">
-      <c r="A50" s="32">
-        <v>7055</v>
-      </c>
-      <c r="B50" s="33" t="s">
-        <v>293</v>
+      <c r="A50" s="31">
+        <v>7057</v>
+      </c>
+      <c r="B50" s="32" t="s">
+        <v>301</v>
       </c>
       <c r="C50" s="5">
         <v>46266</v>
       </c>
-      <c r="D50" s="33" t="s">
-        <v>279</v>
-      </c>
-      <c r="E50" s="33" t="s">
-        <v>64</v>
-      </c>
-      <c r="F50" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="G50" s="33" t="s">
+      <c r="D50" s="32" t="s">
+        <v>302</v>
+      </c>
+      <c r="E50" s="32" t="s">
+        <v>303</v>
+      </c>
+      <c r="F50" s="32" t="s">
+        <v>304</v>
+      </c>
+      <c r="G50" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="H50" s="33" t="s">
+      <c r="H50" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="I50" s="33" t="s">
-        <v>294</v>
-      </c>
-      <c r="J50" s="33" t="s">
-        <v>295</v>
-      </c>
-      <c r="K50" s="33" t="s">
-        <v>296</v>
-      </c>
-      <c r="L50" s="33" t="s">
+      <c r="I50" s="32" t="s">
+        <v>305</v>
+      </c>
+      <c r="J50" s="32" t="s">
+        <v>306</v>
+      </c>
+      <c r="K50" s="32" t="s">
+        <v>307</v>
+      </c>
+      <c r="L50" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="M50" s="33" t="s">
-        <v>297</v>
-      </c>
-      <c r="O50" t="s">
-        <v>38</v>
-      </c>
-      <c r="T50" s="52" t="s">
+      <c r="M50" s="32" t="s">
+        <v>308</v>
+      </c>
+      <c r="N50" s="46"/>
+      <c r="O50" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="P50" s="46"/>
+      <c r="Q50" s="48"/>
+      <c r="R50" s="46"/>
+      <c r="S50" s="48"/>
+      <c r="T50" s="48" t="s">
         <v>38</v>
       </c>
       <c r="U50" s="7"/>
       <c r="V50" s="7"/>
       <c r="W50" s="7"/>
+      <c r="X50" s="48"/>
       <c r="Y50" s="7" t="s">
         <v>38</v>
       </c>
@@ -5191,110 +5309,122 @@
       <c r="AB50" s="14"/>
     </row>
     <row r="51" spans="1:28">
-      <c r="A51" s="34">
-        <v>7056</v>
-      </c>
-      <c r="B51" s="35" t="s">
-        <v>298</v>
+      <c r="A51" s="29">
+        <v>7058</v>
+      </c>
+      <c r="B51" s="30" t="s">
+        <v>309</v>
       </c>
       <c r="C51" s="5">
         <v>46266</v>
       </c>
-      <c r="D51" s="35" t="s">
-        <v>279</v>
-      </c>
-      <c r="E51" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="F51" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="G51" s="35" t="s">
+      <c r="D51" s="30" t="s">
+        <v>302</v>
+      </c>
+      <c r="E51" s="30" t="s">
+        <v>303</v>
+      </c>
+      <c r="F51" s="30" t="s">
+        <v>304</v>
+      </c>
+      <c r="G51" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="H51" s="35" t="s">
+      <c r="H51" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="I51" s="35" t="s">
-        <v>289</v>
-      </c>
-      <c r="J51" s="35" t="s">
-        <v>299</v>
-      </c>
-      <c r="K51" s="35" t="s">
-        <v>296</v>
-      </c>
-      <c r="L51" s="35" t="s">
+      <c r="I51" s="30" t="s">
+        <v>310</v>
+      </c>
+      <c r="J51" s="30" t="s">
+        <v>306</v>
+      </c>
+      <c r="K51" s="30" t="s">
+        <v>307</v>
+      </c>
+      <c r="L51" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="M51" s="35" t="s">
-        <v>300</v>
-      </c>
-      <c r="O51" t="s">
-        <v>38</v>
-      </c>
-      <c r="T51" s="52" t="s">
-        <v>38</v>
-      </c>
-      <c r="U51" s="36"/>
-      <c r="V51" s="36"/>
-      <c r="W51" s="36"/>
+      <c r="M51" s="30" t="s">
+        <v>311</v>
+      </c>
+      <c r="N51" s="46"/>
+      <c r="O51" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="P51" s="46"/>
+      <c r="Q51" s="48"/>
+      <c r="R51" s="46"/>
+      <c r="S51" s="48"/>
+      <c r="T51" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="U51" s="5"/>
+      <c r="V51" s="5"/>
+      <c r="W51" s="5"/>
+      <c r="X51" s="48"/>
       <c r="Y51" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="Z51" s="36"/>
-      <c r="AA51" s="36"/>
-      <c r="AB51" s="36"/>
+      <c r="Z51" s="5"/>
+      <c r="AA51" s="5"/>
+      <c r="AB51" s="5"/>
     </row>
     <row r="52" spans="1:28">
-      <c r="A52" s="34">
-        <v>7057</v>
-      </c>
-      <c r="B52" s="35" t="s">
-        <v>301</v>
+      <c r="A52" s="31">
+        <v>7059</v>
+      </c>
+      <c r="B52" s="32" t="s">
+        <v>312</v>
       </c>
       <c r="C52" s="5">
         <v>46266</v>
       </c>
-      <c r="D52" s="35" t="s">
+      <c r="D52" s="32" t="s">
         <v>302</v>
       </c>
-      <c r="E52" s="35" t="s">
+      <c r="E52" s="32" t="s">
         <v>303</v>
       </c>
-      <c r="F52" s="35" t="s">
+      <c r="F52" s="32" t="s">
         <v>304</v>
       </c>
-      <c r="G52" s="35" t="s">
+      <c r="G52" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="H52" s="35" t="s">
+      <c r="H52" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="I52" s="35" t="s">
-        <v>305</v>
-      </c>
-      <c r="J52" s="35" t="s">
+      <c r="I52" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="J52" s="32" t="s">
         <v>306</v>
       </c>
-      <c r="K52" s="35" t="s">
+      <c r="K52" s="32" t="s">
         <v>307</v>
       </c>
-      <c r="L52" s="35" t="s">
+      <c r="L52" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="M52" s="35" t="s">
-        <v>308</v>
-      </c>
-      <c r="O52" t="s">
-        <v>38</v>
-      </c>
-      <c r="T52" s="52" t="s">
+      <c r="M52" s="32" t="s">
+        <v>311</v>
+      </c>
+      <c r="N52" s="46"/>
+      <c r="O52" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="P52" s="46"/>
+      <c r="Q52" s="48"/>
+      <c r="R52" s="46"/>
+      <c r="S52" s="48"/>
+      <c r="T52" s="48" t="s">
         <v>38</v>
       </c>
       <c r="U52" s="7"/>
       <c r="V52" s="7"/>
       <c r="W52" s="7"/>
+      <c r="X52" s="48"/>
       <c r="Y52" s="7" t="s">
         <v>38</v>
       </c>
@@ -5303,54 +5433,60 @@
       <c r="AB52" s="14"/>
     </row>
     <row r="53" spans="1:28">
-      <c r="A53" s="32">
-        <v>7058</v>
-      </c>
-      <c r="B53" s="33" t="s">
-        <v>309</v>
+      <c r="A53" s="29">
+        <v>7060</v>
+      </c>
+      <c r="B53" s="30" t="s">
+        <v>314</v>
       </c>
       <c r="C53" s="5">
         <v>46266</v>
       </c>
-      <c r="D53" s="33" t="s">
+      <c r="D53" s="30" t="s">
         <v>302</v>
       </c>
-      <c r="E53" s="33" t="s">
+      <c r="E53" s="30" t="s">
         <v>303</v>
       </c>
-      <c r="F53" s="33" t="s">
+      <c r="F53" s="30" t="s">
         <v>304</v>
       </c>
-      <c r="G53" s="33" t="s">
+      <c r="G53" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="H53" s="33" t="s">
+      <c r="H53" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="I53" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="J53" s="33" t="s">
-        <v>306</v>
-      </c>
-      <c r="K53" s="33" t="s">
-        <v>307</v>
-      </c>
-      <c r="L53" s="33" t="s">
+      <c r="I53" s="30" t="s">
+        <v>315</v>
+      </c>
+      <c r="J53" s="30" t="s">
+        <v>316</v>
+      </c>
+      <c r="K53" s="30" t="s">
+        <v>317</v>
+      </c>
+      <c r="L53" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="M53" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="O53" t="s">
-        <v>38</v>
-      </c>
-      <c r="T53" s="52" t="s">
+      <c r="M53" s="30" t="s">
+        <v>318</v>
+      </c>
+      <c r="N53" s="46"/>
+      <c r="O53" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="P53" s="46"/>
+      <c r="Q53" s="48"/>
+      <c r="R53" s="46"/>
+      <c r="S53" s="48"/>
+      <c r="T53" s="48" t="s">
         <v>38</v>
       </c>
       <c r="U53" s="5"/>
       <c r="V53" s="5"/>
       <c r="W53" s="5"/>
+      <c r="X53" s="48"/>
       <c r="Y53" s="7" t="s">
         <v>38</v>
       </c>
@@ -5359,54 +5495,60 @@
       <c r="AB53" s="5"/>
     </row>
     <row r="54" spans="1:28">
-      <c r="A54" s="34">
-        <v>7059</v>
-      </c>
-      <c r="B54" s="35" t="s">
-        <v>312</v>
+      <c r="A54" s="31">
+        <v>7061</v>
+      </c>
+      <c r="B54" s="32" t="s">
+        <v>319</v>
       </c>
       <c r="C54" s="5">
         <v>46266</v>
       </c>
-      <c r="D54" s="35" t="s">
+      <c r="D54" s="32" t="s">
         <v>302</v>
       </c>
-      <c r="E54" s="35" t="s">
+      <c r="E54" s="32" t="s">
         <v>303</v>
       </c>
-      <c r="F54" s="35" t="s">
+      <c r="F54" s="32" t="s">
         <v>304</v>
       </c>
-      <c r="G54" s="35" t="s">
+      <c r="G54" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="H54" s="35" t="s">
+      <c r="H54" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="I54" s="35" t="s">
-        <v>313</v>
-      </c>
-      <c r="J54" s="35" t="s">
-        <v>306</v>
-      </c>
-      <c r="K54" s="35" t="s">
-        <v>307</v>
-      </c>
-      <c r="L54" s="35" t="s">
+      <c r="I54" s="32" t="s">
+        <v>320</v>
+      </c>
+      <c r="J54" s="32" t="s">
+        <v>316</v>
+      </c>
+      <c r="K54" s="32" t="s">
+        <v>317</v>
+      </c>
+      <c r="L54" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="M54" s="35" t="s">
-        <v>311</v>
-      </c>
-      <c r="O54" t="s">
-        <v>38</v>
-      </c>
-      <c r="T54" s="52" t="s">
+      <c r="M54" s="32" t="s">
+        <v>318</v>
+      </c>
+      <c r="N54" s="46"/>
+      <c r="O54" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="P54" s="46"/>
+      <c r="Q54" s="48"/>
+      <c r="R54" s="46"/>
+      <c r="S54" s="48"/>
+      <c r="T54" s="48" t="s">
         <v>38</v>
       </c>
       <c r="U54" s="7"/>
       <c r="V54" s="7"/>
       <c r="W54" s="7"/>
+      <c r="X54" s="48"/>
       <c r="Y54" s="7" t="s">
         <v>38</v>
       </c>
@@ -5415,54 +5557,60 @@
       <c r="AB54" s="14"/>
     </row>
     <row r="55" spans="1:28">
-      <c r="A55" s="32">
-        <v>7060</v>
-      </c>
-      <c r="B55" s="33" t="s">
-        <v>314</v>
+      <c r="A55" s="29">
+        <v>7062</v>
+      </c>
+      <c r="B55" s="30" t="s">
+        <v>321</v>
       </c>
       <c r="C55" s="5">
         <v>46266</v>
       </c>
-      <c r="D55" s="33" t="s">
+      <c r="D55" s="30" t="s">
         <v>302</v>
       </c>
-      <c r="E55" s="33" t="s">
+      <c r="E55" s="30" t="s">
         <v>303</v>
       </c>
-      <c r="F55" s="33" t="s">
+      <c r="F55" s="30" t="s">
         <v>304</v>
       </c>
-      <c r="G55" s="33" t="s">
+      <c r="G55" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="H55" s="33" t="s">
+      <c r="H55" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="I55" s="33" t="s">
-        <v>315</v>
-      </c>
-      <c r="J55" s="33" t="s">
-        <v>316</v>
-      </c>
-      <c r="K55" s="33" t="s">
-        <v>317</v>
-      </c>
-      <c r="L55" s="33" t="s">
+      <c r="I55" s="30" t="s">
+        <v>322</v>
+      </c>
+      <c r="J55" s="30" t="s">
+        <v>306</v>
+      </c>
+      <c r="K55" s="30" t="s">
+        <v>323</v>
+      </c>
+      <c r="L55" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="M55" s="33" t="s">
-        <v>318</v>
-      </c>
-      <c r="O55" t="s">
-        <v>38</v>
-      </c>
-      <c r="T55" s="52" t="s">
+      <c r="M55" s="30" t="s">
+        <v>324</v>
+      </c>
+      <c r="N55" s="46"/>
+      <c r="O55" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="P55" s="46"/>
+      <c r="Q55" s="48"/>
+      <c r="R55" s="46"/>
+      <c r="S55" s="48"/>
+      <c r="T55" s="48" t="s">
         <v>38</v>
       </c>
       <c r="U55" s="5"/>
       <c r="V55" s="5"/>
       <c r="W55" s="5"/>
+      <c r="X55" s="48"/>
       <c r="Y55" s="7" t="s">
         <v>38</v>
       </c>
@@ -5471,54 +5619,60 @@
       <c r="AB55" s="5"/>
     </row>
     <row r="56" spans="1:28">
-      <c r="A56" s="34">
-        <v>7061</v>
-      </c>
-      <c r="B56" s="35" t="s">
-        <v>319</v>
+      <c r="A56" s="31">
+        <v>7063</v>
+      </c>
+      <c r="B56" s="32" t="s">
+        <v>325</v>
       </c>
       <c r="C56" s="5">
         <v>46266</v>
       </c>
-      <c r="D56" s="35" t="s">
+      <c r="D56" s="32" t="s">
         <v>302</v>
       </c>
-      <c r="E56" s="35" t="s">
+      <c r="E56" s="32" t="s">
         <v>303</v>
       </c>
-      <c r="F56" s="35" t="s">
+      <c r="F56" s="32" t="s">
         <v>304</v>
       </c>
-      <c r="G56" s="35" t="s">
+      <c r="G56" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="H56" s="35" t="s">
+      <c r="H56" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="I56" s="35" t="s">
-        <v>320</v>
-      </c>
-      <c r="J56" s="35" t="s">
-        <v>316</v>
-      </c>
-      <c r="K56" s="35" t="s">
-        <v>317</v>
-      </c>
-      <c r="L56" s="35" t="s">
+      <c r="I56" s="32" t="s">
+        <v>326</v>
+      </c>
+      <c r="J56" s="32" t="s">
+        <v>306</v>
+      </c>
+      <c r="K56" s="32" t="s">
+        <v>323</v>
+      </c>
+      <c r="L56" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="M56" s="35" t="s">
-        <v>318</v>
-      </c>
-      <c r="O56" t="s">
-        <v>38</v>
-      </c>
-      <c r="T56" s="52" t="s">
+      <c r="M56" s="32" t="s">
+        <v>327</v>
+      </c>
+      <c r="N56" s="46"/>
+      <c r="O56" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="P56" s="46"/>
+      <c r="Q56" s="48"/>
+      <c r="R56" s="46"/>
+      <c r="S56" s="48"/>
+      <c r="T56" s="48" t="s">
         <v>38</v>
       </c>
       <c r="U56" s="7"/>
       <c r="V56" s="7"/>
       <c r="W56" s="7"/>
+      <c r="X56" s="48"/>
       <c r="Y56" s="7" t="s">
         <v>38</v>
       </c>
@@ -5527,172 +5681,112 @@
       <c r="AB56" s="14"/>
     </row>
     <row r="57" spans="1:28">
-      <c r="A57" s="32">
-        <v>7062</v>
-      </c>
-      <c r="B57" s="33" t="s">
-        <v>321</v>
+      <c r="A57" s="31">
+        <v>7064</v>
+      </c>
+      <c r="B57" s="32" t="s">
+        <v>328</v>
       </c>
       <c r="C57" s="5">
         <v>46266</v>
       </c>
-      <c r="D57" s="33" t="s">
-        <v>302</v>
-      </c>
-      <c r="E57" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="F57" s="33" t="s">
-        <v>304</v>
-      </c>
-      <c r="G57" s="33" t="s">
+      <c r="D57" s="32" t="s">
+        <v>329</v>
+      </c>
+      <c r="E57" s="32" t="s">
+        <v>142</v>
+      </c>
+      <c r="F57" s="32" t="s">
+        <v>267</v>
+      </c>
+      <c r="G57" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="H57" s="33" t="s">
+      <c r="H57" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="I57" s="33" t="s">
-        <v>322</v>
-      </c>
-      <c r="J57" s="33" t="s">
-        <v>306</v>
-      </c>
-      <c r="K57" s="33" t="s">
-        <v>323</v>
-      </c>
-      <c r="L57" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="M57" s="33" t="s">
-        <v>324</v>
-      </c>
-      <c r="O57" t="s">
-        <v>38</v>
-      </c>
-      <c r="T57" s="52" t="s">
-        <v>38</v>
-      </c>
-      <c r="U57" s="5"/>
-      <c r="V57" s="5"/>
-      <c r="W57" s="5"/>
+      <c r="I57" s="32" t="s">
+        <v>330</v>
+      </c>
+      <c r="J57" s="32" t="s">
+        <v>331</v>
+      </c>
+      <c r="K57" s="32" t="s">
+        <v>332</v>
+      </c>
+      <c r="L57" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="M57" s="32" t="s">
+        <v>333</v>
+      </c>
+      <c r="N57" s="46"/>
+      <c r="O57" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="P57" s="46"/>
+      <c r="Q57" s="48"/>
+      <c r="R57" s="46"/>
+      <c r="S57" s="48"/>
+      <c r="T57" s="48" t="s">
+        <v>38</v>
+      </c>
+      <c r="U57" s="7"/>
+      <c r="V57" s="7"/>
+      <c r="W57" s="7"/>
+      <c r="X57" s="48"/>
       <c r="Y57" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="Z57" s="5"/>
-      <c r="AA57" s="5"/>
-      <c r="AB57" s="5"/>
+      <c r="Z57" s="7"/>
+      <c r="AA57" s="7"/>
+      <c r="AB57" s="7"/>
     </row>
     <row r="58" spans="1:28">
-      <c r="A58" s="34">
-        <v>7063</v>
-      </c>
-      <c r="B58" s="35" t="s">
-        <v>325</v>
-      </c>
-      <c r="C58" s="5">
-        <v>46266</v>
-      </c>
-      <c r="D58" s="35" t="s">
-        <v>302</v>
-      </c>
-      <c r="E58" s="35" t="s">
-        <v>303</v>
-      </c>
-      <c r="F58" s="35" t="s">
-        <v>304</v>
-      </c>
-      <c r="G58" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="H58" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="I58" s="35" t="s">
-        <v>326</v>
-      </c>
-      <c r="J58" s="35" t="s">
-        <v>306</v>
-      </c>
-      <c r="K58" s="35" t="s">
-        <v>323</v>
-      </c>
-      <c r="L58" s="35" t="s">
-        <v>36</v>
-      </c>
-      <c r="M58" s="35" t="s">
-        <v>327</v>
-      </c>
-      <c r="O58" t="s">
-        <v>38</v>
-      </c>
-      <c r="T58" s="52" t="s">
-        <v>38</v>
-      </c>
+      <c r="A58" s="31"/>
+      <c r="B58" s="32"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="32"/>
+      <c r="E58" s="32"/>
+      <c r="F58" s="32"/>
+      <c r="G58" s="32"/>
+      <c r="H58" s="32"/>
+      <c r="I58" s="32"/>
+      <c r="J58" s="32"/>
+      <c r="K58" s="32"/>
+      <c r="L58" s="32"/>
+      <c r="M58" s="32"/>
+      <c r="T58" s="48"/>
       <c r="U58" s="7"/>
       <c r="V58" s="7"/>
       <c r="W58" s="7"/>
-      <c r="Y58" s="7" t="s">
-        <v>38</v>
-      </c>
+      <c r="Y58" s="7"/>
       <c r="Z58" s="14"/>
       <c r="AA58" s="14"/>
       <c r="AB58" s="14"/>
     </row>
     <row r="59" spans="1:28">
-      <c r="A59" s="34">
-        <v>7064</v>
-      </c>
-      <c r="B59" s="35" t="s">
-        <v>328</v>
-      </c>
-      <c r="C59" s="5">
-        <v>46266</v>
-      </c>
-      <c r="D59" s="35" t="s">
-        <v>329</v>
-      </c>
-      <c r="E59" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="F59" s="35" t="s">
-        <v>267</v>
-      </c>
-      <c r="G59" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="H59" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="I59" s="35" t="s">
-        <v>330</v>
-      </c>
-      <c r="J59" s="35" t="s">
-        <v>331</v>
-      </c>
-      <c r="K59" s="35" t="s">
-        <v>332</v>
-      </c>
-      <c r="L59" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="M59" s="35" t="s">
-        <v>333</v>
-      </c>
-      <c r="O59" t="s">
-        <v>38</v>
-      </c>
-      <c r="T59" s="52" t="s">
-        <v>38</v>
-      </c>
-      <c r="U59" s="7"/>
-      <c r="V59" s="7"/>
-      <c r="W59" s="7"/>
-      <c r="Y59" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="Z59" s="7"/>
-      <c r="AA59" s="7"/>
-      <c r="AB59" s="7"/>
+      <c r="A59" s="31"/>
+      <c r="B59" s="32"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="32"/>
+      <c r="E59" s="32"/>
+      <c r="F59" s="32"/>
+      <c r="G59" s="32"/>
+      <c r="H59" s="32"/>
+      <c r="I59" s="32"/>
+      <c r="J59" s="32"/>
+      <c r="K59" s="32"/>
+      <c r="L59" s="32"/>
+      <c r="M59" s="32"/>
+      <c r="T59" s="48"/>
+      <c r="U59" s="5"/>
+      <c r="V59" s="5"/>
+      <c r="W59" s="5"/>
+      <c r="Y59" s="7"/>
+      <c r="Z59" s="5"/>
+      <c r="AA59" s="5"/>
+      <c r="AB59" s="5"/>
     </row>
   </sheetData>
   <dataValidations count="8">

--- a/data/base/base implantação.xlsx
+++ b/data/base/base implantação.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/warruda_mgcontecnica_com_br/Documents/Documentos/python/Portal-implantacao-tmp/data/base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="758" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33FC824F-6F27-4656-BD10-F34F4B63516C}"/>
+  <xr:revisionPtr revIDLastSave="768" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F87492B7-3545-4B05-9AE1-F20D73D343FD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="335">
   <si>
     <t>ID</t>
   </si>
@@ -194,6 +194,9 @@
     <t>JGTEC AR CONDICIONADO LTDA</t>
   </si>
   <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
     <t>JGTEC</t>
   </si>
   <si>
@@ -239,8 +242,7 @@
     <t>Reynaldo Santos;</t>
   </si>
   <si>
-    <t xml:space="preserve">RUA DOS JUNQUILHOS, Num.: 153 Comple.: LOTE 26 - QUADRA 08 - SALA 01, Bairro: PARQUE OESTE INDUSTRIAL /
- </t>
+    <t>RUA DOS JUNQUILHOS, Num.: 153 Comple.: LOTE 26 - QUADRA 08 - SALA 01, Bairro: PARQUE OESTE INDUSTRIAL /</t>
   </si>
   <si>
     <t>brasildistribuidoradepecas@gmail.com;</t>
@@ -1285,7 +1287,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1341,6 +1343,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -2251,11 +2259,11 @@
       <c r="B4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="7">
-        <v>46204</v>
+      <c r="C4" s="53" t="s">
+        <v>52</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>30</v>
@@ -2270,19 +2278,19 @@
         <v>33</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L4" s="7" t="s">
         <v>36</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N4" s="8">
         <v>46255</v>
@@ -2317,13 +2325,13 @@
         <v>6924</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" s="5">
+        <v>58</v>
+      </c>
+      <c r="C5" s="54">
         <v>46204</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>30</v>
@@ -2338,19 +2346,19 @@
         <v>33</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L5" s="5" t="s">
         <v>36</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N5" s="9">
         <v>46255</v>
@@ -2380,45 +2388,45 @@
       <c r="AA5" s="5"/>
       <c r="AB5" s="5"/>
     </row>
-    <row r="6" spans="1:28" ht="30.75">
+    <row r="6" spans="1:28">
       <c r="A6" s="12">
         <v>6945</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C6" s="7">
         <v>46174</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>33</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>36</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="N6" s="8">
         <v>46219</v>
@@ -2453,13 +2461,13 @@
         <v>6947</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" s="7">
         <v>46266</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>30</v>
@@ -2468,25 +2476,25 @@
         <v>31</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L7" s="7" t="s">
         <v>36</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N7" s="8">
         <v>46259</v>
@@ -2521,40 +2529,40 @@
         <v>6949</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C8" s="5">
         <v>46204</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>31</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L8" s="5" t="s">
         <v>36</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N8" s="9">
         <v>46205</v>
@@ -2589,40 +2597,40 @@
         <v>6962</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C9" s="5">
         <v>46174</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>31</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L9" s="5" t="s">
         <v>36</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N9" s="9">
         <v>46232</v>
@@ -2655,40 +2663,40 @@
         <v>6963</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C10" s="7">
         <v>46174</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L10" s="7" t="s">
         <v>36</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N10" s="8">
         <v>46232</v>
@@ -2721,40 +2729,40 @@
         <v>6964</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C11" s="5">
         <v>46235</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L11" s="5" t="s">
         <v>48</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N11" s="9">
         <v>46252</v>
@@ -2789,40 +2797,40 @@
         <v>6966</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C12" s="5">
         <v>46235</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>31</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>33</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L12" s="5" t="s">
         <v>48</v>
       </c>
       <c r="M12" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N12" s="9">
         <v>46245</v>
@@ -2857,40 +2865,40 @@
         <v>6967</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C13" s="7">
         <v>46235</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>33</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L13" s="7" t="s">
         <v>48</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N13" s="8">
         <v>46245</v>
@@ -2925,40 +2933,40 @@
         <v>6974</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C14" s="7">
         <v>46204</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L14" s="7" t="s">
         <v>48</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N14" s="8">
         <v>46241</v>
@@ -2991,13 +2999,13 @@
         <v>6976</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C15" s="5">
         <v>46235</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>30</v>
@@ -3006,25 +3014,25 @@
         <v>31</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>33</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L15" s="5" t="s">
         <v>36</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N15" s="9">
         <v>46260</v>
@@ -3059,13 +3067,13 @@
         <v>6977</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C16" s="7">
         <v>46235</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>30</v>
@@ -3074,7 +3082,7 @@
         <v>31</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>33</v>
@@ -3086,7 +3094,7 @@
         <v>36</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N16" s="9">
         <v>46260</v>
@@ -3121,13 +3129,13 @@
         <v>6978</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C17" s="5">
         <v>46266</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>30</v>
@@ -3136,25 +3144,25 @@
         <v>31</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>33</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L17" s="5" t="s">
         <v>36</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N17" s="5"/>
       <c r="O17" s="5" t="s">
@@ -3185,40 +3193,40 @@
         <v>6981</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C18" s="5">
         <v>46235</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>31</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L18" s="5" t="s">
         <v>48</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N18" s="9">
         <v>46253</v>
@@ -3253,40 +3261,40 @@
         <v>6984</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C19" s="7">
         <v>46235</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L19" s="7" t="s">
         <v>48</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N19" s="20"/>
       <c r="O19" s="21"/>
@@ -3309,40 +3317,40 @@
         <v>6989</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C20" s="5">
         <v>46220</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>33</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L20" s="5" t="s">
         <v>36</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N20" s="5"/>
       <c r="O20" s="5" t="s">
@@ -3371,40 +3379,40 @@
         <v>6990</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C21" s="7">
         <v>46235</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H21" s="7" t="s">
         <v>33</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L21" s="7" t="s">
         <v>48</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N21" s="20"/>
       <c r="O21" s="21"/>
@@ -3427,40 +3435,40 @@
         <v>6991</v>
       </c>
       <c r="B22" s="42" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C22" s="42">
         <v>46235</v>
       </c>
       <c r="D22" s="42" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E22" s="42" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F22" s="42" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G22" s="42" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H22" s="42" t="s">
         <v>33</v>
       </c>
       <c r="I22" s="42" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J22" s="42" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K22" s="42" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L22" s="42" t="s">
         <v>48</v>
       </c>
       <c r="M22" s="42" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N22" s="20"/>
       <c r="O22" s="21"/>
@@ -3483,40 +3491,40 @@
         <v>6992</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C23" s="7">
         <v>46266</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L23" s="7" t="s">
         <v>48</v>
       </c>
       <c r="M23" s="7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N23" s="28"/>
       <c r="O23" s="7" t="s">
@@ -3547,40 +3555,40 @@
         <v>6993</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C24" s="5">
         <v>46266</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>33</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L24" s="5" t="s">
         <v>48</v>
       </c>
       <c r="M24" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N24" s="43"/>
       <c r="O24" s="5" t="s">
@@ -3611,13 +3619,13 @@
         <v>6995</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C25" s="7">
         <v>46266</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>30</v>
@@ -3626,25 +3634,25 @@
         <v>42</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H25" s="7" t="s">
         <v>33</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L25" s="7" t="s">
         <v>36</v>
       </c>
       <c r="M25" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N25" s="44">
         <v>46252</v>
@@ -3679,40 +3687,40 @@
         <v>7005</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C26" s="5">
         <v>46266</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>33</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L26" s="5" t="s">
         <v>36</v>
       </c>
       <c r="M26" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N26" s="43"/>
       <c r="O26" s="5" t="s">
@@ -3741,40 +3749,40 @@
         <v>7006</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C27" s="7">
         <v>46266</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H27" s="7" t="s">
         <v>33</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L27" s="7" t="s">
         <v>36</v>
       </c>
       <c r="M27" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N27" s="28"/>
       <c r="O27" s="7" t="s">
@@ -3803,40 +3811,40 @@
         <v>7007</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C28" s="5">
         <v>46266</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H28" s="5" t="s">
         <v>44</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L28" s="5" t="s">
         <v>48</v>
       </c>
       <c r="M28" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N28" s="45">
         <v>46269</v>
@@ -3867,40 +3875,40 @@
         <v>7012</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C29" s="7">
         <v>46235</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K29" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L29" s="7" t="s">
         <v>48</v>
       </c>
       <c r="M29" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N29" s="44">
         <v>46255</v>
@@ -3933,40 +3941,40 @@
         <v>7012</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C30" s="5">
         <v>46235</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L30" s="5" t="s">
         <v>48</v>
       </c>
       <c r="M30" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N30" s="44">
         <v>46255</v>
@@ -3999,40 +4007,40 @@
         <v>7014</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C31" s="7">
         <v>46235</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H31" s="7" t="s">
         <v>44</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K31" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L31" s="7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M31" s="7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N31" s="18">
         <v>46255</v>
@@ -4065,40 +4073,40 @@
         <v>7015</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C32" s="5">
         <v>46235</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H32" s="5" t="s">
         <v>44</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L32" s="5" t="s">
         <v>48</v>
       </c>
       <c r="M32" s="5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N32" s="18">
         <v>46255</v>
@@ -4131,40 +4139,40 @@
         <v>7016</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C33" s="7">
         <v>46235</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H33" s="7" t="s">
         <v>44</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L33" s="7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M33" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N33" s="8">
         <v>46255</v>
@@ -4197,40 +4205,40 @@
         <v>7017</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C34" s="5">
         <v>46235</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H34" s="5" t="s">
         <v>44</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L34" s="5" t="s">
         <v>48</v>
       </c>
       <c r="M34" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N34" s="8">
         <v>46255</v>
@@ -4263,40 +4271,40 @@
         <v>7018</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C35" s="7">
         <v>46235</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H35" s="7" t="s">
         <v>44</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K35" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L35" s="7" t="s">
         <v>48</v>
       </c>
       <c r="M35" s="7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N35" s="8">
         <v>46255</v>
@@ -4329,40 +4337,40 @@
         <v>7019</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C36" s="5">
         <v>46235</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H36" s="5" t="s">
         <v>44</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L36" s="5" t="s">
         <v>48</v>
       </c>
       <c r="M36" s="5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N36" s="8">
         <v>46255</v>
@@ -4395,40 +4403,40 @@
         <v>7020</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C37" s="14">
         <v>46235</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G37" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H37" s="14" t="s">
         <v>44</v>
       </c>
       <c r="I37" s="14" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="J37" s="14" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K37" s="14" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L37" s="14" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M37" s="14" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N37" s="47">
         <v>46255</v>
@@ -4461,40 +4469,40 @@
         <v>7021</v>
       </c>
       <c r="B38" s="39" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C38" s="39">
         <v>46235</v>
       </c>
       <c r="D38" s="39" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E38" s="39" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F38" s="39" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G38" s="39" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H38" s="39" t="s">
         <v>44</v>
       </c>
       <c r="I38" s="39" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J38" s="39" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K38" s="39" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L38" s="39" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M38" s="43" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N38" s="47">
         <v>46255</v>
@@ -4527,40 +4535,40 @@
         <v>7036</v>
       </c>
       <c r="B39" s="41" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C39" s="41">
         <v>46266</v>
       </c>
       <c r="D39" s="41" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E39" s="41" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F39" s="41" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G39" s="41" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H39" s="41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I39" s="41" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J39" s="41" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K39" s="41" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L39" s="41" t="s">
         <v>48</v>
       </c>
       <c r="M39" s="41" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N39" s="45">
         <v>46261</v>
@@ -4569,13 +4577,13 @@
         <v>50</v>
       </c>
       <c r="P39" s="43" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q39" s="43" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R39" s="43" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="S39" s="45">
         <v>46261</v>
@@ -4584,10 +4592,10 @@
         <v>50</v>
       </c>
       <c r="U39" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="V39" s="22" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="W39" s="5"/>
       <c r="X39" s="43"/>
@@ -4595,10 +4603,10 @@
         <v>38</v>
       </c>
       <c r="Z39" s="19" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AA39" s="23" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AB39" s="19"/>
     </row>
@@ -4607,40 +4615,40 @@
         <v>7037</v>
       </c>
       <c r="B40" s="25" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C40" s="25">
         <v>46266</v>
       </c>
       <c r="D40" s="25" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E40" s="25" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F40" s="25" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G40" s="25" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H40" s="25" t="s">
         <v>33</v>
       </c>
       <c r="I40" s="25" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J40" s="25" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K40" s="25" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L40" s="25" t="s">
         <v>48</v>
       </c>
       <c r="M40" s="25" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N40" s="45">
         <v>46261</v>
@@ -4649,13 +4657,13 @@
         <v>50</v>
       </c>
       <c r="P40" s="28" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q40" s="28" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R40" s="51" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="S40" s="45">
         <v>46261</v>
@@ -4664,10 +4672,10 @@
         <v>50</v>
       </c>
       <c r="U40" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="V40" s="22" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="W40" s="7"/>
       <c r="X40" s="28"/>
@@ -4675,10 +4683,10 @@
         <v>38</v>
       </c>
       <c r="Z40" s="5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AA40" s="50" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AB40" s="7"/>
     </row>
@@ -4687,40 +4695,40 @@
         <v>7046</v>
       </c>
       <c r="B41" s="25" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C41" s="25">
         <v>46266</v>
       </c>
       <c r="D41" s="25" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E41" s="25" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F41" s="25" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G41" s="25" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H41" s="25" t="s">
         <v>33</v>
       </c>
       <c r="I41" s="25" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J41" s="25" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K41" s="25" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L41" s="25" t="s">
         <v>48</v>
       </c>
       <c r="M41" s="25" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N41" s="46">
         <v>46267</v>
@@ -4755,40 +4763,40 @@
         <v>7048</v>
       </c>
       <c r="B42" s="25" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C42" s="5">
         <v>46266</v>
       </c>
       <c r="D42" s="25" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E42" s="25" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F42" s="25" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G42" s="25" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H42" s="25" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I42" s="25" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J42" s="25" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K42" s="25" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L42" s="25" t="s">
         <v>36</v>
       </c>
       <c r="M42" s="25" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N42" s="46"/>
       <c r="O42" s="48" t="s">
@@ -4817,40 +4825,40 @@
         <v>7049</v>
       </c>
       <c r="B43" s="40" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C43" s="5">
         <v>46266</v>
       </c>
       <c r="D43" s="40" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E43" s="40" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F43" s="40" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G43" s="40" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H43" s="40" t="s">
         <v>33</v>
       </c>
       <c r="I43" s="40" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J43" s="40" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K43" s="40" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L43" s="40" t="s">
         <v>36</v>
       </c>
       <c r="M43" s="52" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N43" s="46"/>
       <c r="O43" s="48" t="s">
@@ -4879,40 +4887,40 @@
         <v>7050</v>
       </c>
       <c r="B44" s="27" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C44" s="5">
         <v>46266</v>
       </c>
       <c r="D44" s="27" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E44" s="27" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F44" s="27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G44" s="27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H44" s="27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I44" s="27" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J44" s="27" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K44" s="27" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L44" s="27" t="s">
         <v>36</v>
       </c>
       <c r="M44" s="27" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N44" s="46"/>
       <c r="O44" s="48" t="s">
@@ -4941,40 +4949,40 @@
         <v>7052</v>
       </c>
       <c r="B45" s="32" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C45" s="5">
         <v>46266</v>
       </c>
       <c r="D45" s="32" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E45" s="32" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F45" s="32" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G45" s="32" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H45" s="32" t="s">
         <v>33</v>
       </c>
       <c r="I45" s="32" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J45" s="32" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K45" s="32" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L45" s="32" t="s">
         <v>36</v>
       </c>
       <c r="M45" s="32" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N45" s="46"/>
       <c r="O45" s="48" t="s">
@@ -5003,40 +5011,40 @@
         <v>7053</v>
       </c>
       <c r="B46" s="30" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C46" s="5">
         <v>46266</v>
       </c>
       <c r="D46" s="30" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E46" s="30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F46" s="30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G46" s="30" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H46" s="30" t="s">
         <v>33</v>
       </c>
       <c r="I46" s="30" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J46" s="30" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K46" s="30" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L46" s="30" t="s">
         <v>36</v>
       </c>
       <c r="M46" s="30" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N46" s="46"/>
       <c r="O46" s="48" t="s">
@@ -5065,40 +5073,40 @@
         <v>7054</v>
       </c>
       <c r="B47" s="32" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C47" s="5">
         <v>46266</v>
       </c>
       <c r="D47" s="32" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E47" s="32" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F47" s="32" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G47" s="32" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H47" s="32" t="s">
         <v>33</v>
       </c>
       <c r="I47" s="32" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J47" s="32" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K47" s="32" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L47" s="32" t="s">
         <v>36</v>
       </c>
       <c r="M47" s="32" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N47" s="46"/>
       <c r="O47" s="48" t="s">
@@ -5127,40 +5135,40 @@
         <v>7055</v>
       </c>
       <c r="B48" s="30" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C48" s="5">
         <v>46266</v>
       </c>
       <c r="D48" s="30" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E48" s="30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F48" s="30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G48" s="30" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H48" s="30" t="s">
         <v>33</v>
       </c>
       <c r="I48" s="30" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J48" s="30" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K48" s="30" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L48" s="30" t="s">
         <v>36</v>
       </c>
       <c r="M48" s="30" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N48" s="46"/>
       <c r="O48" s="48" t="s">
@@ -5189,40 +5197,40 @@
         <v>7056</v>
       </c>
       <c r="B49" s="32" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C49" s="5">
         <v>46266</v>
       </c>
       <c r="D49" s="32" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E49" s="32" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F49" s="32" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G49" s="32" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H49" s="32" t="s">
         <v>33</v>
       </c>
       <c r="I49" s="32" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J49" s="32" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K49" s="32" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L49" s="32" t="s">
         <v>36</v>
       </c>
       <c r="M49" s="32" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N49" s="46"/>
       <c r="O49" s="48" t="s">
@@ -5251,40 +5259,40 @@
         <v>7057</v>
       </c>
       <c r="B50" s="32" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C50" s="5">
         <v>46266</v>
       </c>
       <c r="D50" s="32" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E50" s="32" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F50" s="32" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G50" s="32" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H50" s="32" t="s">
         <v>33</v>
       </c>
       <c r="I50" s="32" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J50" s="32" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K50" s="32" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L50" s="32" t="s">
         <v>36</v>
       </c>
       <c r="M50" s="32" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N50" s="46"/>
       <c r="O50" s="48" t="s">
@@ -5313,40 +5321,40 @@
         <v>7058</v>
       </c>
       <c r="B51" s="30" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C51" s="5">
         <v>46266</v>
       </c>
       <c r="D51" s="30" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E51" s="30" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F51" s="30" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G51" s="30" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H51" s="30" t="s">
         <v>33</v>
       </c>
       <c r="I51" s="30" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J51" s="30" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K51" s="30" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L51" s="30" t="s">
         <v>36</v>
       </c>
       <c r="M51" s="30" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N51" s="46"/>
       <c r="O51" s="48" t="s">
@@ -5375,40 +5383,40 @@
         <v>7059</v>
       </c>
       <c r="B52" s="32" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C52" s="5">
         <v>46266</v>
       </c>
       <c r="D52" s="32" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E52" s="32" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F52" s="32" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G52" s="32" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H52" s="32" t="s">
         <v>33</v>
       </c>
       <c r="I52" s="32" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J52" s="32" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K52" s="32" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L52" s="32" t="s">
         <v>36</v>
       </c>
       <c r="M52" s="32" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N52" s="46"/>
       <c r="O52" s="48" t="s">
@@ -5437,40 +5445,40 @@
         <v>7060</v>
       </c>
       <c r="B53" s="30" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C53" s="5">
         <v>46266</v>
       </c>
       <c r="D53" s="30" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E53" s="30" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F53" s="30" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G53" s="30" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H53" s="30" t="s">
         <v>33</v>
       </c>
       <c r="I53" s="30" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J53" s="30" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K53" s="30" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L53" s="30" t="s">
         <v>36</v>
       </c>
       <c r="M53" s="30" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N53" s="46"/>
       <c r="O53" s="48" t="s">
@@ -5499,40 +5507,40 @@
         <v>7061</v>
       </c>
       <c r="B54" s="32" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C54" s="5">
         <v>46266</v>
       </c>
       <c r="D54" s="32" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E54" s="32" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F54" s="32" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G54" s="32" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H54" s="32" t="s">
         <v>33</v>
       </c>
       <c r="I54" s="32" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J54" s="32" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K54" s="32" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L54" s="32" t="s">
         <v>36</v>
       </c>
       <c r="M54" s="32" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N54" s="46"/>
       <c r="O54" s="48" t="s">
@@ -5561,40 +5569,40 @@
         <v>7062</v>
       </c>
       <c r="B55" s="30" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C55" s="5">
         <v>46266</v>
       </c>
       <c r="D55" s="30" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E55" s="30" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F55" s="30" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G55" s="30" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H55" s="30" t="s">
         <v>33</v>
       </c>
       <c r="I55" s="30" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J55" s="30" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K55" s="30" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L55" s="30" t="s">
         <v>36</v>
       </c>
       <c r="M55" s="30" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N55" s="46"/>
       <c r="O55" s="48" t="s">
@@ -5623,40 +5631,40 @@
         <v>7063</v>
       </c>
       <c r="B56" s="32" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C56" s="5">
         <v>46266</v>
       </c>
       <c r="D56" s="32" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E56" s="32" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F56" s="32" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G56" s="32" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H56" s="32" t="s">
         <v>33</v>
       </c>
       <c r="I56" s="32" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J56" s="32" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K56" s="32" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L56" s="32" t="s">
         <v>36</v>
       </c>
       <c r="M56" s="32" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N56" s="46"/>
       <c r="O56" s="48" t="s">
@@ -5685,40 +5693,40 @@
         <v>7064</v>
       </c>
       <c r="B57" s="32" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C57" s="5">
         <v>46266</v>
       </c>
       <c r="D57" s="32" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E57" s="32" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F57" s="32" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G57" s="32" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H57" s="32" t="s">
         <v>33</v>
       </c>
       <c r="I57" s="32" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J57" s="32" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K57" s="32" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L57" s="32" t="s">
         <v>48</v>
       </c>
       <c r="M57" s="32" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N57" s="46"/>
       <c r="O57" s="48" t="s">

--- a/data/base/base implantação.xlsx
+++ b/data/base/base implantação.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30431"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/warruda_mgcontecnica_com_br/Documents/Documentos/python/Portal-implantacao-tmp/data/base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="814" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E9E3789-2455-4914-B387-A1EF2AB1FE81}"/>
+  <xr:revisionPtr revIDLastSave="817" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8121C6D9-33D7-4E41-90B9-5D5813A207D2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="334">
   <si>
     <t>ID</t>
   </si>
@@ -1564,7 +1564,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:AB59">
-  <autoFilter ref="A1:AB59" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <autoFilter ref="A1:AB59" xr:uid="{00000000-0009-0000-0100-000001000000}">
+    <filterColumn colId="11">
+      <filters>
+        <filter val="Varejo"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="28">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" totalsRowFunction="average"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="RazaoSocial" totalsRowFunction="average"/>
@@ -2035,7 +2041,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28">
+    <row r="2" spans="1:28" hidden="1">
       <c r="A2" s="4">
         <v>6812</v>
       </c>
@@ -2163,7 +2169,7 @@
       <c r="AA3" s="5"/>
       <c r="AB3" s="13"/>
     </row>
-    <row r="4" spans="1:28">
+    <row r="4" spans="1:28" hidden="1">
       <c r="A4">
         <v>6923</v>
       </c>
@@ -2231,7 +2237,7 @@
       <c r="AA4" s="5"/>
       <c r="AB4" s="5"/>
     </row>
-    <row r="5" spans="1:28">
+    <row r="5" spans="1:28" hidden="1">
       <c r="A5">
         <v>6924</v>
       </c>
@@ -2299,7 +2305,7 @@
       <c r="AA5" s="4"/>
       <c r="AB5" s="4"/>
     </row>
-    <row r="6" spans="1:28">
+    <row r="6" spans="1:28" hidden="1">
       <c r="A6">
         <v>6945</v>
       </c>
@@ -2367,7 +2373,7 @@
       <c r="AA6" s="5"/>
       <c r="AB6" s="5"/>
     </row>
-    <row r="7" spans="1:28">
+    <row r="7" spans="1:28" hidden="1">
       <c r="A7">
         <v>6947</v>
       </c>
@@ -2435,7 +2441,7 @@
       <c r="AA7" s="5"/>
       <c r="AB7" s="5"/>
     </row>
-    <row r="8" spans="1:28">
+    <row r="8" spans="1:28" hidden="1">
       <c r="A8">
         <v>6949</v>
       </c>
@@ -2503,7 +2509,7 @@
       <c r="AA8" s="4"/>
       <c r="AB8" s="4"/>
     </row>
-    <row r="9" spans="1:28">
+    <row r="9" spans="1:28" hidden="1">
       <c r="A9">
         <v>6962</v>
       </c>
@@ -2569,7 +2575,7 @@
       <c r="AA9" s="4"/>
       <c r="AB9" s="4"/>
     </row>
-    <row r="10" spans="1:28">
+    <row r="10" spans="1:28" hidden="1">
       <c r="A10">
         <v>6963</v>
       </c>
@@ -2905,7 +2911,7 @@
       <c r="AA14" s="5"/>
       <c r="AB14" s="5"/>
     </row>
-    <row r="15" spans="1:28">
+    <row r="15" spans="1:28" hidden="1">
       <c r="A15">
         <v>6976</v>
       </c>
@@ -2973,7 +2979,7 @@
       <c r="AA15" s="4"/>
       <c r="AB15" s="4"/>
     </row>
-    <row r="16" spans="1:28">
+    <row r="16" spans="1:28" hidden="1">
       <c r="A16">
         <v>6977</v>
       </c>
@@ -3035,7 +3041,7 @@
       <c r="AA16" s="5"/>
       <c r="AB16" s="5"/>
     </row>
-    <row r="17" spans="1:28">
+    <row r="17" spans="1:28" hidden="1">
       <c r="A17">
         <v>6978</v>
       </c>
@@ -3212,8 +3218,12 @@
       <c r="P19" s="16"/>
       <c r="Q19" s="17"/>
       <c r="R19" s="16"/>
-      <c r="S19" s="17"/>
-      <c r="T19" s="17"/>
+      <c r="S19" s="16">
+        <v>46268</v>
+      </c>
+      <c r="T19" s="17" t="s">
+        <v>50</v>
+      </c>
       <c r="U19" s="4"/>
       <c r="V19" s="4"/>
       <c r="W19" s="4"/>
@@ -3223,7 +3233,7 @@
       <c r="AA19" s="4"/>
       <c r="AB19" s="4"/>
     </row>
-    <row r="20" spans="1:28">
+    <row r="20" spans="1:28" hidden="1">
       <c r="A20">
         <v>6989</v>
       </c>
@@ -3537,7 +3547,7 @@
       <c r="AA24" s="4"/>
       <c r="AB24" s="4"/>
     </row>
-    <row r="25" spans="1:28">
+    <row r="25" spans="1:28" hidden="1">
       <c r="A25">
         <v>6995</v>
       </c>
@@ -3605,7 +3615,7 @@
       <c r="AA25" s="5"/>
       <c r="AB25" s="5"/>
     </row>
-    <row r="26" spans="1:28">
+    <row r="26" spans="1:28" hidden="1">
       <c r="A26">
         <v>7005</v>
       </c>
@@ -3667,7 +3677,7 @@
       <c r="AA26" s="4"/>
       <c r="AB26" s="4"/>
     </row>
-    <row r="27" spans="1:28">
+    <row r="27" spans="1:28" hidden="1">
       <c r="A27">
         <v>7006</v>
       </c>
@@ -3925,7 +3935,7 @@
       <c r="AA30" s="4"/>
       <c r="AB30" s="4"/>
     </row>
-    <row r="31" spans="1:28">
+    <row r="31" spans="1:28" hidden="1">
       <c r="A31">
         <v>7014</v>
       </c>
@@ -4057,7 +4067,7 @@
       <c r="AA32" s="4"/>
       <c r="AB32" s="4"/>
     </row>
-    <row r="33" spans="1:28">
+    <row r="33" spans="1:28" hidden="1">
       <c r="A33">
         <v>7016</v>
       </c>
@@ -4321,7 +4331,7 @@
       <c r="AA36" s="4"/>
       <c r="AB36" s="4"/>
     </row>
-    <row r="37" spans="1:28">
+    <row r="37" spans="1:28" hidden="1">
       <c r="A37">
         <v>7020</v>
       </c>
@@ -4387,7 +4397,7 @@
       <c r="AA37" s="10"/>
       <c r="AB37" s="10"/>
     </row>
-    <row r="38" spans="1:28">
+    <row r="38" spans="1:28" hidden="1">
       <c r="A38">
         <v>7021</v>
       </c>
@@ -4678,7 +4688,7 @@
       <c r="AA41" s="4"/>
       <c r="AB41" s="4"/>
     </row>
-    <row r="42" spans="1:28">
+    <row r="42" spans="1:28" hidden="1">
       <c r="A42">
         <v>7048</v>
       </c>
@@ -4734,7 +4744,7 @@
       <c r="AA42" s="10"/>
       <c r="AB42" s="10"/>
     </row>
-    <row r="43" spans="1:28">
+    <row r="43" spans="1:28" hidden="1">
       <c r="A43">
         <v>7049</v>
       </c>
@@ -4790,7 +4800,7 @@
       <c r="AA43" s="4"/>
       <c r="AB43" s="4"/>
     </row>
-    <row r="44" spans="1:28">
+    <row r="44" spans="1:28" hidden="1">
       <c r="A44">
         <v>7050</v>
       </c>
@@ -4846,7 +4856,7 @@
       <c r="AA44" s="15"/>
       <c r="AB44" s="15"/>
     </row>
-    <row r="45" spans="1:28">
+    <row r="45" spans="1:28" hidden="1">
       <c r="A45">
         <v>7052</v>
       </c>
@@ -4902,7 +4912,7 @@
       <c r="AA45" s="4"/>
       <c r="AB45" s="4"/>
     </row>
-    <row r="46" spans="1:28">
+    <row r="46" spans="1:28" hidden="1">
       <c r="A46">
         <v>7053</v>
       </c>
@@ -4958,7 +4968,7 @@
       <c r="AA46" s="10"/>
       <c r="AB46" s="10"/>
     </row>
-    <row r="47" spans="1:28">
+    <row r="47" spans="1:28" hidden="1">
       <c r="A47">
         <v>7054</v>
       </c>
@@ -5014,7 +5024,7 @@
       <c r="AA47" s="4"/>
       <c r="AB47" s="4"/>
     </row>
-    <row r="48" spans="1:28">
+    <row r="48" spans="1:28" hidden="1">
       <c r="A48">
         <v>7055</v>
       </c>
@@ -5070,7 +5080,7 @@
       <c r="AA48" s="10"/>
       <c r="AB48" s="10"/>
     </row>
-    <row r="49" spans="1:28">
+    <row r="49" spans="1:28" hidden="1">
       <c r="A49">
         <v>7056</v>
       </c>
@@ -5126,7 +5136,7 @@
       <c r="AA49" s="5"/>
       <c r="AB49" s="5"/>
     </row>
-    <row r="50" spans="1:28">
+    <row r="50" spans="1:28" hidden="1">
       <c r="A50">
         <v>7057</v>
       </c>
@@ -5182,7 +5192,7 @@
       <c r="AA50" s="10"/>
       <c r="AB50" s="10"/>
     </row>
-    <row r="51" spans="1:28">
+    <row r="51" spans="1:28" hidden="1">
       <c r="A51">
         <v>7058</v>
       </c>
@@ -5238,7 +5248,7 @@
       <c r="AA51" s="4"/>
       <c r="AB51" s="4"/>
     </row>
-    <row r="52" spans="1:28">
+    <row r="52" spans="1:28" hidden="1">
       <c r="A52">
         <v>7059</v>
       </c>
@@ -5294,7 +5304,7 @@
       <c r="AA52" s="10"/>
       <c r="AB52" s="10"/>
     </row>
-    <row r="53" spans="1:28">
+    <row r="53" spans="1:28" hidden="1">
       <c r="A53">
         <v>7060</v>
       </c>
@@ -5350,7 +5360,7 @@
       <c r="AA53" s="4"/>
       <c r="AB53" s="4"/>
     </row>
-    <row r="54" spans="1:28">
+    <row r="54" spans="1:28" hidden="1">
       <c r="A54">
         <v>7061</v>
       </c>
@@ -5406,7 +5416,7 @@
       <c r="AA54" s="10"/>
       <c r="AB54" s="10"/>
     </row>
-    <row r="55" spans="1:28">
+    <row r="55" spans="1:28" hidden="1">
       <c r="A55">
         <v>7062</v>
       </c>
@@ -5462,7 +5472,7 @@
       <c r="AA55" s="4"/>
       <c r="AB55" s="4"/>
     </row>
-    <row r="56" spans="1:28">
+    <row r="56" spans="1:28" hidden="1">
       <c r="A56">
         <v>7063</v>
       </c>
@@ -5574,7 +5584,7 @@
       <c r="AA57" s="5"/>
       <c r="AB57" s="5"/>
     </row>
-    <row r="58" spans="1:28">
+    <row r="58" spans="1:28" hidden="1">
       <c r="C58" s="34"/>
       <c r="D58" s="4"/>
       <c r="E58" s="20"/>
@@ -5594,7 +5604,7 @@
       <c r="AA58" s="10"/>
       <c r="AB58" s="10"/>
     </row>
-    <row r="59" spans="1:28">
+    <row r="59" spans="1:28" hidden="1">
       <c r="C59" s="5"/>
       <c r="D59" s="5"/>
       <c r="E59" s="20"/>

--- a/data/base/base implantação.xlsx
+++ b/data/base/base implantação.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/warruda_mgcontecnica_com_br/Documents/Documentos/python/Portal-implantacao-tmp/data/base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="817" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8121C6D9-33D7-4E41-90B9-5D5813A207D2}"/>
+  <xr:revisionPtr revIDLastSave="819" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2FEA312-5CAE-49F9-9EC8-857F7B907426}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/base/base implantação.xlsx
+++ b/data/base/base implantação.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30431"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30502"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/warruda_mgcontecnica_com_br/Documents/Documentos/python/Portal-implantacao-tmp/data/base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="819" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2FEA312-5CAE-49F9-9EC8-857F7B907426}"/>
+  <xr:revisionPtr revIDLastSave="821" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B29D8E6-238C-470E-9945-D977B602788C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2041,7 +2041,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" hidden="1">
+    <row r="2" spans="1:28">
       <c r="A2" s="4">
         <v>6812</v>
       </c>
@@ -2169,7 +2169,7 @@
       <c r="AA3" s="5"/>
       <c r="AB3" s="13"/>
     </row>
-    <row r="4" spans="1:28" hidden="1">
+    <row r="4" spans="1:28">
       <c r="A4">
         <v>6923</v>
       </c>
@@ -2237,7 +2237,7 @@
       <c r="AA4" s="5"/>
       <c r="AB4" s="5"/>
     </row>
-    <row r="5" spans="1:28" hidden="1">
+    <row r="5" spans="1:28">
       <c r="A5">
         <v>6924</v>
       </c>
@@ -2305,7 +2305,7 @@
       <c r="AA5" s="4"/>
       <c r="AB5" s="4"/>
     </row>
-    <row r="6" spans="1:28" hidden="1">
+    <row r="6" spans="1:28">
       <c r="A6">
         <v>6945</v>
       </c>
@@ -2373,7 +2373,7 @@
       <c r="AA6" s="5"/>
       <c r="AB6" s="5"/>
     </row>
-    <row r="7" spans="1:28" hidden="1">
+    <row r="7" spans="1:28">
       <c r="A7">
         <v>6947</v>
       </c>
@@ -2441,7 +2441,7 @@
       <c r="AA7" s="5"/>
       <c r="AB7" s="5"/>
     </row>
-    <row r="8" spans="1:28" hidden="1">
+    <row r="8" spans="1:28">
       <c r="A8">
         <v>6949</v>
       </c>
@@ -2509,7 +2509,7 @@
       <c r="AA8" s="4"/>
       <c r="AB8" s="4"/>
     </row>
-    <row r="9" spans="1:28" hidden="1">
+    <row r="9" spans="1:28">
       <c r="A9">
         <v>6962</v>
       </c>
@@ -2575,7 +2575,7 @@
       <c r="AA9" s="4"/>
       <c r="AB9" s="4"/>
     </row>
-    <row r="10" spans="1:28" hidden="1">
+    <row r="10" spans="1:28">
       <c r="A10">
         <v>6963</v>
       </c>
@@ -2911,7 +2911,7 @@
       <c r="AA14" s="5"/>
       <c r="AB14" s="5"/>
     </row>
-    <row r="15" spans="1:28" hidden="1">
+    <row r="15" spans="1:28">
       <c r="A15">
         <v>6976</v>
       </c>
@@ -2979,7 +2979,7 @@
       <c r="AA15" s="4"/>
       <c r="AB15" s="4"/>
     </row>
-    <row r="16" spans="1:28" hidden="1">
+    <row r="16" spans="1:28">
       <c r="A16">
         <v>6977</v>
       </c>
@@ -3041,7 +3041,7 @@
       <c r="AA16" s="5"/>
       <c r="AB16" s="5"/>
     </row>
-    <row r="17" spans="1:28" hidden="1">
+    <row r="17" spans="1:28">
       <c r="A17">
         <v>6978</v>
       </c>
@@ -3233,7 +3233,7 @@
       <c r="AA19" s="4"/>
       <c r="AB19" s="4"/>
     </row>
-    <row r="20" spans="1:28" hidden="1">
+    <row r="20" spans="1:28">
       <c r="A20">
         <v>6989</v>
       </c>
@@ -3547,7 +3547,7 @@
       <c r="AA24" s="4"/>
       <c r="AB24" s="4"/>
     </row>
-    <row r="25" spans="1:28" hidden="1">
+    <row r="25" spans="1:28">
       <c r="A25">
         <v>6995</v>
       </c>
@@ -3615,7 +3615,7 @@
       <c r="AA25" s="5"/>
       <c r="AB25" s="5"/>
     </row>
-    <row r="26" spans="1:28" hidden="1">
+    <row r="26" spans="1:28">
       <c r="A26">
         <v>7005</v>
       </c>
@@ -3677,7 +3677,7 @@
       <c r="AA26" s="4"/>
       <c r="AB26" s="4"/>
     </row>
-    <row r="27" spans="1:28" hidden="1">
+    <row r="27" spans="1:28">
       <c r="A27">
         <v>7006</v>
       </c>
@@ -3935,7 +3935,7 @@
       <c r="AA30" s="4"/>
       <c r="AB30" s="4"/>
     </row>
-    <row r="31" spans="1:28" hidden="1">
+    <row r="31" spans="1:28">
       <c r="A31">
         <v>7014</v>
       </c>
@@ -4067,7 +4067,7 @@
       <c r="AA32" s="4"/>
       <c r="AB32" s="4"/>
     </row>
-    <row r="33" spans="1:28" hidden="1">
+    <row r="33" spans="1:28">
       <c r="A33">
         <v>7016</v>
       </c>
@@ -4331,7 +4331,7 @@
       <c r="AA36" s="4"/>
       <c r="AB36" s="4"/>
     </row>
-    <row r="37" spans="1:28" hidden="1">
+    <row r="37" spans="1:28">
       <c r="A37">
         <v>7020</v>
       </c>
@@ -4397,7 +4397,7 @@
       <c r="AA37" s="10"/>
       <c r="AB37" s="10"/>
     </row>
-    <row r="38" spans="1:28" hidden="1">
+    <row r="38" spans="1:28">
       <c r="A38">
         <v>7021</v>
       </c>
@@ -4688,7 +4688,7 @@
       <c r="AA41" s="4"/>
       <c r="AB41" s="4"/>
     </row>
-    <row r="42" spans="1:28" hidden="1">
+    <row r="42" spans="1:28">
       <c r="A42">
         <v>7048</v>
       </c>
@@ -4744,7 +4744,7 @@
       <c r="AA42" s="10"/>
       <c r="AB42" s="10"/>
     </row>
-    <row r="43" spans="1:28" hidden="1">
+    <row r="43" spans="1:28">
       <c r="A43">
         <v>7049</v>
       </c>
@@ -4800,7 +4800,7 @@
       <c r="AA43" s="4"/>
       <c r="AB43" s="4"/>
     </row>
-    <row r="44" spans="1:28" hidden="1">
+    <row r="44" spans="1:28">
       <c r="A44">
         <v>7050</v>
       </c>
@@ -4842,6 +4842,9 @@
       </c>
       <c r="O44" t="s">
         <v>38</v>
+      </c>
+      <c r="S44" s="1">
+        <v>46279</v>
       </c>
       <c r="T44" t="s">
         <v>38</v>
@@ -4856,7 +4859,7 @@
       <c r="AA44" s="15"/>
       <c r="AB44" s="15"/>
     </row>
-    <row r="45" spans="1:28" hidden="1">
+    <row r="45" spans="1:28">
       <c r="A45">
         <v>7052</v>
       </c>
@@ -4912,7 +4915,7 @@
       <c r="AA45" s="4"/>
       <c r="AB45" s="4"/>
     </row>
-    <row r="46" spans="1:28" hidden="1">
+    <row r="46" spans="1:28">
       <c r="A46">
         <v>7053</v>
       </c>
@@ -4968,7 +4971,7 @@
       <c r="AA46" s="10"/>
       <c r="AB46" s="10"/>
     </row>
-    <row r="47" spans="1:28" hidden="1">
+    <row r="47" spans="1:28">
       <c r="A47">
         <v>7054</v>
       </c>
@@ -5024,7 +5027,7 @@
       <c r="AA47" s="4"/>
       <c r="AB47" s="4"/>
     </row>
-    <row r="48" spans="1:28" hidden="1">
+    <row r="48" spans="1:28">
       <c r="A48">
         <v>7055</v>
       </c>
@@ -5080,7 +5083,7 @@
       <c r="AA48" s="10"/>
       <c r="AB48" s="10"/>
     </row>
-    <row r="49" spans="1:28" hidden="1">
+    <row r="49" spans="1:28">
       <c r="A49">
         <v>7056</v>
       </c>
@@ -5136,7 +5139,7 @@
       <c r="AA49" s="5"/>
       <c r="AB49" s="5"/>
     </row>
-    <row r="50" spans="1:28" hidden="1">
+    <row r="50" spans="1:28">
       <c r="A50">
         <v>7057</v>
       </c>
@@ -5192,7 +5195,7 @@
       <c r="AA50" s="10"/>
       <c r="AB50" s="10"/>
     </row>
-    <row r="51" spans="1:28" hidden="1">
+    <row r="51" spans="1:28">
       <c r="A51">
         <v>7058</v>
       </c>
@@ -5248,7 +5251,7 @@
       <c r="AA51" s="4"/>
       <c r="AB51" s="4"/>
     </row>
-    <row r="52" spans="1:28" hidden="1">
+    <row r="52" spans="1:28">
       <c r="A52">
         <v>7059</v>
       </c>
@@ -5304,7 +5307,7 @@
       <c r="AA52" s="10"/>
       <c r="AB52" s="10"/>
     </row>
-    <row r="53" spans="1:28" hidden="1">
+    <row r="53" spans="1:28">
       <c r="A53">
         <v>7060</v>
       </c>
@@ -5360,7 +5363,7 @@
       <c r="AA53" s="4"/>
       <c r="AB53" s="4"/>
     </row>
-    <row r="54" spans="1:28" hidden="1">
+    <row r="54" spans="1:28">
       <c r="A54">
         <v>7061</v>
       </c>
@@ -5416,7 +5419,7 @@
       <c r="AA54" s="10"/>
       <c r="AB54" s="10"/>
     </row>
-    <row r="55" spans="1:28" hidden="1">
+    <row r="55" spans="1:28">
       <c r="A55">
         <v>7062</v>
       </c>
@@ -5472,7 +5475,7 @@
       <c r="AA55" s="4"/>
       <c r="AB55" s="4"/>
     </row>
-    <row r="56" spans="1:28" hidden="1">
+    <row r="56" spans="1:28">
       <c r="A56">
         <v>7063</v>
       </c>
@@ -5584,7 +5587,7 @@
       <c r="AA57" s="5"/>
       <c r="AB57" s="5"/>
     </row>
-    <row r="58" spans="1:28" hidden="1">
+    <row r="58" spans="1:28">
       <c r="C58" s="34"/>
       <c r="D58" s="4"/>
       <c r="E58" s="20"/>
@@ -5604,7 +5607,7 @@
       <c r="AA58" s="10"/>
       <c r="AB58" s="10"/>
     </row>
-    <row r="59" spans="1:28" hidden="1">
+    <row r="59" spans="1:28">
       <c r="C59" s="5"/>
       <c r="D59" s="5"/>
       <c r="E59" s="20"/>

--- a/data/base/base implantação.xlsx
+++ b/data/base/base implantação.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30502"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30524"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/warruda_mgcontecnica_com_br/Documents/Documentos/python/Portal-implantacao-tmp/data/base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="821" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B29D8E6-238C-470E-9945-D977B602788C}"/>
+  <xr:revisionPtr revIDLastSave="841" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79B31CB0-5618-4F0E-9B20-EEDE99858C10}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="350">
   <si>
     <t>ID</t>
   </si>
@@ -1038,6 +1038,54 @@
   </si>
   <si>
     <t>FRANCERLEY RAMOS DE CARVALHO;SUELY ROSA VIEIRA DE CARVALHO;</t>
+  </si>
+  <si>
+    <t>MINI SUPERMERCADO TULIO LTDA</t>
+  </si>
+  <si>
+    <t>SUPER GOIAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUA JOSÉ HERMANO (APTO 2303), Num.: 1799 Comple.: QUADRA 5 LA LOTE 06, Bairro: SETOR CAMPINAS / </t>
+  </si>
+  <si>
+    <t>supergoias1@hotmail.com;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(62) 3233-8451 / </t>
+  </si>
+  <si>
+    <t>AMAILTON FONSECA MENEZES;</t>
+  </si>
+  <si>
+    <t>GOIAS SERVICE LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUA JOSÉ HERMANO, Num.: 1781 Comple.: QUADRA 05 - LOTE 06 - SALA 01, Bairro: SETOR CAMPINAS / </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(62) 2575-1800 / </t>
+  </si>
+  <si>
+    <t>ROSANGELA MARIA GALDINO;</t>
+  </si>
+  <si>
+    <t>RRV RECURSOS HUMANOS E REPRESENTACOES LTDA</t>
+  </si>
+  <si>
+    <t>RRV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUA CARLOS WEBER, Num.: 195 Comple.: SALA 02, Bairro: VILA LEOPOLDINA / </t>
+  </si>
+  <si>
+    <t>rogerio.marin@rrvrecursoshumanos.com.br; aguinaldo.aguiar@rrvrecursoshumanos.com.br;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(11) 99456-1931 / </t>
+  </si>
+  <si>
+    <t>ROGÉRIO MARIN;ROBERTO SCHIAVON;VALMIR DE CASTRO;</t>
   </si>
 </sst>
 </file>
@@ -1105,7 +1153,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -1218,12 +1266,36 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF44B3E1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF44B3E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF44B3E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF44B3E1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF44B3E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1263,6 +1335,12 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -1563,8 +1641,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:AB59">
-  <autoFilter ref="A1:AB59" xr:uid="{00000000-0009-0000-0100-000001000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:AB60">
+  <autoFilter ref="A1:AB60" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="11">
       <filters>
         <filter val="Varejo"/>
@@ -1922,7 +2000,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB59"/>
+  <dimension ref="A1:AB60"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
@@ -4728,8 +4806,11 @@
       <c r="M42" s="4" t="s">
         <v>265</v>
       </c>
+      <c r="N42" s="1">
+        <v>46279</v>
+      </c>
       <c r="O42" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="T42" t="s">
         <v>38</v>
@@ -4784,8 +4865,11 @@
       <c r="M43" s="5" t="s">
         <v>271</v>
       </c>
+      <c r="N43" s="1">
+        <v>46282</v>
+      </c>
       <c r="O43" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="T43" t="s">
         <v>38</v>
@@ -4840,8 +4924,11 @@
       <c r="M44" s="4" t="s">
         <v>277</v>
       </c>
+      <c r="N44" s="1">
+        <v>46282</v>
+      </c>
       <c r="O44" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="S44" s="1">
         <v>46279</v>
@@ -4899,8 +4986,11 @@
       <c r="M45" s="5" t="s">
         <v>283</v>
       </c>
+      <c r="N45" s="1">
+        <v>46290</v>
+      </c>
       <c r="O45" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="T45" t="s">
         <v>38</v>
@@ -4955,8 +5045,11 @@
       <c r="M46" s="4" t="s">
         <v>287</v>
       </c>
+      <c r="N46" s="1">
+        <v>46290</v>
+      </c>
       <c r="O46" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="T46" t="s">
         <v>38</v>
@@ -5011,8 +5104,11 @@
       <c r="M47" s="5" t="s">
         <v>292</v>
       </c>
+      <c r="N47" s="1">
+        <v>46290</v>
+      </c>
       <c r="O47" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="T47" t="s">
         <v>38</v>
@@ -5067,8 +5163,11 @@
       <c r="M48" s="4" t="s">
         <v>297</v>
       </c>
+      <c r="N48" s="1">
+        <v>46290</v>
+      </c>
       <c r="O48" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="T48" t="s">
         <v>38</v>
@@ -5123,8 +5222,11 @@
       <c r="M49" s="5" t="s">
         <v>300</v>
       </c>
+      <c r="N49" s="1">
+        <v>46290</v>
+      </c>
       <c r="O49" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="T49" t="s">
         <v>38</v>
@@ -5179,8 +5281,11 @@
       <c r="M50" s="4" t="s">
         <v>308</v>
       </c>
+      <c r="N50" s="1">
+        <v>46288</v>
+      </c>
       <c r="O50" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="T50" t="s">
         <v>38</v>
@@ -5235,8 +5340,11 @@
       <c r="M51" s="5" t="s">
         <v>311</v>
       </c>
+      <c r="N51" s="1">
+        <v>46288</v>
+      </c>
       <c r="O51" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="T51" t="s">
         <v>38</v>
@@ -5291,8 +5399,11 @@
       <c r="M52" s="4" t="s">
         <v>311</v>
       </c>
+      <c r="N52" s="1">
+        <v>46288</v>
+      </c>
       <c r="O52" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="T52" t="s">
         <v>38</v>
@@ -5347,8 +5458,11 @@
       <c r="M53" s="5" t="s">
         <v>318</v>
       </c>
+      <c r="N53" s="1">
+        <v>46288</v>
+      </c>
       <c r="O53" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="T53" t="s">
         <v>38</v>
@@ -5403,8 +5517,11 @@
       <c r="M54" s="4" t="s">
         <v>318</v>
       </c>
+      <c r="N54" s="1">
+        <v>46288</v>
+      </c>
       <c r="O54" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="T54" t="s">
         <v>38</v>
@@ -5459,8 +5576,11 @@
       <c r="M55" s="5" t="s">
         <v>324</v>
       </c>
+      <c r="N55" s="1">
+        <v>46288</v>
+      </c>
       <c r="O55" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="T55" t="s">
         <v>38</v>
@@ -5515,8 +5635,11 @@
       <c r="M56" s="4" t="s">
         <v>327</v>
       </c>
+      <c r="N56" s="1">
+        <v>46288</v>
+      </c>
       <c r="O56" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="T56" t="s">
         <v>38</v>
@@ -5588,67 +5711,195 @@
       <c r="AB57" s="5"/>
     </row>
     <row r="58" spans="1:28">
-      <c r="C58" s="34"/>
-      <c r="D58" s="4"/>
-      <c r="E58" s="20"/>
-      <c r="F58" s="4"/>
-      <c r="G58" s="20"/>
-      <c r="H58" s="20"/>
-      <c r="I58" s="4"/>
-      <c r="J58" s="4"/>
-      <c r="K58" s="4"/>
-      <c r="L58" s="4"/>
-      <c r="M58" s="4"/>
+      <c r="A58" s="35">
+        <v>7106</v>
+      </c>
+      <c r="B58" s="36" t="s">
+        <v>334</v>
+      </c>
+      <c r="C58" s="34">
+        <v>46327</v>
+      </c>
+      <c r="D58" s="36" t="s">
+        <v>335</v>
+      </c>
+      <c r="E58" s="36" t="s">
+        <v>170</v>
+      </c>
+      <c r="F58" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="G58" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="H58" s="36" t="s">
+        <v>74</v>
+      </c>
+      <c r="I58" s="36" t="s">
+        <v>336</v>
+      </c>
+      <c r="J58" s="36" t="s">
+        <v>337</v>
+      </c>
+      <c r="K58" s="36" t="s">
+        <v>338</v>
+      </c>
+      <c r="L58" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="M58" s="36" t="s">
+        <v>339</v>
+      </c>
+      <c r="O58" t="s">
+        <v>38</v>
+      </c>
+      <c r="T58" t="s">
+        <v>38</v>
+      </c>
       <c r="U58" s="5"/>
       <c r="V58" s="5"/>
       <c r="W58" s="5"/>
-      <c r="Y58" s="5"/>
+      <c r="Y58" s="5" t="s">
+        <v>38</v>
+      </c>
       <c r="Z58" s="10"/>
       <c r="AA58" s="10"/>
       <c r="AB58" s="10"/>
     </row>
     <row r="59" spans="1:28">
-      <c r="C59" s="5"/>
-      <c r="D59" s="5"/>
-      <c r="E59" s="20"/>
-      <c r="F59" s="5"/>
-      <c r="G59" s="20"/>
-      <c r="H59" s="20"/>
-      <c r="I59" s="9"/>
-      <c r="J59" s="5"/>
-      <c r="K59" s="5"/>
-      <c r="L59" s="5"/>
-      <c r="M59" s="5"/>
+      <c r="A59" s="37">
+        <v>7107</v>
+      </c>
+      <c r="B59" s="38" t="s">
+        <v>340</v>
+      </c>
+      <c r="C59" s="34">
+        <v>46327</v>
+      </c>
+      <c r="D59" s="38" t="s">
+        <v>335</v>
+      </c>
+      <c r="E59" s="38" t="s">
+        <v>170</v>
+      </c>
+      <c r="F59" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="G59" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="H59" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="I59" s="38" t="s">
+        <v>341</v>
+      </c>
+      <c r="J59" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="K59" s="38" t="s">
+        <v>342</v>
+      </c>
+      <c r="L59" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="M59" s="38" t="s">
+        <v>343</v>
+      </c>
+      <c r="O59" t="s">
+        <v>38</v>
+      </c>
+      <c r="T59" t="s">
+        <v>38</v>
+      </c>
       <c r="U59" s="4"/>
       <c r="V59" s="4"/>
       <c r="W59" s="4"/>
-      <c r="Y59" s="5"/>
+      <c r="Y59" s="5" t="s">
+        <v>38</v>
+      </c>
       <c r="Z59" s="4"/>
       <c r="AA59" s="4"/>
       <c r="AB59" s="4"/>
     </row>
+    <row r="60" spans="1:28">
+      <c r="A60" s="39">
+        <v>7105</v>
+      </c>
+      <c r="B60" s="39" t="s">
+        <v>344</v>
+      </c>
+      <c r="C60" s="34">
+        <v>46327</v>
+      </c>
+      <c r="D60" s="39" t="s">
+        <v>345</v>
+      </c>
+      <c r="E60" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="F60" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="G60" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="H60" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="I60" s="39" t="s">
+        <v>346</v>
+      </c>
+      <c r="J60" s="39" t="s">
+        <v>347</v>
+      </c>
+      <c r="K60" s="39" t="s">
+        <v>348</v>
+      </c>
+      <c r="L60" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="M60" s="39" t="s">
+        <v>349</v>
+      </c>
+      <c r="O60" t="s">
+        <v>38</v>
+      </c>
+      <c r="T60" t="s">
+        <v>38</v>
+      </c>
+      <c r="U60" s="40"/>
+      <c r="V60" s="40"/>
+      <c r="W60" s="40"/>
+      <c r="Y60" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z60" s="40"/>
+      <c r="AA60" s="40"/>
+      <c r="AB60" s="40"/>
+    </row>
   </sheetData>
   <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S60:S1048576" xr:uid="{F98435C8-1E0D-420B-93AD-1750A0AD1E4D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S61:S1048576" xr:uid="{F98435C8-1E0D-420B-93AD-1750A0AD1E4D}">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Insira uma data" error="O valor digitado deve ser uma data." promptTitle="Insira uma data" prompt="Use o formato dd/mm/aaaa" sqref="N60:N1048576" xr:uid="{E30AD5C4-327F-471C-A8FE-8847233F32A8}">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Insira uma data" error="O valor digitado deve ser uma data." promptTitle="Insira uma data" prompt="Use o formato dd/mm/aaaa" sqref="N61:N1048576" xr:uid="{E30AD5C4-327F-471C-A8FE-8847233F32A8}">
       <formula1>46023</formula1>
       <formula2>46387</formula2>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="O valor digitado deve ser uma data." promptTitle="Insira uma data " prompt="Use o formato dd/mm/aaaa" sqref="P60:P1048576" xr:uid="{C38150F2-07B9-4A40-94E9-2F60486C9785}">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="O valor digitado deve ser uma data." promptTitle="Insira uma data " prompt="Use o formato dd/mm/aaaa" sqref="P61:P1048576" xr:uid="{C38150F2-07B9-4A40-94E9-2F60486C9785}">
       <formula1>46023</formula1>
       <formula2>46387</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Sim ou Não" promptTitle="Sim ou Não" sqref="Q60:Q1048576 T2:T59 O2:O1048576 Y2:Y59" xr:uid="{A33B9050-2903-44EC-9C32-C551C6DD218F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Sim ou Não" promptTitle="Sim ou Não" sqref="Q61:Q1048576 T2:T60 Y2:Y60 O2:O1048576" xr:uid="{A33B9050-2903-44EC-9C32-C551C6DD218F}">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:R59" xr:uid="{66A39B3A-FA32-40B1-A327-70A015F2D105}"/>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Data inválida" error="Informe uma data entre 01/01/2026 e 31/12/2026." sqref="N2:N59 X2:X59 S2:S59" xr:uid="{7CAE3D66-F37A-4DC6-831F-B6867AFE899B}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:R60" xr:uid="{66A39B3A-FA32-40B1-A327-70A015F2D105}"/>
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Data inválida" error="Informe uma data entre 01/01/2026 e 31/12/2026." sqref="S2:S60 X2:X60 N2:N60" xr:uid="{7CAE3D66-F37A-4DC6-831F-B6867AFE899B}">
       <formula1>46023</formula1>
       <formula2>46387</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Sim ou Não" promptTitle="Sim ou Não" sqref="O2:O59" xr:uid="{DA1ED78E-091C-41E8-9E96-D1D63B85A012}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Sim ou Não" promptTitle="Sim ou Não" sqref="O2:O60" xr:uid="{DA1ED78E-091C-41E8-9E96-D1D63B85A012}">
       <formula1>"Sim;Não"</formula1>
     </dataValidation>
     <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="O valor digitado deve ser uma data." promptTitle="Insira uma data" prompt="Use o formato dd/mm/aaaa" sqref="R38:R1048576" xr:uid="{B80591A4-C609-4DDF-A9CB-595A54330A1C}">

--- a/data/base/base implantação.xlsx
+++ b/data/base/base implantação.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/warruda_mgcontecnica_com_br/Documents/Documentos/python/Portal-implantacao-tmp/data/base/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="841" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79B31CB0-5618-4F0E-9B20-EEDE99858C10}"/>
+  <xr:revisionPtr revIDLastSave="843" documentId="11_4F56B3A8CB9C0E20059044E3BFE40D0DED129F61" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F84A81AD-F879-4151-BFAA-EBF9C25D9EDB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1295,7 +1295,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1335,12 +1335,8 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -3159,9 +3155,11 @@
       <c r="M17" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="N17" s="4"/>
+      <c r="N17" s="7">
+        <v>46294</v>
+      </c>
       <c r="O17" s="4" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
@@ -5714,40 +5712,40 @@
       <c r="A58" s="35">
         <v>7106</v>
       </c>
-      <c r="B58" s="36" t="s">
+      <c r="B58" s="21" t="s">
         <v>334</v>
       </c>
       <c r="C58" s="34">
         <v>46327</v>
       </c>
-      <c r="D58" s="36" t="s">
+      <c r="D58" s="21" t="s">
         <v>335</v>
       </c>
-      <c r="E58" s="36" t="s">
+      <c r="E58" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="F58" s="36" t="s">
+      <c r="F58" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="G58" s="36" t="s">
+      <c r="G58" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="H58" s="36" t="s">
+      <c r="H58" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="I58" s="36" t="s">
+      <c r="I58" s="21" t="s">
         <v>336</v>
       </c>
-      <c r="J58" s="36" t="s">
+      <c r="J58" s="21" t="s">
         <v>337</v>
       </c>
-      <c r="K58" s="36" t="s">
+      <c r="K58" s="21" t="s">
         <v>338</v>
       </c>
-      <c r="L58" s="36" t="s">
+      <c r="L58" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="M58" s="36" t="s">
+      <c r="M58" s="21" t="s">
         <v>339</v>
       </c>
       <c r="O58" t="s">
@@ -5767,43 +5765,43 @@
       <c r="AB58" s="10"/>
     </row>
     <row r="59" spans="1:28">
-      <c r="A59" s="37">
+      <c r="A59" s="36">
         <v>7107</v>
       </c>
-      <c r="B59" s="38" t="s">
+      <c r="B59" s="23" t="s">
         <v>340</v>
       </c>
       <c r="C59" s="34">
         <v>46327</v>
       </c>
-      <c r="D59" s="38" t="s">
+      <c r="D59" s="23" t="s">
         <v>335</v>
       </c>
-      <c r="E59" s="38" t="s">
+      <c r="E59" s="23" t="s">
         <v>170</v>
       </c>
-      <c r="F59" s="38" t="s">
+      <c r="F59" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="G59" s="38" t="s">
+      <c r="G59" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="H59" s="38" t="s">
+      <c r="H59" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="I59" s="38" t="s">
+      <c r="I59" s="23" t="s">
         <v>341</v>
       </c>
-      <c r="J59" s="38" t="s">
+      <c r="J59" s="23" t="s">
         <v>337</v>
       </c>
-      <c r="K59" s="38" t="s">
+      <c r="K59" s="23" t="s">
         <v>342</v>
       </c>
-      <c r="L59" s="38" t="s">
+      <c r="L59" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="M59" s="38" t="s">
+      <c r="M59" s="23" t="s">
         <v>343</v>
       </c>
       <c r="O59" t="s">
@@ -5823,43 +5821,43 @@
       <c r="AB59" s="4"/>
     </row>
     <row r="60" spans="1:28">
-      <c r="A60" s="39">
+      <c r="A60">
         <v>7105</v>
       </c>
-      <c r="B60" s="39" t="s">
+      <c r="B60" t="s">
         <v>344</v>
       </c>
       <c r="C60" s="34">
         <v>46327</v>
       </c>
-      <c r="D60" s="39" t="s">
+      <c r="D60" t="s">
         <v>345</v>
       </c>
-      <c r="E60" s="39" t="s">
+      <c r="E60" t="s">
         <v>64</v>
       </c>
-      <c r="F60" s="39" t="s">
+      <c r="F60" t="s">
         <v>65</v>
       </c>
-      <c r="G60" s="39" t="s">
+      <c r="G60" t="s">
         <v>66</v>
       </c>
-      <c r="H60" s="39" t="s">
+      <c r="H60" t="s">
         <v>44</v>
       </c>
-      <c r="I60" s="39" t="s">
+      <c r="I60" t="s">
         <v>346</v>
       </c>
-      <c r="J60" s="39" t="s">
+      <c r="J60" t="s">
         <v>347</v>
       </c>
-      <c r="K60" s="39" t="s">
+      <c r="K60" t="s">
         <v>348</v>
       </c>
-      <c r="L60" s="39" t="s">
+      <c r="L60" t="s">
         <v>36</v>
       </c>
-      <c r="M60" s="39" t="s">
+      <c r="M60" t="s">
         <v>349</v>
       </c>
       <c r="O60" t="s">
@@ -5868,15 +5866,15 @@
       <c r="T60" t="s">
         <v>38</v>
       </c>
-      <c r="U60" s="40"/>
-      <c r="V60" s="40"/>
-      <c r="W60" s="40"/>
-      <c r="Y60" s="40" t="s">
-        <v>38</v>
-      </c>
-      <c r="Z60" s="40"/>
-      <c r="AA60" s="40"/>
-      <c r="AB60" s="40"/>
+      <c r="U60" s="5"/>
+      <c r="V60" s="5"/>
+      <c r="W60" s="5"/>
+      <c r="Y60" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z60" s="5"/>
+      <c r="AA60" s="5"/>
+      <c r="AB60" s="5"/>
     </row>
   </sheetData>
   <dataValidations count="8">
